--- a/sba_application/09_financial_model/Azalea_Hospice_Investor_Package.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_Investor_Package.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Investment Options" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Unit Economics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Options" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Economics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="rhc_tier1">Inputs!$B$5</definedName>
@@ -99,8 +99,8 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0.00;(#,##0.00);&quot;&quot;"/>
     <numFmt numFmtId="174" formatCode="#,##0.00;(#,##0.00)"/>
   </numFmts>
@@ -231,7 +231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -271,11 +271,44 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -347,7 +380,7 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -365,7 +398,7 @@
     <xf numFmtId="165" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -418,7 +451,7 @@
     <xf numFmtId="169" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -450,13 +483,26 @@
     <xf numFmtId="174" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3467,7 +3513,7 @@
         </is>
       </c>
       <c r="B110" s="9" t="n">
-        <v>500000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="111">
@@ -3497,7 +3543,7 @@
         </is>
       </c>
       <c r="B113" s="9" t="n">
-        <v>250000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="114">
@@ -3715,11 +3761,11 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>Opening cash = equity + loan - startup - capex</t>
+          <t>Opening cash = equity + loan - startup - capex - license (paid at close)</t>
         </is>
       </c>
       <c r="B139" s="23">
-        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117</f>
+        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117-Inputs!$B$120</f>
         <v/>
       </c>
     </row>
@@ -3738,10 +3784,10 @@
   <mergeCells count="18">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A16:V16"/>
+    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A137:V137"/>
+    <mergeCell ref="A90:V90"/>
     <mergeCell ref="A76:V76"/>
-    <mergeCell ref="A90:V90"/>
-    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A85:V85"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A80:V80"/>
@@ -3751,7 +3797,7 @@
     <mergeCell ref="A27:V27"/>
     <mergeCell ref="A105:V105"/>
     <mergeCell ref="A69:V69"/>
-    <mergeCell ref="A35:V35"/>
+    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A4:V4"/>
     <mergeCell ref="A24:V24"/>
   </mergeCells>
@@ -3804,7 +3850,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Debt Schedule - SBA 7(a) + Hickory license seller note | Combined DSCR shown (target &gt;= 1.25x)</t>
+          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4453,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HICKORY LICENSE SELLER NOTE ($300K, 6%, 36 mo)</t>
+          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
         </is>
       </c>
     </row>
@@ -4417,9 +4463,8 @@
           <t>Beginning balance</t>
         </is>
       </c>
-      <c r="C18" s="26">
-        <f>Inputs!$B$120</f>
-        <v/>
+      <c r="C18" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="D18" s="24">
         <f>C22</f>
@@ -5207,83 +5252,83 @@
           <t>COMBINED DSCR (period)</t>
         </is>
       </c>
-      <c r="C29" s="62">
+      <c r="C29" s="71">
         <f>IF(C27=0,0,C28/C27)</f>
         <v/>
       </c>
-      <c r="D29" s="62">
+      <c r="D29" s="71">
         <f>IF(D27=0,0,D28/D27)</f>
         <v/>
       </c>
-      <c r="E29" s="62">
+      <c r="E29" s="71">
         <f>IF(E27=0,0,E28/E27)</f>
         <v/>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="71">
         <f>IF(F27=0,0,F28/F27)</f>
         <v/>
       </c>
-      <c r="G29" s="62">
+      <c r="G29" s="71">
         <f>IF(G27=0,0,G28/G27)</f>
         <v/>
       </c>
-      <c r="H29" s="62">
+      <c r="H29" s="71">
         <f>IF(H27=0,0,H28/H27)</f>
         <v/>
       </c>
-      <c r="I29" s="62">
+      <c r="I29" s="71">
         <f>IF(I27=0,0,I28/I27)</f>
         <v/>
       </c>
-      <c r="J29" s="62">
+      <c r="J29" s="71">
         <f>IF(J27=0,0,J28/J27)</f>
         <v/>
       </c>
-      <c r="K29" s="62">
+      <c r="K29" s="71">
         <f>IF(K27=0,0,K28/K27)</f>
         <v/>
       </c>
-      <c r="L29" s="62">
+      <c r="L29" s="71">
         <f>IF(L27=0,0,L28/L27)</f>
         <v/>
       </c>
-      <c r="M29" s="62">
+      <c r="M29" s="71">
         <f>IF(M27=0,0,M28/M27)</f>
         <v/>
       </c>
-      <c r="N29" s="62">
+      <c r="N29" s="71">
         <f>IF(N27=0,0,N28/N27)</f>
         <v/>
       </c>
-      <c r="O29" s="62">
+      <c r="O29" s="71">
         <f>IF(O27=0,0,O28/O27)</f>
         <v/>
       </c>
-      <c r="P29" s="62">
+      <c r="P29" s="71">
         <f>IF(P27=0,0,P28/P27)</f>
         <v/>
       </c>
-      <c r="Q29" s="62">
+      <c r="Q29" s="71">
         <f>IF(Q27=0,0,Q28/Q27)</f>
         <v/>
       </c>
-      <c r="R29" s="62">
+      <c r="R29" s="71">
         <f>IF(R27=0,0,R28/R27)</f>
         <v/>
       </c>
-      <c r="S29" s="62">
+      <c r="S29" s="71">
         <f>IF(S27=0,0,S28/S27)</f>
         <v/>
       </c>
-      <c r="T29" s="62">
+      <c r="T29" s="71">
         <f>IF(T27=0,0,T28/T27)</f>
         <v/>
       </c>
-      <c r="U29" s="62">
+      <c r="U29" s="71">
         <f>IF(U27=0,0,U28/U27)</f>
         <v/>
       </c>
-      <c r="V29" s="62">
+      <c r="V29" s="71">
         <f>IF(V27=0,0,V28/V27)</f>
         <v/>
       </c>
@@ -7646,9 +7691,8 @@
           <t>Hickory license note balance</t>
         </is>
       </c>
-      <c r="B34" s="26">
-        <f>Inputs!$B$120</f>
-        <v/>
+      <c r="B34" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="26">
         <f>'Debt Schedule'!C22</f>
@@ -8582,7 +8626,7 @@
           <t>Exit EBITDA multiple</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="67" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8707,7 +8751,7 @@
           <t>MOIC (gross multiple)</t>
         </is>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="68">
         <f>SUM(C12:E12)/$B$6</f>
         <v/>
       </c>
@@ -8813,7 +8857,7 @@
           <t>Exit EBITDA multiple</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="67" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9171,15 +9215,15 @@
           <t>MOIC (gross multiple)</t>
         </is>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="68">
         <f>SUM(C24:G24)/$B$5</f>
         <v/>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="68">
         <f>SUM(C25:G25)/$B$5</f>
         <v/>
       </c>
-      <c r="F32" s="31">
+      <c r="F32" s="68">
         <f>SUM(C26:G26)/$B$5</f>
         <v/>
       </c>
@@ -9240,16 +9284,19 @@
           <t>Lowest risk | fixed yield</t>
         </is>
       </c>
+      <c r="C37" s="69" t="n"/>
       <c r="D37" s="37" t="inlineStr">
         <is>
           <t>Medium risk | upside option</t>
         </is>
       </c>
+      <c r="E37" s="69" t="n"/>
       <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Highest risk | highest upside</t>
         </is>
       </c>
+      <c r="G37" s="69" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
@@ -9520,10 +9567,10 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="D31:E31"/>
     <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D31:E31"/>
     <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A43:G43"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="F12:G12"/>
@@ -10359,83 +10406,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="70">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="70">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="70">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="70">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="70">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="70">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="70">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="50">
+      <c r="J12" s="70">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="50">
+      <c r="K12" s="70">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="50">
+      <c r="L12" s="70">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="50">
+      <c r="M12" s="70">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="50">
+      <c r="N12" s="70">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="50">
+      <c r="O12" s="70">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="50">
+      <c r="P12" s="70">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="50">
+      <c r="Q12" s="70">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="50">
+      <c r="R12" s="70">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="50">
+      <c r="S12" s="70">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="50">
+      <c r="T12" s="70">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="50">
+      <c r="U12" s="70">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="50">
+      <c r="V12" s="70">
         <f>V10*V11</f>
         <v/>
       </c>

--- a/sba_application/09_financial_model/Azalea_Hospice_Investor_Package.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_Investor_Package.xlsx
@@ -99,8 +99,8 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0.00;(#,##0.00);&quot;&quot;"/>
     <numFmt numFmtId="174" formatCode="#,##0.00;(#,##0.00)"/>
   </numFmts>
@@ -231,7 +231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -271,44 +271,11 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -380,7 +347,7 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -398,7 +365,7 @@
     <xf numFmtId="165" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -451,7 +418,7 @@
     <xf numFmtId="169" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -483,26 +450,13 @@
     <xf numFmtId="174" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1269,7 +1223,7 @@
     </comment>
     <comment ref="B110" authorId="0" shapeId="0">
       <text>
-        <t>Sized to fund ramp-period operating need + startup costs. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Sized to pay the seller in full at close + fund startup costs and working-capital reserve. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0" shapeId="0">
@@ -1284,7 +1238,7 @@
     </comment>
     <comment ref="B113" authorId="0" shapeId="0">
       <text>
-        <t>FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Cash capital contribution by James Bullard (19.5% passive member). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B114" authorId="0" shapeId="0">
@@ -3784,10 +3738,10 @@
   <mergeCells count="18">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A16:V16"/>
-    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A137:V137"/>
+    <mergeCell ref="A76:V76"/>
     <mergeCell ref="A90:V90"/>
-    <mergeCell ref="A76:V76"/>
+    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A85:V85"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A80:V80"/>
@@ -3797,7 +3751,7 @@
     <mergeCell ref="A27:V27"/>
     <mergeCell ref="A105:V105"/>
     <mergeCell ref="A69:V69"/>
-    <mergeCell ref="A109:V109"/>
+    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A4:V4"/>
     <mergeCell ref="A24:V24"/>
   </mergeCells>
@@ -3879,7 +3833,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>PMT(Inputs!$B$121/12,Inputs!$B$122,-Inputs!$B$120)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -4463,8 +4417,9 @@
           <t>Beginning balance</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n">
-        <v>0</v>
+      <c r="C18" s="26">
+        <f>0</f>
+        <v/>
       </c>
       <c r="D18" s="24">
         <f>C22</f>
@@ -4894,7 +4849,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>COMBINED DEBT SERVICE &amp; COVERAGE</t>
+          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5030,7 @@
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>TOTAL DEBT SERVICE (P+I, combined)</t>
+          <t>TOTAL DEBT SERVICE (P+I)</t>
         </is>
       </c>
       <c r="C27" s="23">
@@ -5249,86 +5204,86 @@
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>COMBINED DSCR (period)</t>
-        </is>
-      </c>
-      <c r="C29" s="71">
+          <t>DSCR (period)</t>
+        </is>
+      </c>
+      <c r="C29" s="62">
         <f>IF(C27=0,0,C28/C27)</f>
         <v/>
       </c>
-      <c r="D29" s="71">
+      <c r="D29" s="62">
         <f>IF(D27=0,0,D28/D27)</f>
         <v/>
       </c>
-      <c r="E29" s="71">
+      <c r="E29" s="62">
         <f>IF(E27=0,0,E28/E27)</f>
         <v/>
       </c>
-      <c r="F29" s="71">
+      <c r="F29" s="62">
         <f>IF(F27=0,0,F28/F27)</f>
         <v/>
       </c>
-      <c r="G29" s="71">
+      <c r="G29" s="62">
         <f>IF(G27=0,0,G28/G27)</f>
         <v/>
       </c>
-      <c r="H29" s="71">
+      <c r="H29" s="62">
         <f>IF(H27=0,0,H28/H27)</f>
         <v/>
       </c>
-      <c r="I29" s="71">
+      <c r="I29" s="62">
         <f>IF(I27=0,0,I28/I27)</f>
         <v/>
       </c>
-      <c r="J29" s="71">
+      <c r="J29" s="62">
         <f>IF(J27=0,0,J28/J27)</f>
         <v/>
       </c>
-      <c r="K29" s="71">
+      <c r="K29" s="62">
         <f>IF(K27=0,0,K28/K27)</f>
         <v/>
       </c>
-      <c r="L29" s="71">
+      <c r="L29" s="62">
         <f>IF(L27=0,0,L28/L27)</f>
         <v/>
       </c>
-      <c r="M29" s="71">
+      <c r="M29" s="62">
         <f>IF(M27=0,0,M28/M27)</f>
         <v/>
       </c>
-      <c r="N29" s="71">
+      <c r="N29" s="62">
         <f>IF(N27=0,0,N28/N27)</f>
         <v/>
       </c>
-      <c r="O29" s="71">
+      <c r="O29" s="62">
         <f>IF(O27=0,0,O28/O27)</f>
         <v/>
       </c>
-      <c r="P29" s="71">
+      <c r="P29" s="62">
         <f>IF(P27=0,0,P28/P27)</f>
         <v/>
       </c>
-      <c r="Q29" s="71">
+      <c r="Q29" s="62">
         <f>IF(Q27=0,0,Q28/Q27)</f>
         <v/>
       </c>
-      <c r="R29" s="71">
+      <c r="R29" s="62">
         <f>IF(R27=0,0,R28/R27)</f>
         <v/>
       </c>
-      <c r="S29" s="71">
+      <c r="S29" s="62">
         <f>IF(S27=0,0,S28/S27)</f>
         <v/>
       </c>
-      <c r="T29" s="71">
+      <c r="T29" s="62">
         <f>IF(T27=0,0,T28/T27)</f>
         <v/>
       </c>
-      <c r="U29" s="71">
+      <c r="U29" s="62">
         <f>IF(U27=0,0,U28/U27)</f>
         <v/>
       </c>
-      <c r="V29" s="71">
+      <c r="V29" s="62">
         <f>IF(V27=0,0,V28/V27)</f>
         <v/>
       </c>
@@ -7691,8 +7646,9 @@
           <t>Hickory license note balance</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
-        <v>0</v>
+      <c r="B34" s="26">
+        <f>0</f>
+        <v/>
       </c>
       <c r="C34" s="26">
         <f>'Debt Schedule'!C22</f>
@@ -8626,7 +8582,7 @@
           <t>Exit EBITDA multiple</t>
         </is>
       </c>
-      <c r="B5" s="67" t="n">
+      <c r="B5" s="25" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8751,7 +8707,7 @@
           <t>MOIC (gross multiple)</t>
         </is>
       </c>
-      <c r="B16" s="68">
+      <c r="B16" s="31">
         <f>SUM(C12:E12)/$B$6</f>
         <v/>
       </c>
@@ -8857,7 +8813,7 @@
           <t>Exit EBITDA multiple</t>
         </is>
       </c>
-      <c r="B7" s="67" t="n">
+      <c r="B7" s="25" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9215,15 +9171,15 @@
           <t>MOIC (gross multiple)</t>
         </is>
       </c>
-      <c r="B32" s="68">
+      <c r="B32" s="31">
         <f>SUM(C24:G24)/$B$5</f>
         <v/>
       </c>
-      <c r="D32" s="68">
+      <c r="D32" s="31">
         <f>SUM(C25:G25)/$B$5</f>
         <v/>
       </c>
-      <c r="F32" s="68">
+      <c r="F32" s="31">
         <f>SUM(C26:G26)/$B$5</f>
         <v/>
       </c>
@@ -9284,19 +9240,16 @@
           <t>Lowest risk | fixed yield</t>
         </is>
       </c>
-      <c r="C37" s="69" t="n"/>
       <c r="D37" s="37" t="inlineStr">
         <is>
           <t>Medium risk | upside option</t>
         </is>
       </c>
-      <c r="E37" s="69" t="n"/>
       <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Highest risk | highest upside</t>
         </is>
       </c>
-      <c r="G37" s="69" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
@@ -9567,10 +9520,10 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F40:G40"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="F12:G12"/>
@@ -10406,83 +10359,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="50">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="70">
+      <c r="D12" s="50">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="50">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="70">
+      <c r="F12" s="50">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="70">
+      <c r="G12" s="50">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="50">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="70">
+      <c r="I12" s="50">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="70">
+      <c r="J12" s="50">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="70">
+      <c r="K12" s="50">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="70">
+      <c r="L12" s="50">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="70">
+      <c r="M12" s="50">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="70">
+      <c r="N12" s="50">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="70">
+      <c r="O12" s="50">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="70">
+      <c r="P12" s="50">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="70">
+      <c r="Q12" s="50">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="70">
+      <c r="R12" s="50">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="70">
+      <c r="S12" s="50">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="70">
+      <c r="T12" s="50">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="70">
+      <c r="U12" s="50">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="70">
+      <c r="V12" s="50">
         <f>V10*V11</f>
         <v/>
       </c>

--- a/sba_application/09_financial_model/Azalea_Hospice_Investor_Package.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_Investor_Package.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Options" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investor Position" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Economics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
@@ -275,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -374,28 +374,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -413,6 +398,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,6 +444,9 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1356,64 +1347,14 @@
     <author>Azalea Hospice</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0" shapeId="0">
+    <comment ref="B8" authorId="0" shapeId="0">
       <text>
-        <t>Per-investor check size. Tiers $25K / $50K / $100K are common.</t>
+        <t>Bullard's direct, fully funded passive interest. Under 20% - no SBA personal guaranty and no PFS.</t>
       </text>
     </comment>
-    <comment ref="B6" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Years to maturity / exit (model assumes redemption/exit at end).</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>Drives convertible and preferred equity exit value.</t>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
-      <text>
-        <t>Senior subordinated debt: 9-12% typical given subordination to SBA.</t>
-      </text>
-    </comment>
-    <comment ref="D15" authorId="0" shapeId="0">
-      <text>
-        <t>Convertible coupon (lower than straight debt; equity upside compensates).</t>
-      </text>
-    </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
-      <text>
-        <t>Preferred dividend rate, cumulative.</t>
-      </text>
-    </comment>
-    <comment ref="B16" authorId="0" shapeId="0">
-      <text>
-        <t>Years; monthly P+I amortization in this model.</t>
-      </text>
-    </comment>
-    <comment ref="D16" authorId="0" shapeId="0">
-      <text>
-        <t>Years to maturity / conversion trigger.</t>
-      </text>
-    </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
-      <text>
-        <t>Years to redemption / exit.</t>
-      </text>
-    </comment>
-    <comment ref="D18" authorId="0" shapeId="0">
-      <text>
-        <t>Discount applied at conversion vs. exit/round price.</t>
-      </text>
-    </comment>
-    <comment ref="D19" authorId="0" shapeId="0">
-      <text>
-        <t>Implied pre-money cap; conversion uses MIN(cap, exit_val x (1-discount)).</t>
-      </text>
-    </comment>
-    <comment ref="F20" authorId="0" shapeId="0">
-      <text>
-        <t>1 = participating (1x back, then pro-rata). 0 = non-participating (greater of preference or as-converted).</t>
+        <t>Exit enterprise value = multiple x Year-3 EBITDA.</t>
       </text>
     </comment>
   </commentList>
@@ -3838,29 +3779,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O8" s="35" t="inlineStr">
+      <c r="O8" s="43" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S8" s="35" t="inlineStr">
+      <c r="S8" s="43" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr"/>
+      <c r="A9" s="44" t="inlineStr"/>
       <c r="C9" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -5207,83 +5148,83 @@
           <t>DSCR (period)</t>
         </is>
       </c>
-      <c r="C29" s="62">
+      <c r="C29" s="58">
         <f>IF(C27=0,0,C28/C27)</f>
         <v/>
       </c>
-      <c r="D29" s="62">
+      <c r="D29" s="58">
         <f>IF(D27=0,0,D28/D27)</f>
         <v/>
       </c>
-      <c r="E29" s="62">
+      <c r="E29" s="58">
         <f>IF(E27=0,0,E28/E27)</f>
         <v/>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="58">
         <f>IF(F27=0,0,F28/F27)</f>
         <v/>
       </c>
-      <c r="G29" s="62">
+      <c r="G29" s="58">
         <f>IF(G27=0,0,G28/G27)</f>
         <v/>
       </c>
-      <c r="H29" s="62">
+      <c r="H29" s="58">
         <f>IF(H27=0,0,H28/H27)</f>
         <v/>
       </c>
-      <c r="I29" s="62">
+      <c r="I29" s="58">
         <f>IF(I27=0,0,I28/I27)</f>
         <v/>
       </c>
-      <c r="J29" s="62">
+      <c r="J29" s="58">
         <f>IF(J27=0,0,J28/J27)</f>
         <v/>
       </c>
-      <c r="K29" s="62">
+      <c r="K29" s="58">
         <f>IF(K27=0,0,K28/K27)</f>
         <v/>
       </c>
-      <c r="L29" s="62">
+      <c r="L29" s="58">
         <f>IF(L27=0,0,L28/L27)</f>
         <v/>
       </c>
-      <c r="M29" s="62">
+      <c r="M29" s="58">
         <f>IF(M27=0,0,M28/M27)</f>
         <v/>
       </c>
-      <c r="N29" s="62">
+      <c r="N29" s="58">
         <f>IF(N27=0,0,N28/N27)</f>
         <v/>
       </c>
-      <c r="O29" s="62">
+      <c r="O29" s="58">
         <f>IF(O27=0,0,O28/O27)</f>
         <v/>
       </c>
-      <c r="P29" s="62">
+      <c r="P29" s="58">
         <f>IF(P27=0,0,P28/P27)</f>
         <v/>
       </c>
-      <c r="Q29" s="62">
+      <c r="Q29" s="58">
         <f>IF(Q27=0,0,Q28/Q27)</f>
         <v/>
       </c>
-      <c r="R29" s="62">
+      <c r="R29" s="58">
         <f>IF(R27=0,0,R28/R27)</f>
         <v/>
       </c>
-      <c r="S29" s="62">
+      <c r="S29" s="58">
         <f>IF(S27=0,0,S28/S27)</f>
         <v/>
       </c>
-      <c r="T29" s="62">
+      <c r="T29" s="58">
         <f>IF(T27=0,0,T28/T27)</f>
         <v/>
       </c>
-      <c r="U29" s="62">
+      <c r="U29" s="58">
         <f>IF(U27=0,0,U28/U27)</f>
         <v/>
       </c>
-      <c r="V29" s="62">
+      <c r="V29" s="58">
         <f>IF(V27=0,0,V28/V27)</f>
         <v/>
       </c>
@@ -5353,34 +5294,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>Opening</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="35" t="inlineStr">
+      <c r="O4" s="43" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="35" t="inlineStr">
+      <c r="S4" s="43" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr"/>
+      <c r="A5" s="44" t="inlineStr"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -7282,87 +7223,87 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B29" s="63">
+      <c r="B29" s="59">
         <f>B24+B25+B26+B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="63">
+      <c r="C29" s="59">
         <f>C24+C25+C26+C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="63">
+      <c r="D29" s="59">
         <f>D24+D25+D26+D27+D28</f>
         <v/>
       </c>
-      <c r="E29" s="63">
+      <c r="E29" s="59">
         <f>E24+E25+E26+E27+E28</f>
         <v/>
       </c>
-      <c r="F29" s="63">
+      <c r="F29" s="59">
         <f>F24+F25+F26+F27+F28</f>
         <v/>
       </c>
-      <c r="G29" s="63">
+      <c r="G29" s="59">
         <f>G24+G25+G26+G27+G28</f>
         <v/>
       </c>
-      <c r="H29" s="63">
+      <c r="H29" s="59">
         <f>H24+H25+H26+H27+H28</f>
         <v/>
       </c>
-      <c r="I29" s="63">
+      <c r="I29" s="59">
         <f>I24+I25+I26+I27+I28</f>
         <v/>
       </c>
-      <c r="J29" s="63">
+      <c r="J29" s="59">
         <f>J24+J25+J26+J27+J28</f>
         <v/>
       </c>
-      <c r="K29" s="63">
+      <c r="K29" s="59">
         <f>K24+K25+K26+K27+K28</f>
         <v/>
       </c>
-      <c r="L29" s="63">
+      <c r="L29" s="59">
         <f>L24+L25+L26+L27+L28</f>
         <v/>
       </c>
-      <c r="M29" s="63">
+      <c r="M29" s="59">
         <f>M24+M25+M26+M27+M28</f>
         <v/>
       </c>
-      <c r="N29" s="63">
+      <c r="N29" s="59">
         <f>N24+N25+N26+N27+N28</f>
         <v/>
       </c>
-      <c r="O29" s="63">
+      <c r="O29" s="59">
         <f>O24+O25+O26+O27+O28</f>
         <v/>
       </c>
-      <c r="P29" s="63">
+      <c r="P29" s="59">
         <f>P24+P25+P26+P27+P28</f>
         <v/>
       </c>
-      <c r="Q29" s="63">
+      <c r="Q29" s="59">
         <f>Q24+Q25+Q26+Q27+Q28</f>
         <v/>
       </c>
-      <c r="R29" s="63">
+      <c r="R29" s="59">
         <f>R24+R25+R26+R27+R28</f>
         <v/>
       </c>
-      <c r="S29" s="63">
+      <c r="S29" s="59">
         <f>S24+S25+S26+S27+S28</f>
         <v/>
       </c>
-      <c r="T29" s="63">
+      <c r="T29" s="59">
         <f>T24+T25+T26+T27+T28</f>
         <v/>
       </c>
-      <c r="U29" s="63">
+      <c r="U29" s="59">
         <f>U24+U25+U26+U27+U28</f>
         <v/>
       </c>
-      <c r="V29" s="63">
+      <c r="V29" s="59">
         <f>V24+V25+V26+V27+V28</f>
         <v/>
       </c>
@@ -7737,87 +7678,87 @@
           <t>Paid-in equity</t>
         </is>
       </c>
-      <c r="B35" s="64">
+      <c r="B35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="C35" s="64">
+      <c r="C35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="D35" s="64">
+      <c r="D35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="E35" s="64">
+      <c r="E35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="F35" s="64">
+      <c r="F35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="G35" s="64">
+      <c r="G35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="H35" s="64">
+      <c r="H35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="I35" s="64">
+      <c r="I35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="J35" s="64">
+      <c r="J35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="K35" s="64">
+      <c r="K35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="L35" s="64">
+      <c r="L35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="M35" s="64">
+      <c r="M35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="N35" s="64">
+      <c r="N35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="O35" s="64">
+      <c r="O35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="P35" s="64">
+      <c r="P35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="Q35" s="64">
+      <c r="Q35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="R35" s="64">
+      <c r="R35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="S35" s="64">
+      <c r="S35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="T35" s="64">
+      <c r="T35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="U35" s="64">
+      <c r="U35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
-      <c r="V35" s="64">
+      <c r="V35" s="60">
         <f>Inputs!$B$113</f>
         <v/>
       </c>
@@ -7919,87 +7860,87 @@
           <t>TOTAL LIABILITIES &amp; EQUITY</t>
         </is>
       </c>
-      <c r="B37" s="63">
+      <c r="B37" s="59">
         <f>B31+B32+B33+B34+B35+B36</f>
         <v/>
       </c>
-      <c r="C37" s="63">
+      <c r="C37" s="59">
         <f>C31+C32+C33+C34+C35+C36</f>
         <v/>
       </c>
-      <c r="D37" s="63">
+      <c r="D37" s="59">
         <f>D31+D32+D33+D34+D35+D36</f>
         <v/>
       </c>
-      <c r="E37" s="63">
+      <c r="E37" s="59">
         <f>E31+E32+E33+E34+E35+E36</f>
         <v/>
       </c>
-      <c r="F37" s="63">
+      <c r="F37" s="59">
         <f>F31+F32+F33+F34+F35+F36</f>
         <v/>
       </c>
-      <c r="G37" s="63">
+      <c r="G37" s="59">
         <f>G31+G32+G33+G34+G35+G36</f>
         <v/>
       </c>
-      <c r="H37" s="63">
+      <c r="H37" s="59">
         <f>H31+H32+H33+H34+H35+H36</f>
         <v/>
       </c>
-      <c r="I37" s="63">
+      <c r="I37" s="59">
         <f>I31+I32+I33+I34+I35+I36</f>
         <v/>
       </c>
-      <c r="J37" s="63">
+      <c r="J37" s="59">
         <f>J31+J32+J33+J34+J35+J36</f>
         <v/>
       </c>
-      <c r="K37" s="63">
+      <c r="K37" s="59">
         <f>K31+K32+K33+K34+K35+K36</f>
         <v/>
       </c>
-      <c r="L37" s="63">
+      <c r="L37" s="59">
         <f>L31+L32+L33+L34+L35+L36</f>
         <v/>
       </c>
-      <c r="M37" s="63">
+      <c r="M37" s="59">
         <f>M31+M32+M33+M34+M35+M36</f>
         <v/>
       </c>
-      <c r="N37" s="63">
+      <c r="N37" s="59">
         <f>N31+N32+N33+N34+N35+N36</f>
         <v/>
       </c>
-      <c r="O37" s="63">
+      <c r="O37" s="59">
         <f>O31+O32+O33+O34+O35+O36</f>
         <v/>
       </c>
-      <c r="P37" s="63">
+      <c r="P37" s="59">
         <f>P31+P32+P33+P34+P35+P36</f>
         <v/>
       </c>
-      <c r="Q37" s="63">
+      <c r="Q37" s="59">
         <f>Q31+Q32+Q33+Q34+Q35+Q36</f>
         <v/>
       </c>
-      <c r="R37" s="63">
+      <c r="R37" s="59">
         <f>R31+R32+R33+R34+R35+R36</f>
         <v/>
       </c>
-      <c r="S37" s="63">
+      <c r="S37" s="59">
         <f>S31+S32+S33+S34+S35+S36</f>
         <v/>
       </c>
-      <c r="T37" s="63">
+      <c r="T37" s="59">
         <f>T31+T32+T33+T34+T35+T36</f>
         <v/>
       </c>
-      <c r="U37" s="63">
+      <c r="U37" s="59">
         <f>U31+U32+U33+U34+U35+U36</f>
         <v/>
       </c>
-      <c r="V37" s="63">
+      <c r="V37" s="59">
         <f>V31+V32+V33+V34+V35+V36</f>
         <v/>
       </c>
@@ -8010,87 +7951,87 @@
           <t>CHECK: Assets - (L+E) to 0</t>
         </is>
       </c>
-      <c r="B38" s="65">
+      <c r="B38" s="61">
         <f>B29-B37</f>
         <v/>
       </c>
-      <c r="C38" s="65">
+      <c r="C38" s="61">
         <f>C29-C37</f>
         <v/>
       </c>
-      <c r="D38" s="65">
+      <c r="D38" s="61">
         <f>D29-D37</f>
         <v/>
       </c>
-      <c r="E38" s="65">
+      <c r="E38" s="61">
         <f>E29-E37</f>
         <v/>
       </c>
-      <c r="F38" s="65">
+      <c r="F38" s="61">
         <f>F29-F37</f>
         <v/>
       </c>
-      <c r="G38" s="65">
+      <c r="G38" s="61">
         <f>G29-G37</f>
         <v/>
       </c>
-      <c r="H38" s="65">
+      <c r="H38" s="61">
         <f>H29-H37</f>
         <v/>
       </c>
-      <c r="I38" s="65">
+      <c r="I38" s="61">
         <f>I29-I37</f>
         <v/>
       </c>
-      <c r="J38" s="65">
+      <c r="J38" s="61">
         <f>J29-J37</f>
         <v/>
       </c>
-      <c r="K38" s="65">
+      <c r="K38" s="61">
         <f>K29-K37</f>
         <v/>
       </c>
-      <c r="L38" s="65">
+      <c r="L38" s="61">
         <f>L29-L37</f>
         <v/>
       </c>
-      <c r="M38" s="65">
+      <c r="M38" s="61">
         <f>M29-M37</f>
         <v/>
       </c>
-      <c r="N38" s="65">
+      <c r="N38" s="61">
         <f>N29-N37</f>
         <v/>
       </c>
-      <c r="O38" s="65">
+      <c r="O38" s="61">
         <f>O29-O37</f>
         <v/>
       </c>
-      <c r="P38" s="65">
+      <c r="P38" s="61">
         <f>P29-P37</f>
         <v/>
       </c>
-      <c r="Q38" s="65">
+      <c r="Q38" s="61">
         <f>Q29-Q37</f>
         <v/>
       </c>
-      <c r="R38" s="65">
+      <c r="R38" s="61">
         <f>R29-R37</f>
         <v/>
       </c>
-      <c r="S38" s="65">
+      <c r="S38" s="61">
         <f>S29-S37</f>
         <v/>
       </c>
-      <c r="T38" s="65">
+      <c r="T38" s="61">
         <f>T29-T37</f>
         <v/>
       </c>
-      <c r="U38" s="65">
+      <c r="U38" s="61">
         <f>U29-U37</f>
         <v/>
       </c>
-      <c r="V38" s="65">
+      <c r="V38" s="61">
         <f>V29-V37</f>
         <v/>
       </c>
@@ -8144,7 +8085,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
@@ -8211,7 +8152,7 @@
         <f>'Revenue Model'!E14</f>
         <v/>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="36">
         <f>IF(F5=0,0,(G5-F5)/F5)</f>
         <v/>
       </c>
@@ -8288,7 +8229,7 @@
         <f>AVERAGE(C8:E8)</f>
         <v/>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="47">
         <f>'Revenue Model'!E17</f>
         <v/>
       </c>
@@ -8303,31 +8244,31 @@
           <t>Implied ADC (net ÷ $181 ÷ days)</t>
         </is>
       </c>
-      <c r="B9" s="66">
+      <c r="B9" s="63">
         <f>B8/Inputs!$B$12/31</f>
         <v/>
       </c>
-      <c r="C9" s="66">
+      <c r="C9" s="63">
         <f>C8/Inputs!$B$12/30</f>
         <v/>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="63">
         <f>D8/Inputs!$B$12/31</f>
         <v/>
       </c>
-      <c r="E9" s="66">
+      <c r="E9" s="63">
         <f>E8/Inputs!$B$12/30</f>
         <v/>
       </c>
-      <c r="F9" s="66">
+      <c r="F9" s="63">
         <f>AVERAGE(C9:E9)</f>
         <v/>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="45">
         <f>'Revenue Model'!E10</f>
         <v/>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="36">
         <f>IF(F9=0,0,(G9-F9)/F9)</f>
         <v/>
       </c>
@@ -8365,7 +8306,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="36">
         <f>IF(F12=0,0,(G12-F12)/F12)</f>
         <v/>
       </c>
@@ -8396,7 +8337,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="36">
         <f>IF(F13=0,0,(G13-F13)/F13)</f>
         <v/>
       </c>
@@ -8427,7 +8368,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="36">
         <f>IF(F14=0,0,(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -8511,7 +8452,7 @@
         <f>AVERAGE(C19:E19)</f>
         <v/>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="47">
         <f>'Staffing &amp; Payroll'!E53+'Staffing &amp; Payroll'!E54</f>
         <v/>
       </c>
@@ -8753,17 +8694,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8776,790 +8714,244 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Investor Capital - Three Instruments | debt | convertible | preferred equity | choose by yield vs. upside</t>
+          <t>Investor Position - James Bullard | straight common equity (member units)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SHARED INPUTS (edit blue cells)</t>
+          <t>DEAL TERMS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Investment amount ($)</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>50000</v>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>James E. Bullard</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Hold period (years)</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="n">
-        <v>5</v>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Straight common equity (LLC member units)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Exit EBITDA multiple</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>5</v>
+          <t>Capital contribution</t>
+        </is>
+      </c>
+      <c r="B7" s="26">
+        <f>Inputs!$B$113</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Y3 EBITDA (link)</t>
-        </is>
-      </c>
-      <c r="B8" s="26">
-        <f>SUM('Operating Budget'!S24:V24)</f>
-        <v/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Membership interest</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.195</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Equity exit value (Y3 EBITDA x multiple - net debt)</t>
-        </is>
-      </c>
-      <c r="B9" s="26">
-        <f>$B$7*$B$8-'Debt Schedule'!V15-'Cash Flow &amp; BS'!V20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>OPTION A - Promissory Note</t>
-        </is>
-      </c>
-      <c r="D11" s="34" t="inlineStr">
-        <is>
-          <t>OPTION B - Convertible Note</t>
-        </is>
-      </c>
-      <c r="F11" s="34" t="inlineStr">
-        <is>
-          <t>OPTION C - Preferred Equity</t>
+          <t>Guaranty / preference</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>None - passive minority; no debt, no convertible, no liquidation preference</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>RETURN - 3-yr hold, exit at EBITDA multiple</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="35" t="inlineStr">
-        <is>
-          <t>Pure DEBT</t>
-        </is>
-      </c>
-      <c r="D12" s="35" t="inlineStr">
-        <is>
-          <t>HYBRID</t>
-        </is>
-      </c>
-      <c r="F12" s="35" t="inlineStr">
-        <is>
-          <t>EQUITY w/ floor</t>
-        </is>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Exit EBITDA multiple</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Total terminal equity value (all members)</t>
+        </is>
+      </c>
+      <c r="B13" s="26">
+        <f>$B$12*SUM('Operating Budget'!S24:V24)-'Debt Schedule'!V15-'Cash Flow &amp; BS'!V20</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>TERMS (blue = adjust per offer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Interest rate (APR)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0.08</v>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Bullard share of terminal value</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>$B$8*$B$13</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Term / amortization</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>5</v>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>BULLARD EQUITY CASH FLOWS</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Payment style / conversion / preference</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>Monthly P+I</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>Discount + valuation cap</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>1x liq preference, then participate</t>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>Year 3</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>(Convertible) Discount on equity round</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>0.2</v>
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Total free cash flow to equity (all members)</t>
+        </is>
+      </c>
+      <c r="C18" s="26">
+        <f>SUM('Cash Flow &amp; BS'!C13:N13)+SUM('Cash Flow &amp; BS'!C14:N14)</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>SUM('Cash Flow &amp; BS'!O13:R13)+SUM('Cash Flow &amp; BS'!O14:R14)</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>SUM('Cash Flow &amp; BS'!S13:V13)+SUM('Cash Flow &amp; BS'!S14:V14)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>(Convertible) Valuation cap ($)</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>(Preferred) Participate after preference</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>1</v>
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Bullard net cash flow (19.5% pro-rata)</t>
+        </is>
+      </c>
+      <c r="B19" s="23">
+        <f>-$B$7</f>
+        <v/>
+      </c>
+      <c r="C19" s="29">
+        <f>$B$8*C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>$B$8*D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>$B$8*E18+$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>BULLARD RETURNS</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>INVESTOR CASH FLOW SCHEDULE (annual, Year 0 = close)</t>
-        </is>
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Equity IRR (3-yr)</t>
+        </is>
+      </c>
+      <c r="B22" s="30">
+        <f>IRR(B19:E19)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>Y0</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="D23" s="27" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="G23" s="27" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>MOIC (gross multiple)</t>
+        </is>
+      </c>
+      <c r="B23" s="31">
+        <f>SUM(C19:E19)/$B$7</f>
+        <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>OPTION A - Promissory Note</t>
-        </is>
-      </c>
-      <c r="B24" s="23">
-        <f>-$B$5</f>
-        <v/>
-      </c>
-      <c r="C24" s="24">
-        <f>IF(1&lt;=$B$16,PMT($B$15/12,$B$16*12,-$B$5)*12,0)</f>
-        <v/>
-      </c>
-      <c r="D24" s="24">
-        <f>IF(2&lt;=$B$16,PMT($B$15/12,$B$16*12,-$B$5)*12,0)</f>
-        <v/>
-      </c>
-      <c r="E24" s="24">
-        <f>IF(3&lt;=$B$16,PMT($B$15/12,$B$16*12,-$B$5)*12,0)</f>
-        <v/>
-      </c>
-      <c r="F24" s="24">
-        <f>IF(4&lt;=$B$16,PMT($B$15/12,$B$16*12,-$B$5)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="24">
-        <f>IF(5&lt;=$B$16,PMT($B$15/12,$B$16*12,-$B$5)*12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>OPTION B - Convertible Note</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>-$B$5</f>
-        <v/>
-      </c>
-      <c r="C25" s="24">
-        <f>IF(1&lt;$D$16,$B$5*$D$15,IF(1=$D$16,MAX($B$5+$B$5*$D$15,(($B$5/MIN($D$19,$B$9*(1-$D$18)))*$B$9)),0))</f>
-        <v/>
-      </c>
-      <c r="D25" s="24">
-        <f>IF(2&lt;$D$16,$B$5*$D$15,IF(2=$D$16,MAX($B$5+$B$5*$D$15,(($B$5/MIN($D$19,$B$9*(1-$D$18)))*$B$9)),0))</f>
-        <v/>
-      </c>
-      <c r="E25" s="24">
-        <f>IF(3&lt;$D$16,$B$5*$D$15,IF(3=$D$16,MAX($B$5+$B$5*$D$15,(($B$5/MIN($D$19,$B$9*(1-$D$18)))*$B$9)),0))</f>
-        <v/>
-      </c>
-      <c r="F25" s="24">
-        <f>IF(4&lt;$D$16,$B$5*$D$15,IF(4=$D$16,MAX($B$5+$B$5*$D$15,(($B$5/MIN($D$19,$B$9*(1-$D$18)))*$B$9)),0))</f>
-        <v/>
-      </c>
-      <c r="G25" s="24">
-        <f>IF(5&lt;$D$16,$B$5*$D$15,IF(5=$D$16,MAX($B$5+$B$5*$D$15,(($B$5/MIN($D$19,$B$9*(1-$D$18)))*$B$9)),0))</f>
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Avg cash-on-cash (Y1-Y3, distributions only)</t>
+        </is>
+      </c>
+      <c r="B24" s="32">
+        <f>$B$8*AVERAGE(C18:E18)/$B$7</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>OPTION C - Preferred Equity</t>
-        </is>
-      </c>
-      <c r="B26" s="23">
-        <f>-$B$5</f>
-        <v/>
-      </c>
-      <c r="C26" s="24">
-        <f>IF(1&lt;$F$16,$B$5*$F$15,IF(1=$F$16,$B$5*$F$15+$B$5+IF($F$20=1,($B$5/$B$9)*MAX(0,$B$9-$B$5),MAX($B$5,($B$5/$B$9)*$B$9)-$B$5),0))</f>
-        <v/>
-      </c>
-      <c r="D26" s="24">
-        <f>IF(2&lt;$F$16,$B$5*$F$15,IF(2=$F$16,$B$5*$F$15+$B$5+IF($F$20=1,($B$5/$B$9)*MAX(0,$B$9-$B$5),MAX($B$5,($B$5/$B$9)*$B$9)-$B$5),0))</f>
-        <v/>
-      </c>
-      <c r="E26" s="24">
-        <f>IF(3&lt;$F$16,$B$5*$F$15,IF(3=$F$16,$B$5*$F$15+$B$5+IF($F$20=1,($B$5/$B$9)*MAX(0,$B$9-$B$5),MAX($B$5,($B$5/$B$9)*$B$9)-$B$5),0))</f>
-        <v/>
-      </c>
-      <c r="F26" s="24">
-        <f>IF(4&lt;$F$16,$B$5*$F$15,IF(4=$F$16,$B$5*$F$15+$B$5+IF($F$20=1,($B$5/$B$9)*MAX(0,$B$9-$B$5),MAX($B$5,($B$5/$B$9)*$B$9)-$B$5),0))</f>
-        <v/>
-      </c>
-      <c r="G26" s="24">
-        <f>IF(5&lt;$F$16,$B$5*$F$15,IF(5=$F$16,$B$5*$F$15+$B$5+IF($F$20=1,($B$5/$B$9)*MAX(0,$B$9-$B$5),MAX($B$5,($B$5/$B$9)*$B$9)-$B$5),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>RETURNS COMPARISON (Y0 = -investment; subsequent years per schedule above)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Headline rate (APR / coupon / pref div)</t>
-        </is>
-      </c>
-      <c r="B29" s="32">
-        <f>$B$15</f>
-        <v/>
-      </c>
-      <c r="D29" s="32">
-        <f>$D$15</f>
-        <v/>
-      </c>
-      <c r="F29" s="32">
-        <f>$F$15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Total cash to investor (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B30" s="23">
-        <f>SUM(C24:G24)</f>
-        <v/>
-      </c>
-      <c r="D30" s="23">
-        <f>SUM(C25:G25)</f>
-        <v/>
-      </c>
-      <c r="F30" s="23">
-        <f>SUM(C26:G26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Total profit (cash - investment)</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>SUM(C24:G24)-$B$5</f>
-        <v/>
-      </c>
-      <c r="D31" s="23">
-        <f>SUM(C25:G25)-$B$5</f>
-        <v/>
-      </c>
-      <c r="F31" s="23">
-        <f>SUM(C26:G26)-$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>MOIC (gross multiple)</t>
-        </is>
-      </c>
-      <c r="B32" s="31">
-        <f>SUM(C24:G24)/$B$5</f>
-        <v/>
-      </c>
-      <c r="D32" s="31">
-        <f>SUM(C25:G25)/$B$5</f>
-        <v/>
-      </c>
-      <c r="F32" s="31">
-        <f>SUM(C26:G26)/$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>IRR / effective annual yield</t>
-        </is>
-      </c>
-      <c r="B33" s="30">
-        <f>(1+$B$15/12)^12-1</f>
-        <v/>
-      </c>
-      <c r="D33" s="30">
-        <f>IRR(B25:G25)</f>
-        <v/>
-      </c>
-      <c r="F33" s="30">
-        <f>IRR(B26:G26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Average annual cash yield (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B34" s="32">
-        <f>AVERAGE(C24:G24)/$B$5</f>
-        <v/>
-      </c>
-      <c r="D34" s="32">
-        <f>AVERAGE(C25:G25)/$B$5</f>
-        <v/>
-      </c>
-      <c r="F34" s="32">
-        <f>AVERAGE(C26:G26)/$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>RISK &amp; FIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="36" t="inlineStr">
-        <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="B37" s="37" t="inlineStr">
-        <is>
-          <t>Lowest risk | fixed yield</t>
-        </is>
-      </c>
-      <c r="D37" s="37" t="inlineStr">
-        <is>
-          <t>Medium risk | upside option</t>
-        </is>
-      </c>
-      <c r="F37" s="37" t="inlineStr">
-        <is>
-          <t>Highest risk | highest upside</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Security / position</t>
-        </is>
-      </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>Senior subordinated debt; subordinate to SBA</t>
-        </is>
-      </c>
-      <c r="D38" s="33" t="inlineStr">
-        <is>
-          <t>Debt at maturity OR equity at exit (greater)</t>
-        </is>
-      </c>
-      <c r="F38" s="33" t="inlineStr">
-        <is>
-          <t>Equity; subordinate to all debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>Cash flow to investor</t>
-        </is>
-      </c>
-      <c r="B39" s="33" t="inlineStr">
-        <is>
-          <t>Monthly P+I, predictable</t>
-        </is>
-      </c>
-      <c r="D39" s="33" t="inlineStr">
-        <is>
-          <t>Annual coupon, lump at exit</t>
-        </is>
-      </c>
-      <c r="F39" s="33" t="inlineStr">
-        <is>
-          <t>Annual dividend, lump at exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>Tax treatment</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>Interest = ordinary income</t>
-        </is>
-      </c>
-      <c r="D40" s="33" t="inlineStr">
-        <is>
-          <t>Interest = ordinary; conversion = capital gain</t>
-        </is>
-      </c>
-      <c r="F40" s="33" t="inlineStr">
-        <is>
-          <t>Dividends + capital gain on exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Best for</t>
-        </is>
-      </c>
-      <c r="B41" s="33" t="inlineStr">
-        <is>
-          <t>Yield-focused, risk-averse passive lenders</t>
-        </is>
-      </c>
-      <c r="D41" s="33" t="inlineStr">
-        <is>
-          <t>Investors who want yield AND a shot at equity upside</t>
-        </is>
-      </c>
-      <c r="F41" s="33" t="inlineStr">
-        <is>
-          <t>Believers in the upside who can take equity risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>ILLUSTRATIVE TIERS (recompute by changing 'Investment amount' above)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="27" t="inlineStr">
-        <is>
-          <t>Check size</t>
-        </is>
-      </c>
-      <c r="B44" s="27" t="inlineStr">
-        <is>
-          <t>Option A: 5-yr IRR</t>
-        </is>
-      </c>
-      <c r="C44" s="27" t="inlineStr">
-        <is>
-          <t>Option A: total cash</t>
-        </is>
-      </c>
-      <c r="D44" s="27" t="inlineStr">
-        <is>
-          <t>Option B: IRR @5x exit</t>
-        </is>
-      </c>
-      <c r="E44" s="27" t="inlineStr">
-        <is>
-          <t>Option B: total cash</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="inlineStr">
-        <is>
-          <t>Option C: IRR @5x exit</t>
-        </is>
-      </c>
-      <c r="G44" s="27" t="inlineStr">
-        <is>
-          <t>Option C: total cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="38" t="n">
-        <v>25000</v>
-      </c>
-      <c r="B45" s="39">
-        <f>(1+$B$15/12)^12-1</f>
-        <v/>
-      </c>
-      <c r="C45" s="24">
-        <f>PMT($B$15/12,$B$16*12,-A45)*12*$B$16</f>
-        <v/>
-      </c>
-      <c r="D45" s="39">
-        <f>$D$33</f>
-        <v/>
-      </c>
-      <c r="E45" s="24">
-        <f>A45/$B$5*$D$30</f>
-        <v/>
-      </c>
-      <c r="F45" s="39">
-        <f>$F$33</f>
-        <v/>
-      </c>
-      <c r="G45" s="24">
-        <f>A45/$B$5*$F$30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="38" t="n">
-        <v>50000</v>
-      </c>
-      <c r="B46" s="39">
-        <f>(1+$B$15/12)^12-1</f>
-        <v/>
-      </c>
-      <c r="C46" s="24">
-        <f>PMT($B$15/12,$B$16*12,-A46)*12*$B$16</f>
-        <v/>
-      </c>
-      <c r="D46" s="39">
-        <f>$D$33</f>
-        <v/>
-      </c>
-      <c r="E46" s="24">
-        <f>A46/$B$5*$D$30</f>
-        <v/>
-      </c>
-      <c r="F46" s="39">
-        <f>$F$33</f>
-        <v/>
-      </c>
-      <c r="G46" s="24">
-        <f>A46/$B$5*$F$30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="38" t="n">
-        <v>100000</v>
-      </c>
-      <c r="B47" s="39">
-        <f>(1+$B$15/12)^12-1</f>
-        <v/>
-      </c>
-      <c r="C47" s="24">
-        <f>PMT($B$15/12,$B$16*12,-A47)*12*$B$16</f>
-        <v/>
-      </c>
-      <c r="D47" s="39">
-        <f>$D$33</f>
-        <v/>
-      </c>
-      <c r="E47" s="24">
-        <f>A47/$B$5*$D$30</f>
-        <v/>
-      </c>
-      <c r="F47" s="39">
-        <f>$F$33</f>
-        <v/>
-      </c>
-      <c r="G47" s="24">
-        <f>A47/$B$5*$F$30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="38" t="n">
-        <v>250000</v>
-      </c>
-      <c r="B48" s="39">
-        <f>(1+$B$15/12)^12-1</f>
-        <v/>
-      </c>
-      <c r="C48" s="24">
-        <f>PMT($B$15/12,$B$16*12,-A48)*12*$B$16</f>
-        <v/>
-      </c>
-      <c r="D48" s="39">
-        <f>$D$33</f>
-        <v/>
-      </c>
-      <c r="E48" s="24">
-        <f>A48/$B$5*$D$30</f>
-        <v/>
-      </c>
-      <c r="F48" s="39">
-        <f>$F$33</f>
-        <v/>
-      </c>
-      <c r="G48" s="24">
-        <f>A48/$B$5*$F$30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="33" t="inlineStr">
-        <is>
-          <t>Conventions: Year-0 cash flow is the investor's check (negative). Subsequent years are cash received. Option A IRR ≈ rate (slight compounding bump from monthly payments). Options B and C IRR/cash scale linearly with check size when terms and exit value are fixed - use the tier menu to size offers, then change 'Investment amount' to see the live cash-flow schedule update. Conversion math: Option B holder receives MAX(principal + final coupon, equity-as-converted) at year = term, where conversion ownership = investment ÷ MIN(cap, exit x (1 - discount)).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>James Bullard's subscription closed as straight common equity: a $195,000 cash capital contribution for a 19.5% non-controlling member interest (no debt, no convertible note, no liquidation preference). Because the interest is below 20% and passive, no SBA personal guaranty or PFS is required. Return is his 19.5% pro-rata share of free cash flow to equity (distributed annually) plus 19.5% of terminal equity value, which exits at the EBITDA multiple net of remaining debt. He funds the entire cash injection but holds a minority stake, so his multiple is below the blended all-equity figure on the Returns tab. Editable cells (blue): exit multiple and membership %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="A50:H54"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B41:C41"/>
+  <mergeCells count="7">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A26:E30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -9600,7 +8992,7 @@
           <t>Net revenue per patient-day</t>
         </is>
       </c>
-      <c r="B4" s="40">
+      <c r="B4" s="34">
         <f>Inputs!$B$21</f>
         <v/>
       </c>
@@ -9611,7 +9003,7 @@
           <t>Medical supplies / PD</t>
         </is>
       </c>
-      <c r="B5" s="40">
+      <c r="B5" s="34">
         <f>-Inputs!$B$86</f>
         <v/>
       </c>
@@ -9622,7 +9014,7 @@
           <t>DME / PD</t>
         </is>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="34">
         <f>-Inputs!$B$87</f>
         <v/>
       </c>
@@ -9633,7 +9025,7 @@
           <t>Pharmacy / PD</t>
         </is>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="34">
         <f>-Inputs!$B$88</f>
         <v/>
       </c>
@@ -9644,7 +9036,7 @@
           <t>PRN / per-visit labor / PD</t>
         </is>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="34">
         <f>-(Inputs!$C$63*Inputs!$D$63+Inputs!$C$64*Inputs!$D$64+Inputs!$C$65*Inputs!$D$65+Inputs!$C$66*Inputs!$D$66+Inputs!$C$67*Inputs!$D$67)/Inputs!$B$25</f>
         <v/>
       </c>
@@ -9655,7 +9047,7 @@
           <t>QR payment fee / PD</t>
         </is>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="34">
         <f>-Inputs!$B$20*Inputs!$B$107</f>
         <v/>
       </c>
@@ -9666,7 +9058,7 @@
           <t>CONTRIBUTION MARGIN / PD</t>
         </is>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="35">
         <f>B4-SUM(B5:B9)</f>
         <v/>
       </c>
@@ -9677,7 +9069,7 @@
           <t>Contribution margin %</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="36">
         <f>B10/B4</f>
         <v/>
       </c>
@@ -9688,7 +9080,7 @@
           <t>Daily fixed-cost burden (annual fixed ÷ 365)</t>
         </is>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="34">
         <f>((Inputs!$C$37+Inputs!$C$38+Inputs!$C$39+Inputs!$C$40+Inputs!$C$41+Inputs!$C$42+Inputs!$C$43+Inputs!$C$44+Inputs!$C$45+Inputs!$C$46+Inputs!$C$47+Inputs!$C$48+Inputs!$C$49+Inputs!$C$50+Inputs!$C$51+Inputs!$C$52+Inputs!$C$53+Inputs!$C$54+Inputs!$C$55+Inputs!$C$56+Inputs!$C$57+Inputs!$C$58+Inputs!$C$59)*(1+Inputs!$B$77)+Inputs!$B$78*22*12+Inputs!$B$81*12+SUM(Inputs!$B$91:$B$103)*12)/(Inputs!$B$25*12)</f>
         <v/>
       </c>
@@ -9699,7 +9091,7 @@
           <t>Break-even ADC (fixed ÷ contribution/PD)</t>
         </is>
       </c>
-      <c r="B14" s="42">
+      <c r="B14" s="37">
         <f>B13/B10</f>
         <v/>
       </c>
@@ -9756,7 +9148,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>EBITDA ($/yr)</t>
         </is>
@@ -9768,24 +9160,24 @@
           <t>ADC (rows) / net rate (cols)</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="39" t="n">
         <v>170</v>
       </c>
-      <c r="C5" s="44" t="n">
+      <c r="C5" s="39" t="n">
         <v>176</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="39" t="n">
         <v>181</v>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="39" t="n">
         <v>186</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="39" t="n">
         <v>192</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="n">
+      <c r="A6" s="40" t="n">
         <v>16</v>
       </c>
       <c r="B6" s="24">
@@ -9810,7 +9202,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="n">
+      <c r="A7" s="40" t="n">
         <v>18</v>
       </c>
       <c r="B7" s="24">
@@ -9835,7 +9227,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="n">
+      <c r="A8" s="40" t="n">
         <v>20</v>
       </c>
       <c r="B8" s="24">
@@ -9860,7 +9252,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="n">
+      <c r="A9" s="40" t="n">
         <v>22</v>
       </c>
       <c r="B9" s="24">
@@ -9885,7 +9277,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="n">
+      <c r="A10" s="40" t="n">
         <v>26</v>
       </c>
       <c r="B10" s="24">
@@ -9910,7 +9302,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="n">
+      <c r="A11" s="40" t="n">
         <v>30</v>
       </c>
       <c r="B11" s="24">
@@ -9935,7 +9327,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="n">
+      <c r="A12" s="40" t="n">
         <v>35</v>
       </c>
       <c r="B12" s="24">
@@ -10038,7 +9430,7 @@
           <t>Blended GROSS rate ($/PD)</t>
         </is>
       </c>
-      <c r="B5" s="46">
+      <c r="B5" s="41">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
@@ -10049,35 +9441,35 @@
           <t>Blended NET rate ($/PD)</t>
         </is>
       </c>
-      <c r="B6" s="46">
+      <c r="B6" s="41">
         <f>Inputs!$B$21</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O8" s="35" t="inlineStr">
+      <c r="O8" s="43" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S8" s="35" t="inlineStr">
+      <c r="S8" s="43" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr"/>
+      <c r="A9" s="44" t="inlineStr"/>
       <c r="C9" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -10185,83 +9577,83 @@
           <t>Average daily census (ADC)</t>
         </is>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="45">
         <f>Inputs!C$33</f>
         <v/>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="45">
         <f>Inputs!D$33</f>
         <v/>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="45">
         <f>Inputs!E$33</f>
         <v/>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="45">
         <f>Inputs!F$33</f>
         <v/>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="45">
         <f>Inputs!G$33</f>
         <v/>
       </c>
-      <c r="H10" s="49">
+      <c r="H10" s="45">
         <f>Inputs!H$33</f>
         <v/>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="45">
         <f>Inputs!I$33</f>
         <v/>
       </c>
-      <c r="J10" s="49">
+      <c r="J10" s="45">
         <f>Inputs!J$33</f>
         <v/>
       </c>
-      <c r="K10" s="49">
+      <c r="K10" s="45">
         <f>Inputs!K$33</f>
         <v/>
       </c>
-      <c r="L10" s="49">
+      <c r="L10" s="45">
         <f>Inputs!L$33</f>
         <v/>
       </c>
-      <c r="M10" s="49">
+      <c r="M10" s="45">
         <f>Inputs!M$33</f>
         <v/>
       </c>
-      <c r="N10" s="49">
+      <c r="N10" s="45">
         <f>Inputs!N$33</f>
         <v/>
       </c>
-      <c r="O10" s="49">
+      <c r="O10" s="45">
         <f>Inputs!O$33</f>
         <v/>
       </c>
-      <c r="P10" s="49">
+      <c r="P10" s="45">
         <f>Inputs!P$33</f>
         <v/>
       </c>
-      <c r="Q10" s="49">
+      <c r="Q10" s="45">
         <f>Inputs!Q$33</f>
         <v/>
       </c>
-      <c r="R10" s="49">
+      <c r="R10" s="45">
         <f>Inputs!R$33</f>
         <v/>
       </c>
-      <c r="S10" s="49">
+      <c r="S10" s="45">
         <f>Inputs!S$33</f>
         <v/>
       </c>
-      <c r="T10" s="49">
+      <c r="T10" s="45">
         <f>Inputs!T$33</f>
         <v/>
       </c>
-      <c r="U10" s="49">
+      <c r="U10" s="45">
         <f>Inputs!U$33</f>
         <v/>
       </c>
-      <c r="V10" s="49">
+      <c r="V10" s="45">
         <f>Inputs!V$33</f>
         <v/>
       </c>
@@ -10272,83 +9664,83 @@
           <t>Days in period</t>
         </is>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="F11" s="49">
+      <c r="F11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="H11" s="49">
+      <c r="H11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="J11" s="49">
+      <c r="J11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="K11" s="49">
+      <c r="K11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="M11" s="49">
+      <c r="M11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="N11" s="49">
+      <c r="N11" s="45">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="O11" s="49">
+      <c r="O11" s="45">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="P11" s="49">
+      <c r="P11" s="45">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="Q11" s="49">
+      <c r="Q11" s="45">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="R11" s="49">
+      <c r="R11" s="45">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="S11" s="49">
+      <c r="S11" s="45">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="T11" s="49">
+      <c r="T11" s="45">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="U11" s="49">
+      <c r="U11" s="45">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="V11" s="49">
+      <c r="V11" s="45">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
@@ -10359,83 +9751,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="46">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="46">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="46">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="46">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="46">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="46">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="46">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="50">
+      <c r="J12" s="46">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="50">
+      <c r="K12" s="46">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="50">
+      <c r="L12" s="46">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="50">
+      <c r="M12" s="46">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="50">
+      <c r="N12" s="46">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="50">
+      <c r="O12" s="46">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="50">
+      <c r="P12" s="46">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="50">
+      <c r="Q12" s="46">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="50">
+      <c r="R12" s="46">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="50">
+      <c r="S12" s="46">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="50">
+      <c r="T12" s="46">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="50">
+      <c r="U12" s="46">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="50">
+      <c r="V12" s="46">
         <f>V10*V11</f>
         <v/>
       </c>
@@ -11024,29 +10416,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="35" t="inlineStr">
+      <c r="O4" s="43" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="35" t="inlineStr">
+      <c r="S4" s="43" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr"/>
+      <c r="A5" s="44" t="inlineStr"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -11154,83 +10546,83 @@
           <t>ADC (driver)</t>
         </is>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="45">
         <f>'Revenue Model'!C10</f>
         <v/>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="45">
         <f>'Revenue Model'!D10</f>
         <v/>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="45">
         <f>'Revenue Model'!E10</f>
         <v/>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="45">
         <f>'Revenue Model'!F10</f>
         <v/>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="45">
         <f>'Revenue Model'!G10</f>
         <v/>
       </c>
-      <c r="H6" s="49">
+      <c r="H6" s="45">
         <f>'Revenue Model'!H10</f>
         <v/>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="45">
         <f>'Revenue Model'!I10</f>
         <v/>
       </c>
-      <c r="J6" s="49">
+      <c r="J6" s="45">
         <f>'Revenue Model'!J10</f>
         <v/>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="45">
         <f>'Revenue Model'!K10</f>
         <v/>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="45">
         <f>'Revenue Model'!L10</f>
         <v/>
       </c>
-      <c r="M6" s="49">
+      <c r="M6" s="45">
         <f>'Revenue Model'!M10</f>
         <v/>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="45">
         <f>'Revenue Model'!N10</f>
         <v/>
       </c>
-      <c r="O6" s="49">
+      <c r="O6" s="45">
         <f>'Revenue Model'!O10</f>
         <v/>
       </c>
-      <c r="P6" s="49">
+      <c r="P6" s="45">
         <f>'Revenue Model'!P10</f>
         <v/>
       </c>
-      <c r="Q6" s="49">
+      <c r="Q6" s="45">
         <f>'Revenue Model'!Q10</f>
         <v/>
       </c>
-      <c r="R6" s="49">
+      <c r="R6" s="45">
         <f>'Revenue Model'!R10</f>
         <v/>
       </c>
-      <c r="S6" s="49">
+      <c r="S6" s="45">
         <f>'Revenue Model'!S10</f>
         <v/>
       </c>
-      <c r="T6" s="49">
+      <c r="T6" s="45">
         <f>'Revenue Model'!T10</f>
         <v/>
       </c>
-      <c r="U6" s="49">
+      <c r="U6" s="45">
         <f>'Revenue Model'!U10</f>
         <v/>
       </c>
-      <c r="V6" s="49">
+      <c r="V6" s="45">
         <f>'Revenue Model'!V10</f>
         <v/>
       </c>
@@ -14808,29 +14200,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="35" t="inlineStr">
+      <c r="O4" s="43" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="35" t="inlineStr">
+      <c r="S4" s="43" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr"/>
+      <c r="A5" s="44" t="inlineStr"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -14938,83 +14330,83 @@
           <t>NET REVENUE</t>
         </is>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="47">
         <f>'Revenue Model'!C17</f>
         <v/>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="47">
         <f>'Revenue Model'!D17</f>
         <v/>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="47">
         <f>'Revenue Model'!E17</f>
         <v/>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="47">
         <f>'Revenue Model'!F17</f>
         <v/>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="47">
         <f>'Revenue Model'!G17</f>
         <v/>
       </c>
-      <c r="H6" s="51">
+      <c r="H6" s="47">
         <f>'Revenue Model'!H17</f>
         <v/>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="47">
         <f>'Revenue Model'!I17</f>
         <v/>
       </c>
-      <c r="J6" s="51">
+      <c r="J6" s="47">
         <f>'Revenue Model'!J17</f>
         <v/>
       </c>
-      <c r="K6" s="51">
+      <c r="K6" s="47">
         <f>'Revenue Model'!K17</f>
         <v/>
       </c>
-      <c r="L6" s="51">
+      <c r="L6" s="47">
         <f>'Revenue Model'!L17</f>
         <v/>
       </c>
-      <c r="M6" s="51">
+      <c r="M6" s="47">
         <f>'Revenue Model'!M17</f>
         <v/>
       </c>
-      <c r="N6" s="51">
+      <c r="N6" s="47">
         <f>'Revenue Model'!N17</f>
         <v/>
       </c>
-      <c r="O6" s="51">
+      <c r="O6" s="47">
         <f>'Revenue Model'!O17</f>
         <v/>
       </c>
-      <c r="P6" s="51">
+      <c r="P6" s="47">
         <f>'Revenue Model'!P17</f>
         <v/>
       </c>
-      <c r="Q6" s="51">
+      <c r="Q6" s="47">
         <f>'Revenue Model'!Q17</f>
         <v/>
       </c>
-      <c r="R6" s="51">
+      <c r="R6" s="47">
         <f>'Revenue Model'!R17</f>
         <v/>
       </c>
-      <c r="S6" s="51">
+      <c r="S6" s="47">
         <f>'Revenue Model'!S17</f>
         <v/>
       </c>
-      <c r="T6" s="51">
+      <c r="T6" s="47">
         <f>'Revenue Model'!T17</f>
         <v/>
       </c>
-      <c r="U6" s="51">
+      <c r="U6" s="47">
         <f>'Revenue Model'!U17</f>
         <v/>
       </c>
-      <c r="V6" s="51">
+      <c r="V6" s="47">
         <f>'Revenue Model'!V17</f>
         <v/>
       </c>
@@ -15641,83 +15033,83 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="36">
         <f>IF(C6=0,0,C15/C6)</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="36">
         <f>IF(D6=0,0,D15/D6)</f>
         <v/>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="36">
         <f>IF(E6=0,0,E15/E6)</f>
         <v/>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="36">
         <f>IF(F6=0,0,F15/F6)</f>
         <v/>
       </c>
-      <c r="G16" s="39">
+      <c r="G16" s="36">
         <f>IF(G6=0,0,G15/G6)</f>
         <v/>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="36">
         <f>IF(H6=0,0,H15/H6)</f>
         <v/>
       </c>
-      <c r="I16" s="39">
+      <c r="I16" s="36">
         <f>IF(I6=0,0,I15/I6)</f>
         <v/>
       </c>
-      <c r="J16" s="39">
+      <c r="J16" s="36">
         <f>IF(J6=0,0,J15/J6)</f>
         <v/>
       </c>
-      <c r="K16" s="39">
+      <c r="K16" s="36">
         <f>IF(K6=0,0,K15/K6)</f>
         <v/>
       </c>
-      <c r="L16" s="39">
+      <c r="L16" s="36">
         <f>IF(L6=0,0,L15/L6)</f>
         <v/>
       </c>
-      <c r="M16" s="39">
+      <c r="M16" s="36">
         <f>IF(M6=0,0,M15/M6)</f>
         <v/>
       </c>
-      <c r="N16" s="39">
+      <c r="N16" s="36">
         <f>IF(N6=0,0,N15/N6)</f>
         <v/>
       </c>
-      <c r="O16" s="39">
+      <c r="O16" s="36">
         <f>IF(O6=0,0,O15/O6)</f>
         <v/>
       </c>
-      <c r="P16" s="39">
+      <c r="P16" s="36">
         <f>IF(P6=0,0,P15/P6)</f>
         <v/>
       </c>
-      <c r="Q16" s="39">
+      <c r="Q16" s="36">
         <f>IF(Q6=0,0,Q15/Q6)</f>
         <v/>
       </c>
-      <c r="R16" s="39">
+      <c r="R16" s="36">
         <f>IF(R6=0,0,R15/R6)</f>
         <v/>
       </c>
-      <c r="S16" s="39">
+      <c r="S16" s="36">
         <f>IF(S6=0,0,S15/S6)</f>
         <v/>
       </c>
-      <c r="T16" s="39">
+      <c r="T16" s="36">
         <f>IF(T6=0,0,T15/T6)</f>
         <v/>
       </c>
-      <c r="U16" s="39">
+      <c r="U16" s="36">
         <f>IF(U6=0,0,U15/U6)</f>
         <v/>
       </c>
-      <c r="V16" s="39">
+      <c r="V16" s="36">
         <f>IF(V6=0,0,V15/V6)</f>
         <v/>
       </c>
@@ -16170,83 +15562,83 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C24" s="52">
+      <c r="C24" s="48">
         <f>C15-C23</f>
         <v/>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="48">
         <f>D15-D23</f>
         <v/>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="48">
         <f>E15-E23</f>
         <v/>
       </c>
-      <c r="F24" s="52">
+      <c r="F24" s="48">
         <f>F15-F23</f>
         <v/>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="48">
         <f>G15-G23</f>
         <v/>
       </c>
-      <c r="H24" s="52">
+      <c r="H24" s="48">
         <f>H15-H23</f>
         <v/>
       </c>
-      <c r="I24" s="52">
+      <c r="I24" s="48">
         <f>I15-I23</f>
         <v/>
       </c>
-      <c r="J24" s="52">
+      <c r="J24" s="48">
         <f>J15-J23</f>
         <v/>
       </c>
-      <c r="K24" s="52">
+      <c r="K24" s="48">
         <f>K15-K23</f>
         <v/>
       </c>
-      <c r="L24" s="52">
+      <c r="L24" s="48">
         <f>L15-L23</f>
         <v/>
       </c>
-      <c r="M24" s="52">
+      <c r="M24" s="48">
         <f>M15-M23</f>
         <v/>
       </c>
-      <c r="N24" s="52">
+      <c r="N24" s="48">
         <f>N15-N23</f>
         <v/>
       </c>
-      <c r="O24" s="52">
+      <c r="O24" s="48">
         <f>O15-O23</f>
         <v/>
       </c>
-      <c r="P24" s="52">
+      <c r="P24" s="48">
         <f>P15-P23</f>
         <v/>
       </c>
-      <c r="Q24" s="52">
+      <c r="Q24" s="48">
         <f>Q15-Q23</f>
         <v/>
       </c>
-      <c r="R24" s="52">
+      <c r="R24" s="48">
         <f>R15-R23</f>
         <v/>
       </c>
-      <c r="S24" s="52">
+      <c r="S24" s="48">
         <f>S15-S23</f>
         <v/>
       </c>
-      <c r="T24" s="52">
+      <c r="T24" s="48">
         <f>T15-T23</f>
         <v/>
       </c>
-      <c r="U24" s="52">
+      <c r="U24" s="48">
         <f>U15-U23</f>
         <v/>
       </c>
-      <c r="V24" s="52">
+      <c r="V24" s="48">
         <f>V15-V23</f>
         <v/>
       </c>
@@ -16257,83 +15649,83 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="36">
         <f>IF(C6=0,0,C24/C6)</f>
         <v/>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="36">
         <f>IF(D6=0,0,D24/D6)</f>
         <v/>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="36">
         <f>IF(E6=0,0,E24/E6)</f>
         <v/>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="36">
         <f>IF(F6=0,0,F24/F6)</f>
         <v/>
       </c>
-      <c r="G25" s="39">
+      <c r="G25" s="36">
         <f>IF(G6=0,0,G24/G6)</f>
         <v/>
       </c>
-      <c r="H25" s="39">
+      <c r="H25" s="36">
         <f>IF(H6=0,0,H24/H6)</f>
         <v/>
       </c>
-      <c r="I25" s="39">
+      <c r="I25" s="36">
         <f>IF(I6=0,0,I24/I6)</f>
         <v/>
       </c>
-      <c r="J25" s="39">
+      <c r="J25" s="36">
         <f>IF(J6=0,0,J24/J6)</f>
         <v/>
       </c>
-      <c r="K25" s="39">
+      <c r="K25" s="36">
         <f>IF(K6=0,0,K24/K6)</f>
         <v/>
       </c>
-      <c r="L25" s="39">
+      <c r="L25" s="36">
         <f>IF(L6=0,0,L24/L6)</f>
         <v/>
       </c>
-      <c r="M25" s="39">
+      <c r="M25" s="36">
         <f>IF(M6=0,0,M24/M6)</f>
         <v/>
       </c>
-      <c r="N25" s="39">
+      <c r="N25" s="36">
         <f>IF(N6=0,0,N24/N6)</f>
         <v/>
       </c>
-      <c r="O25" s="39">
+      <c r="O25" s="36">
         <f>IF(O6=0,0,O24/O6)</f>
         <v/>
       </c>
-      <c r="P25" s="39">
+      <c r="P25" s="36">
         <f>IF(P6=0,0,P24/P6)</f>
         <v/>
       </c>
-      <c r="Q25" s="39">
+      <c r="Q25" s="36">
         <f>IF(Q6=0,0,Q24/Q6)</f>
         <v/>
       </c>
-      <c r="R25" s="39">
+      <c r="R25" s="36">
         <f>IF(R6=0,0,R24/R6)</f>
         <v/>
       </c>
-      <c r="S25" s="39">
+      <c r="S25" s="36">
         <f>IF(S6=0,0,S24/S6)</f>
         <v/>
       </c>
-      <c r="T25" s="39">
+      <c r="T25" s="36">
         <f>IF(T6=0,0,T24/T6)</f>
         <v/>
       </c>
-      <c r="U25" s="39">
+      <c r="U25" s="36">
         <f>IF(U6=0,0,U24/U6)</f>
         <v/>
       </c>
-      <c r="V25" s="39">
+      <c r="V25" s="36">
         <f>IF(V6=0,0,V24/V6)</f>
         <v/>
       </c>
@@ -16998,14 +16390,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>Azalea Hospice &amp; Palliative Care - Tyler, TX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>Profit and Loss</t>
         </is>
@@ -17019,77 +16411,77 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="55" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C5" s="55" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D5" s="55" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E5" s="55" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="F5" s="55" t="inlineStr">
+      <c r="F5" s="51" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="G5" s="55" t="inlineStr">
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="H5" s="55" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="I5" s="55" t="inlineStr">
+      <c r="I5" s="51" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="J5" s="55" t="inlineStr">
+      <c r="J5" s="51" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="K5" s="55" t="inlineStr">
+      <c r="K5" s="51" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="L5" s="55" t="inlineStr">
+      <c r="L5" s="51" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="M5" s="55" t="inlineStr">
+      <c r="M5" s="51" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="N5" s="55" t="inlineStr">
+      <c r="N5" s="51" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="O5" s="55" t="inlineStr">
+      <c r="O5" s="51" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="P5" s="55" t="inlineStr">
+      <c r="P5" s="51" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -17108,63 +16500,63 @@
           <t>Gross Billed Revenue</t>
         </is>
       </c>
-      <c r="B7" s="56">
+      <c r="B7" s="52">
         <f>'Revenue Model'!C14</f>
         <v/>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="52">
         <f>'Revenue Model'!D14</f>
         <v/>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="52">
         <f>'Revenue Model'!E14</f>
         <v/>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="52">
         <f>'Revenue Model'!F14</f>
         <v/>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="52">
         <f>'Revenue Model'!G14</f>
         <v/>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="52">
         <f>'Revenue Model'!H14</f>
         <v/>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="52">
         <f>'Revenue Model'!I14</f>
         <v/>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="52">
         <f>'Revenue Model'!J14</f>
         <v/>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="52">
         <f>'Revenue Model'!K14</f>
         <v/>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="52">
         <f>'Revenue Model'!L14</f>
         <v/>
       </c>
-      <c r="L7" s="56">
+      <c r="L7" s="52">
         <f>'Revenue Model'!M14</f>
         <v/>
       </c>
-      <c r="M7" s="56">
+      <c r="M7" s="52">
         <f>'Revenue Model'!N14</f>
         <v/>
       </c>
-      <c r="N7" s="57">
+      <c r="N7" s="53">
         <f>SUM('Revenue Model'!O14:R14)</f>
         <v/>
       </c>
-      <c r="O7" s="57">
+      <c r="O7" s="53">
         <f>SUM('Revenue Model'!S14:V14)</f>
         <v/>
       </c>
-      <c r="P7" s="58">
+      <c r="P7" s="54">
         <f>SUM(B7:M7)+N7+O7</f>
         <v/>
       </c>
@@ -17175,63 +16567,63 @@
           <t>Less: CDAs Adjustment</t>
         </is>
       </c>
-      <c r="B8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M8" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N8" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O8" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P8" s="58">
+      <c r="B8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N8" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O8" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P8" s="54">
         <f>SUM(B8:M8)+N8+O8</f>
         <v/>
       </c>
@@ -17242,63 +16634,63 @@
           <t>Less: Net Due Zero (Write-offs)</t>
         </is>
       </c>
-      <c r="B9" s="56">
+      <c r="B9" s="52">
         <f>'Revenue Model'!C14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="52">
         <f>'Revenue Model'!D14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="52">
         <f>'Revenue Model'!E14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="52">
         <f>'Revenue Model'!F14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="52">
         <f>'Revenue Model'!G14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="52">
         <f>'Revenue Model'!H14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="H9" s="56">
+      <c r="H9" s="52">
         <f>'Revenue Model'!I14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="I9" s="56">
+      <c r="I9" s="52">
         <f>'Revenue Model'!J14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="J9" s="56">
+      <c r="J9" s="52">
         <f>'Revenue Model'!K14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="K9" s="56">
+      <c r="K9" s="52">
         <f>'Revenue Model'!L14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="L9" s="56">
+      <c r="L9" s="52">
         <f>'Revenue Model'!M14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="M9" s="56">
+      <c r="M9" s="52">
         <f>'Revenue Model'!N14*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="N9" s="57">
+      <c r="N9" s="53">
         <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="O9" s="57">
+      <c r="O9" s="53">
         <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$11</f>
         <v/>
       </c>
-      <c r="P9" s="58">
+      <c r="P9" s="54">
         <f>SUM(B9:M9)+N9+O9</f>
         <v/>
       </c>
@@ -17309,63 +16701,63 @@
           <t>Less: Sequestration</t>
         </is>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="52">
         <f>'Revenue Model'!C14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="52">
         <f>'Revenue Model'!D14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="52">
         <f>'Revenue Model'!E14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="52">
         <f>'Revenue Model'!F14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="52">
         <f>'Revenue Model'!G14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="52">
         <f>'Revenue Model'!H14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="H10" s="56">
+      <c r="H10" s="52">
         <f>'Revenue Model'!I14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="I10" s="56">
+      <c r="I10" s="52">
         <f>'Revenue Model'!J14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="J10" s="56">
+      <c r="J10" s="52">
         <f>'Revenue Model'!K14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="K10" s="56">
+      <c r="K10" s="52">
         <f>'Revenue Model'!L14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="L10" s="56">
+      <c r="L10" s="52">
         <f>'Revenue Model'!M14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="M10" s="56">
+      <c r="M10" s="52">
         <f>'Revenue Model'!N14*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="N10" s="57">
+      <c r="N10" s="53">
         <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="O10" s="57">
+      <c r="O10" s="53">
         <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$10</f>
         <v/>
       </c>
-      <c r="P10" s="58">
+      <c r="P10" s="54">
         <f>SUM(B10:M10)+N10+O10</f>
         <v/>
       </c>
@@ -17376,63 +16768,63 @@
           <t>Less: Medication Adjustments</t>
         </is>
       </c>
-      <c r="B11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M11" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N11" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O11" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P11" s="58">
+      <c r="B11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N11" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O11" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P11" s="54">
         <f>SUM(B11:M11)+N11+O11</f>
         <v/>
       </c>
@@ -17443,63 +16835,63 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="59">
+      <c r="B12" s="55">
         <f>B7-B8-B9-B10-B11</f>
         <v/>
       </c>
-      <c r="C12" s="59">
+      <c r="C12" s="55">
         <f>C7-C8-C9-C10-C11</f>
         <v/>
       </c>
-      <c r="D12" s="59">
+      <c r="D12" s="55">
         <f>D7-D8-D9-D10-D11</f>
         <v/>
       </c>
-      <c r="E12" s="59">
+      <c r="E12" s="55">
         <f>E7-E8-E9-E10-E11</f>
         <v/>
       </c>
-      <c r="F12" s="59">
+      <c r="F12" s="55">
         <f>F7-F8-F9-F10-F11</f>
         <v/>
       </c>
-      <c r="G12" s="59">
+      <c r="G12" s="55">
         <f>G7-G8-G9-G10-G11</f>
         <v/>
       </c>
-      <c r="H12" s="59">
+      <c r="H12" s="55">
         <f>H7-H8-H9-H10-H11</f>
         <v/>
       </c>
-      <c r="I12" s="59">
+      <c r="I12" s="55">
         <f>I7-I8-I9-I10-I11</f>
         <v/>
       </c>
-      <c r="J12" s="59">
+      <c r="J12" s="55">
         <f>J7-J8-J9-J10-J11</f>
         <v/>
       </c>
-      <c r="K12" s="59">
+      <c r="K12" s="55">
         <f>K7-K8-K9-K10-K11</f>
         <v/>
       </c>
-      <c r="L12" s="59">
+      <c r="L12" s="55">
         <f>L7-L8-L9-L10-L11</f>
         <v/>
       </c>
-      <c r="M12" s="59">
+      <c r="M12" s="55">
         <f>M7-M8-M9-M10-M11</f>
         <v/>
       </c>
-      <c r="N12" s="59">
+      <c r="N12" s="55">
         <f>N7-N8-N9-N10-N11</f>
         <v/>
       </c>
-      <c r="O12" s="59">
+      <c r="O12" s="55">
         <f>O7-O8-O9-O10-O11</f>
         <v/>
       </c>
-      <c r="P12" s="59">
+      <c r="P12" s="55">
         <f>P7-P8-P9-P10-P11</f>
         <v/>
       </c>
@@ -17517,63 +16909,63 @@
           <t>Pharmacy</t>
         </is>
       </c>
-      <c r="B15" s="56">
+      <c r="B15" s="52">
         <f>'Revenue Model'!C12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="C15" s="56">
+      <c r="C15" s="52">
         <f>'Revenue Model'!D12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="52">
         <f>'Revenue Model'!E12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="52">
         <f>'Revenue Model'!F12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="52">
         <f>'Revenue Model'!G12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="52">
         <f>'Revenue Model'!H12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="H15" s="56">
+      <c r="H15" s="52">
         <f>'Revenue Model'!I12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="I15" s="56">
+      <c r="I15" s="52">
         <f>'Revenue Model'!J12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="J15" s="56">
+      <c r="J15" s="52">
         <f>'Revenue Model'!K12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="K15" s="56">
+      <c r="K15" s="52">
         <f>'Revenue Model'!L12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="L15" s="56">
+      <c r="L15" s="52">
         <f>'Revenue Model'!M12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="M15" s="56">
+      <c r="M15" s="52">
         <f>'Revenue Model'!N12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="N15" s="57">
+      <c r="N15" s="53">
         <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="O15" s="57">
+      <c r="O15" s="53">
         <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="P15" s="58">
+      <c r="P15" s="54">
         <f>SUM(B15:M15)+N15+O15</f>
         <v/>
       </c>
@@ -17584,63 +16976,63 @@
           <t>Medical Supplies</t>
         </is>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="52">
         <f>'Revenue Model'!C12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="52">
         <f>'Revenue Model'!D12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="52">
         <f>'Revenue Model'!E12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="52">
         <f>'Revenue Model'!F12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="52">
         <f>'Revenue Model'!G12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="G16" s="56">
+      <c r="G16" s="52">
         <f>'Revenue Model'!H12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="H16" s="56">
+      <c r="H16" s="52">
         <f>'Revenue Model'!I12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="I16" s="56">
+      <c r="I16" s="52">
         <f>'Revenue Model'!J12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="J16" s="56">
+      <c r="J16" s="52">
         <f>'Revenue Model'!K12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="K16" s="56">
+      <c r="K16" s="52">
         <f>'Revenue Model'!L12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="L16" s="56">
+      <c r="L16" s="52">
         <f>'Revenue Model'!M12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="M16" s="56">
+      <c r="M16" s="52">
         <f>'Revenue Model'!N12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="N16" s="57">
+      <c r="N16" s="53">
         <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="O16" s="57">
+      <c r="O16" s="53">
         <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="P16" s="58">
+      <c r="P16" s="54">
         <f>SUM(B16:M16)+N16+O16</f>
         <v/>
       </c>
@@ -17651,63 +17043,63 @@
           <t>Durable Medical Equipment (DME)</t>
         </is>
       </c>
-      <c r="B17" s="56">
+      <c r="B17" s="52">
         <f>'Revenue Model'!C12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="C17" s="56">
+      <c r="C17" s="52">
         <f>'Revenue Model'!D12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="D17" s="56">
+      <c r="D17" s="52">
         <f>'Revenue Model'!E12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="52">
         <f>'Revenue Model'!F12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="52">
         <f>'Revenue Model'!G12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="52">
         <f>'Revenue Model'!H12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="52">
         <f>'Revenue Model'!I12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="52">
         <f>'Revenue Model'!J12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="J17" s="56">
+      <c r="J17" s="52">
         <f>'Revenue Model'!K12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="K17" s="56">
+      <c r="K17" s="52">
         <f>'Revenue Model'!L12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="L17" s="56">
+      <c r="L17" s="52">
         <f>'Revenue Model'!M12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="M17" s="56">
+      <c r="M17" s="52">
         <f>'Revenue Model'!N12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="N17" s="57">
+      <c r="N17" s="53">
         <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="O17" s="57">
+      <c r="O17" s="53">
         <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="P17" s="58">
+      <c r="P17" s="54">
         <f>SUM(B17:M17)+N17+O17</f>
         <v/>
       </c>
@@ -17718,63 +17110,63 @@
           <t>Respite Care</t>
         </is>
       </c>
-      <c r="B18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M18" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N18" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O18" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P18" s="58">
+      <c r="B18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N18" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O18" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P18" s="54">
         <f>SUM(B18:M18)+N18+O18</f>
         <v/>
       </c>
@@ -17785,63 +17177,63 @@
           <t>Transportation</t>
         </is>
       </c>
-      <c r="B19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M19" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N19" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O19" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P19" s="58">
+      <c r="B19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N19" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O19" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P19" s="54">
         <f>SUM(B19:M19)+N19+O19</f>
         <v/>
       </c>
@@ -17852,63 +17244,63 @@
           <t>Infusion / Labs</t>
         </is>
       </c>
-      <c r="B20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M20" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N20" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O20" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P20" s="58">
+      <c r="B20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N20" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O20" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P20" s="54">
         <f>SUM(B20:M20)+N20+O20</f>
         <v/>
       </c>
@@ -17919,63 +17311,63 @@
           <t>PT / OT / ST</t>
         </is>
       </c>
-      <c r="B21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M21" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N21" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O21" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P21" s="58">
+      <c r="B21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N21" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O21" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P21" s="54">
         <f>SUM(B21:M21)+N21+O21</f>
         <v/>
       </c>
@@ -17986,63 +17378,63 @@
           <t>Total Cost of Services</t>
         </is>
       </c>
-      <c r="B22" s="59">
+      <c r="B22" s="55">
         <f>SUM(B15:B21)</f>
         <v/>
       </c>
-      <c r="C22" s="59">
+      <c r="C22" s="55">
         <f>SUM(C15:C21)</f>
         <v/>
       </c>
-      <c r="D22" s="59">
+      <c r="D22" s="55">
         <f>SUM(D15:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="59">
+      <c r="E22" s="55">
         <f>SUM(E15:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="59">
+      <c r="F22" s="55">
         <f>SUM(F15:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="59">
+      <c r="G22" s="55">
         <f>SUM(G15:G21)</f>
         <v/>
       </c>
-      <c r="H22" s="59">
+      <c r="H22" s="55">
         <f>SUM(H15:H21)</f>
         <v/>
       </c>
-      <c r="I22" s="59">
+      <c r="I22" s="55">
         <f>SUM(I15:I21)</f>
         <v/>
       </c>
-      <c r="J22" s="59">
+      <c r="J22" s="55">
         <f>SUM(J15:J21)</f>
         <v/>
       </c>
-      <c r="K22" s="59">
+      <c r="K22" s="55">
         <f>SUM(K15:K21)</f>
         <v/>
       </c>
-      <c r="L22" s="59">
+      <c r="L22" s="55">
         <f>SUM(L15:L21)</f>
         <v/>
       </c>
-      <c r="M22" s="59">
+      <c r="M22" s="55">
         <f>SUM(M15:M21)</f>
         <v/>
       </c>
-      <c r="N22" s="59">
+      <c r="N22" s="55">
         <f>SUM(N15:N21)</f>
         <v/>
       </c>
-      <c r="O22" s="59">
+      <c r="O22" s="55">
         <f>SUM(O15:O21)</f>
         <v/>
       </c>
-      <c r="P22" s="59">
+      <c r="P22" s="55">
         <f>SUM(P15:P21)</f>
         <v/>
       </c>
@@ -18053,63 +17445,63 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B24" s="59">
+      <c r="B24" s="55">
         <f>B12-B22</f>
         <v/>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="55">
         <f>C12-C22</f>
         <v/>
       </c>
-      <c r="D24" s="59">
+      <c r="D24" s="55">
         <f>D12-D22</f>
         <v/>
       </c>
-      <c r="E24" s="59">
+      <c r="E24" s="55">
         <f>E12-E22</f>
         <v/>
       </c>
-      <c r="F24" s="59">
+      <c r="F24" s="55">
         <f>F12-F22</f>
         <v/>
       </c>
-      <c r="G24" s="59">
+      <c r="G24" s="55">
         <f>G12-G22</f>
         <v/>
       </c>
-      <c r="H24" s="59">
+      <c r="H24" s="55">
         <f>H12-H22</f>
         <v/>
       </c>
-      <c r="I24" s="59">
+      <c r="I24" s="55">
         <f>I12-I22</f>
         <v/>
       </c>
-      <c r="J24" s="59">
+      <c r="J24" s="55">
         <f>J12-J22</f>
         <v/>
       </c>
-      <c r="K24" s="59">
+      <c r="K24" s="55">
         <f>K12-K22</f>
         <v/>
       </c>
-      <c r="L24" s="59">
+      <c r="L24" s="55">
         <f>L12-L22</f>
         <v/>
       </c>
-      <c r="M24" s="59">
+      <c r="M24" s="55">
         <f>M12-M22</f>
         <v/>
       </c>
-      <c r="N24" s="59">
+      <c r="N24" s="55">
         <f>N12-N22</f>
         <v/>
       </c>
-      <c r="O24" s="59">
+      <c r="O24" s="55">
         <f>O12-O22</f>
         <v/>
       </c>
-      <c r="P24" s="59">
+      <c r="P24" s="55">
         <f>P12-P22</f>
         <v/>
       </c>
@@ -18129,604 +17521,604 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="60" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>Payroll - 1st Half</t>
         </is>
       </c>
-      <c r="B28" s="56">
+      <c r="B28" s="52">
         <f>('Staffing &amp; Payroll'!C30+'Staffing &amp; Payroll'!C42+'Staffing &amp; Payroll'!C38+'Staffing &amp; Payroll'!C43)/2</f>
         <v/>
       </c>
-      <c r="C28" s="56">
+      <c r="C28" s="52">
         <f>('Staffing &amp; Payroll'!D30+'Staffing &amp; Payroll'!D42+'Staffing &amp; Payroll'!D38+'Staffing &amp; Payroll'!D43)/2</f>
         <v/>
       </c>
-      <c r="D28" s="56">
+      <c r="D28" s="52">
         <f>('Staffing &amp; Payroll'!E30+'Staffing &amp; Payroll'!E42+'Staffing &amp; Payroll'!E38+'Staffing &amp; Payroll'!E43)/2</f>
         <v/>
       </c>
-      <c r="E28" s="56">
+      <c r="E28" s="52">
         <f>('Staffing &amp; Payroll'!F30+'Staffing &amp; Payroll'!F42+'Staffing &amp; Payroll'!F38+'Staffing &amp; Payroll'!F43)/2</f>
         <v/>
       </c>
-      <c r="F28" s="56">
+      <c r="F28" s="52">
         <f>('Staffing &amp; Payroll'!G30+'Staffing &amp; Payroll'!G42+'Staffing &amp; Payroll'!G38+'Staffing &amp; Payroll'!G43)/2</f>
         <v/>
       </c>
-      <c r="G28" s="56">
+      <c r="G28" s="52">
         <f>('Staffing &amp; Payroll'!H30+'Staffing &amp; Payroll'!H42+'Staffing &amp; Payroll'!H38+'Staffing &amp; Payroll'!H43)/2</f>
         <v/>
       </c>
-      <c r="H28" s="56">
+      <c r="H28" s="52">
         <f>('Staffing &amp; Payroll'!I30+'Staffing &amp; Payroll'!I42+'Staffing &amp; Payroll'!I38+'Staffing &amp; Payroll'!I43)/2</f>
         <v/>
       </c>
-      <c r="I28" s="56">
+      <c r="I28" s="52">
         <f>('Staffing &amp; Payroll'!J30+'Staffing &amp; Payroll'!J42+'Staffing &amp; Payroll'!J38+'Staffing &amp; Payroll'!J43)/2</f>
         <v/>
       </c>
-      <c r="J28" s="56">
+      <c r="J28" s="52">
         <f>('Staffing &amp; Payroll'!K30+'Staffing &amp; Payroll'!K42+'Staffing &amp; Payroll'!K38+'Staffing &amp; Payroll'!K43)/2</f>
         <v/>
       </c>
-      <c r="K28" s="56">
+      <c r="K28" s="52">
         <f>('Staffing &amp; Payroll'!L30+'Staffing &amp; Payroll'!L42+'Staffing &amp; Payroll'!L38+'Staffing &amp; Payroll'!L43)/2</f>
         <v/>
       </c>
-      <c r="L28" s="56">
+      <c r="L28" s="52">
         <f>('Staffing &amp; Payroll'!M30+'Staffing &amp; Payroll'!M42+'Staffing &amp; Payroll'!M38+'Staffing &amp; Payroll'!M43)/2</f>
         <v/>
       </c>
-      <c r="M28" s="56">
+      <c r="M28" s="52">
         <f>('Staffing &amp; Payroll'!N30+'Staffing &amp; Payroll'!N42+'Staffing &amp; Payroll'!N38+'Staffing &amp; Payroll'!N43)/2</f>
         <v/>
       </c>
-      <c r="N28" s="57">
+      <c r="N28" s="53">
         <f>(SUM('Staffing &amp; Payroll'!O30:R30)+SUM('Staffing &amp; Payroll'!O42:R42)+SUM('Staffing &amp; Payroll'!O38:R38)+SUM('Staffing &amp; Payroll'!O43:R43))/2</f>
         <v/>
       </c>
-      <c r="O28" s="57">
+      <c r="O28" s="53">
         <f>(SUM('Staffing &amp; Payroll'!S30:V30)+SUM('Staffing &amp; Payroll'!S42:V42)+SUM('Staffing &amp; Payroll'!S38:V38)+SUM('Staffing &amp; Payroll'!S43:V43))/2</f>
         <v/>
       </c>
-      <c r="P28" s="58">
+      <c r="P28" s="54">
         <f>SUM(B28:M28)+N28+O28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>Payroll - 2nd Half</t>
         </is>
       </c>
-      <c r="B29" s="56">
+      <c r="B29" s="52">
         <f>('Staffing &amp; Payroll'!C30+'Staffing &amp; Payroll'!C42+'Staffing &amp; Payroll'!C38+'Staffing &amp; Payroll'!C43)/2</f>
         <v/>
       </c>
-      <c r="C29" s="56">
+      <c r="C29" s="52">
         <f>('Staffing &amp; Payroll'!D30+'Staffing &amp; Payroll'!D42+'Staffing &amp; Payroll'!D38+'Staffing &amp; Payroll'!D43)/2</f>
         <v/>
       </c>
-      <c r="D29" s="56">
+      <c r="D29" s="52">
         <f>('Staffing &amp; Payroll'!E30+'Staffing &amp; Payroll'!E42+'Staffing &amp; Payroll'!E38+'Staffing &amp; Payroll'!E43)/2</f>
         <v/>
       </c>
-      <c r="E29" s="56">
+      <c r="E29" s="52">
         <f>('Staffing &amp; Payroll'!F30+'Staffing &amp; Payroll'!F42+'Staffing &amp; Payroll'!F38+'Staffing &amp; Payroll'!F43)/2</f>
         <v/>
       </c>
-      <c r="F29" s="56">
+      <c r="F29" s="52">
         <f>('Staffing &amp; Payroll'!G30+'Staffing &amp; Payroll'!G42+'Staffing &amp; Payroll'!G38+'Staffing &amp; Payroll'!G43)/2</f>
         <v/>
       </c>
-      <c r="G29" s="56">
+      <c r="G29" s="52">
         <f>('Staffing &amp; Payroll'!H30+'Staffing &amp; Payroll'!H42+'Staffing &amp; Payroll'!H38+'Staffing &amp; Payroll'!H43)/2</f>
         <v/>
       </c>
-      <c r="H29" s="56">
+      <c r="H29" s="52">
         <f>('Staffing &amp; Payroll'!I30+'Staffing &amp; Payroll'!I42+'Staffing &amp; Payroll'!I38+'Staffing &amp; Payroll'!I43)/2</f>
         <v/>
       </c>
-      <c r="I29" s="56">
+      <c r="I29" s="52">
         <f>('Staffing &amp; Payroll'!J30+'Staffing &amp; Payroll'!J42+'Staffing &amp; Payroll'!J38+'Staffing &amp; Payroll'!J43)/2</f>
         <v/>
       </c>
-      <c r="J29" s="56">
+      <c r="J29" s="52">
         <f>('Staffing &amp; Payroll'!K30+'Staffing &amp; Payroll'!K42+'Staffing &amp; Payroll'!K38+'Staffing &amp; Payroll'!K43)/2</f>
         <v/>
       </c>
-      <c r="K29" s="56">
+      <c r="K29" s="52">
         <f>('Staffing &amp; Payroll'!L30+'Staffing &amp; Payroll'!L42+'Staffing &amp; Payroll'!L38+'Staffing &amp; Payroll'!L43)/2</f>
         <v/>
       </c>
-      <c r="L29" s="56">
+      <c r="L29" s="52">
         <f>('Staffing &amp; Payroll'!M30+'Staffing &amp; Payroll'!M42+'Staffing &amp; Payroll'!M38+'Staffing &amp; Payroll'!M43)/2</f>
         <v/>
       </c>
-      <c r="M29" s="56">
+      <c r="M29" s="52">
         <f>('Staffing &amp; Payroll'!N30+'Staffing &amp; Payroll'!N42+'Staffing &amp; Payroll'!N38+'Staffing &amp; Payroll'!N43)/2</f>
         <v/>
       </c>
-      <c r="N29" s="57">
+      <c r="N29" s="53">
         <f>(SUM('Staffing &amp; Payroll'!O30:R30)+SUM('Staffing &amp; Payroll'!O42:R42)+SUM('Staffing &amp; Payroll'!O38:R38)+SUM('Staffing &amp; Payroll'!O43:R43))/2</f>
         <v/>
       </c>
-      <c r="O29" s="57">
+      <c r="O29" s="53">
         <f>(SUM('Staffing &amp; Payroll'!S30:V30)+SUM('Staffing &amp; Payroll'!S42:V42)+SUM('Staffing &amp; Payroll'!S38:V38)+SUM('Staffing &amp; Payroll'!S43:V43))/2</f>
         <v/>
       </c>
-      <c r="P29" s="58">
+      <c r="P29" s="54">
         <f>SUM(B29:M29)+N29+O29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="56" t="inlineStr">
         <is>
           <t>Payroll YTD Adjustments</t>
         </is>
       </c>
-      <c r="B30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M30" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N30" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O30" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P30" s="58">
+      <c r="B30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N30" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O30" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P30" s="54">
         <f>SUM(B30:M30)+N30+O30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="56" t="inlineStr">
         <is>
           <t>Employer Taxes (FUTA/SUI/FICA/WC)</t>
         </is>
       </c>
-      <c r="B31" s="56">
+      <c r="B31" s="52">
         <f>'Staffing &amp; Payroll'!C48+'Staffing &amp; Payroll'!C49</f>
         <v/>
       </c>
-      <c r="C31" s="56">
+      <c r="C31" s="52">
         <f>'Staffing &amp; Payroll'!D48+'Staffing &amp; Payroll'!D49</f>
         <v/>
       </c>
-      <c r="D31" s="56">
+      <c r="D31" s="52">
         <f>'Staffing &amp; Payroll'!E48+'Staffing &amp; Payroll'!E49</f>
         <v/>
       </c>
-      <c r="E31" s="56">
+      <c r="E31" s="52">
         <f>'Staffing &amp; Payroll'!F48+'Staffing &amp; Payroll'!F49</f>
         <v/>
       </c>
-      <c r="F31" s="56">
+      <c r="F31" s="52">
         <f>'Staffing &amp; Payroll'!G48+'Staffing &amp; Payroll'!G49</f>
         <v/>
       </c>
-      <c r="G31" s="56">
+      <c r="G31" s="52">
         <f>'Staffing &amp; Payroll'!H48+'Staffing &amp; Payroll'!H49</f>
         <v/>
       </c>
-      <c r="H31" s="56">
+      <c r="H31" s="52">
         <f>'Staffing &amp; Payroll'!I48+'Staffing &amp; Payroll'!I49</f>
         <v/>
       </c>
-      <c r="I31" s="56">
+      <c r="I31" s="52">
         <f>'Staffing &amp; Payroll'!J48+'Staffing &amp; Payroll'!J49</f>
         <v/>
       </c>
-      <c r="J31" s="56">
+      <c r="J31" s="52">
         <f>'Staffing &amp; Payroll'!K48+'Staffing &amp; Payroll'!K49</f>
         <v/>
       </c>
-      <c r="K31" s="56">
+      <c r="K31" s="52">
         <f>'Staffing &amp; Payroll'!L48+'Staffing &amp; Payroll'!L49</f>
         <v/>
       </c>
-      <c r="L31" s="56">
+      <c r="L31" s="52">
         <f>'Staffing &amp; Payroll'!M48+'Staffing &amp; Payroll'!M49</f>
         <v/>
       </c>
-      <c r="M31" s="56">
+      <c r="M31" s="52">
         <f>'Staffing &amp; Payroll'!N48+'Staffing &amp; Payroll'!N49</f>
         <v/>
       </c>
-      <c r="N31" s="57">
+      <c r="N31" s="53">
         <f>SUM('Staffing &amp; Payroll'!O48:R48)+SUM('Staffing &amp; Payroll'!O49:R49)</f>
         <v/>
       </c>
-      <c r="O31" s="57">
+      <c r="O31" s="53">
         <f>SUM('Staffing &amp; Payroll'!S48:V48)+SUM('Staffing &amp; Payroll'!S49:V49)</f>
         <v/>
       </c>
-      <c r="P31" s="58">
+      <c r="P31" s="54">
         <f>SUM(B31:M31)+N31+O31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="60" t="inlineStr">
+      <c r="A32" s="56" t="inlineStr">
         <is>
           <t>Contract Labor</t>
         </is>
       </c>
-      <c r="B32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M32" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N32" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O32" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P32" s="58">
+      <c r="B32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N32" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O32" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P32" s="54">
         <f>SUM(B32:M32)+N32+O32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr">
+      <c r="A33" s="56" t="inlineStr">
         <is>
           <t>Medical Director</t>
         </is>
       </c>
-      <c r="B33" s="56">
+      <c r="B33" s="52">
         <f>'Staffing &amp; Payroll'!C39</f>
         <v/>
       </c>
-      <c r="C33" s="56">
+      <c r="C33" s="52">
         <f>'Staffing &amp; Payroll'!D39</f>
         <v/>
       </c>
-      <c r="D33" s="56">
+      <c r="D33" s="52">
         <f>'Staffing &amp; Payroll'!E39</f>
         <v/>
       </c>
-      <c r="E33" s="56">
+      <c r="E33" s="52">
         <f>'Staffing &amp; Payroll'!F39</f>
         <v/>
       </c>
-      <c r="F33" s="56">
+      <c r="F33" s="52">
         <f>'Staffing &amp; Payroll'!G39</f>
         <v/>
       </c>
-      <c r="G33" s="56">
+      <c r="G33" s="52">
         <f>'Staffing &amp; Payroll'!H39</f>
         <v/>
       </c>
-      <c r="H33" s="56">
+      <c r="H33" s="52">
         <f>'Staffing &amp; Payroll'!I39</f>
         <v/>
       </c>
-      <c r="I33" s="56">
+      <c r="I33" s="52">
         <f>'Staffing &amp; Payroll'!J39</f>
         <v/>
       </c>
-      <c r="J33" s="56">
+      <c r="J33" s="52">
         <f>'Staffing &amp; Payroll'!K39</f>
         <v/>
       </c>
-      <c r="K33" s="56">
+      <c r="K33" s="52">
         <f>'Staffing &amp; Payroll'!L39</f>
         <v/>
       </c>
-      <c r="L33" s="56">
+      <c r="L33" s="52">
         <f>'Staffing &amp; Payroll'!M39</f>
         <v/>
       </c>
-      <c r="M33" s="56">
+      <c r="M33" s="52">
         <f>'Staffing &amp; Payroll'!N39</f>
         <v/>
       </c>
-      <c r="N33" s="57">
+      <c r="N33" s="53">
         <f>SUM('Staffing &amp; Payroll'!O39:R39)</f>
         <v/>
       </c>
-      <c r="O33" s="57">
+      <c r="O33" s="53">
         <f>SUM('Staffing &amp; Payroll'!S39:V39)</f>
         <v/>
       </c>
-      <c r="P33" s="58">
+      <c r="P33" s="54">
         <f>SUM(B33:M33)+N33+O33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="56" t="inlineStr">
         <is>
           <t>Medical Director 2</t>
         </is>
       </c>
-      <c r="B34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M34" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N34" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O34" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P34" s="58">
+      <c r="B34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N34" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O34" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P34" s="54">
         <f>SUM(B34:M34)+N34+O34</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="A35" s="56" t="inlineStr">
         <is>
           <t>Intercompany Transfer</t>
         </is>
       </c>
-      <c r="B35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M35" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N35" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O35" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P35" s="58">
+      <c r="B35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N35" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O35" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P35" s="54">
         <f>SUM(B35:M35)+N35+O35</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="56" t="inlineStr">
         <is>
           <t>Staff Other (health insurance)</t>
         </is>
       </c>
-      <c r="B36" s="56">
+      <c r="B36" s="52">
         <f>'Staffing &amp; Payroll'!C50+'Staffing &amp; Payroll'!C51</f>
         <v/>
       </c>
-      <c r="C36" s="56">
+      <c r="C36" s="52">
         <f>'Staffing &amp; Payroll'!D50+'Staffing &amp; Payroll'!D51</f>
         <v/>
       </c>
-      <c r="D36" s="56">
+      <c r="D36" s="52">
         <f>'Staffing &amp; Payroll'!E50+'Staffing &amp; Payroll'!E51</f>
         <v/>
       </c>
-      <c r="E36" s="56">
+      <c r="E36" s="52">
         <f>'Staffing &amp; Payroll'!F50+'Staffing &amp; Payroll'!F51</f>
         <v/>
       </c>
-      <c r="F36" s="56">
+      <c r="F36" s="52">
         <f>'Staffing &amp; Payroll'!G50+'Staffing &amp; Payroll'!G51</f>
         <v/>
       </c>
-      <c r="G36" s="56">
+      <c r="G36" s="52">
         <f>'Staffing &amp; Payroll'!H50+'Staffing &amp; Payroll'!H51</f>
         <v/>
       </c>
-      <c r="H36" s="56">
+      <c r="H36" s="52">
         <f>'Staffing &amp; Payroll'!I50+'Staffing &amp; Payroll'!I51</f>
         <v/>
       </c>
-      <c r="I36" s="56">
+      <c r="I36" s="52">
         <f>'Staffing &amp; Payroll'!J50+'Staffing &amp; Payroll'!J51</f>
         <v/>
       </c>
-      <c r="J36" s="56">
+      <c r="J36" s="52">
         <f>'Staffing &amp; Payroll'!K50+'Staffing &amp; Payroll'!K51</f>
         <v/>
       </c>
-      <c r="K36" s="56">
+      <c r="K36" s="52">
         <f>'Staffing &amp; Payroll'!L50+'Staffing &amp; Payroll'!L51</f>
         <v/>
       </c>
-      <c r="L36" s="56">
+      <c r="L36" s="52">
         <f>'Staffing &amp; Payroll'!M50+'Staffing &amp; Payroll'!M51</f>
         <v/>
       </c>
-      <c r="M36" s="56">
+      <c r="M36" s="52">
         <f>'Staffing &amp; Payroll'!N50+'Staffing &amp; Payroll'!N51</f>
         <v/>
       </c>
-      <c r="N36" s="57">
+      <c r="N36" s="53">
         <f>SUM('Staffing &amp; Payroll'!O50:R50)+SUM('Staffing &amp; Payroll'!O51:R51)</f>
         <v/>
       </c>
-      <c r="O36" s="57">
+      <c r="O36" s="53">
         <f>SUM('Staffing &amp; Payroll'!S50:V50)+SUM('Staffing &amp; Payroll'!S51:V51)</f>
         <v/>
       </c>
-      <c r="P36" s="58">
+      <c r="P36" s="54">
         <f>SUM(B36:M36)+N36+O36</f>
         <v/>
       </c>
@@ -18737,63 +18129,63 @@
           <t>Total Payroll &amp; Related</t>
         </is>
       </c>
-      <c r="B37" s="59">
+      <c r="B37" s="55">
         <f>SUM(B28:B36)</f>
         <v/>
       </c>
-      <c r="C37" s="59">
+      <c r="C37" s="55">
         <f>SUM(C28:C36)</f>
         <v/>
       </c>
-      <c r="D37" s="59">
+      <c r="D37" s="55">
         <f>SUM(D28:D36)</f>
         <v/>
       </c>
-      <c r="E37" s="59">
+      <c r="E37" s="55">
         <f>SUM(E28:E36)</f>
         <v/>
       </c>
-      <c r="F37" s="59">
+      <c r="F37" s="55">
         <f>SUM(F28:F36)</f>
         <v/>
       </c>
-      <c r="G37" s="59">
+      <c r="G37" s="55">
         <f>SUM(G28:G36)</f>
         <v/>
       </c>
-      <c r="H37" s="59">
+      <c r="H37" s="55">
         <f>SUM(H28:H36)</f>
         <v/>
       </c>
-      <c r="I37" s="59">
+      <c r="I37" s="55">
         <f>SUM(I28:I36)</f>
         <v/>
       </c>
-      <c r="J37" s="59">
+      <c r="J37" s="55">
         <f>SUM(J28:J36)</f>
         <v/>
       </c>
-      <c r="K37" s="59">
+      <c r="K37" s="55">
         <f>SUM(K28:K36)</f>
         <v/>
       </c>
-      <c r="L37" s="59">
+      <c r="L37" s="55">
         <f>SUM(L28:L36)</f>
         <v/>
       </c>
-      <c r="M37" s="59">
+      <c r="M37" s="55">
         <f>SUM(M28:M36)</f>
         <v/>
       </c>
-      <c r="N37" s="59">
+      <c r="N37" s="55">
         <f>SUM(N28:N36)</f>
         <v/>
       </c>
-      <c r="O37" s="59">
+      <c r="O37" s="55">
         <f>SUM(O28:O36)</f>
         <v/>
       </c>
-      <c r="P37" s="59">
+      <c r="P37" s="55">
         <f>SUM(P28:P36)</f>
         <v/>
       </c>
@@ -18806,1542 +18198,1542 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="60" t="inlineStr">
+      <c r="A40" s="56" t="inlineStr">
         <is>
           <t>Bank / Payroll Fees</t>
         </is>
       </c>
-      <c r="B40" s="56">
+      <c r="B40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="C40" s="56">
+      <c r="C40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="D40" s="56">
+      <c r="D40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="E40" s="56">
+      <c r="E40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="F40" s="56">
+      <c r="F40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="G40" s="56">
+      <c r="G40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="H40" s="56">
+      <c r="H40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="I40" s="56">
+      <c r="I40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="J40" s="56">
+      <c r="J40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="K40" s="56">
+      <c r="K40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="L40" s="56">
+      <c r="L40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="M40" s="56">
+      <c r="M40" s="52">
         <f>Inputs!$B$101</f>
         <v/>
       </c>
-      <c r="N40" s="57">
+      <c r="N40" s="53">
         <f>Inputs!$B$101*12</f>
         <v/>
       </c>
-      <c r="O40" s="57">
+      <c r="O40" s="53">
         <f>Inputs!$B$101*12</f>
         <v/>
       </c>
-      <c r="P40" s="58">
+      <c r="P40" s="54">
         <f>SUM(B40:M40)+N40+O40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>Triple Net Rent</t>
         </is>
       </c>
-      <c r="B41" s="56">
+      <c r="B41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="C41" s="56">
+      <c r="C41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="D41" s="56">
+      <c r="D41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="E41" s="56">
+      <c r="E41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="F41" s="56">
+      <c r="F41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="G41" s="56">
+      <c r="G41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="H41" s="56">
+      <c r="H41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="I41" s="56">
+      <c r="I41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="J41" s="56">
+      <c r="J41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="K41" s="56">
+      <c r="K41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="L41" s="56">
+      <c r="L41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="M41" s="56">
+      <c r="M41" s="52">
         <f>Inputs!$B$102</f>
         <v/>
       </c>
-      <c r="N41" s="57">
+      <c r="N41" s="53">
         <f>Inputs!$B$102*12</f>
         <v/>
       </c>
-      <c r="O41" s="57">
+      <c r="O41" s="53">
         <f>Inputs!$B$102*12</f>
         <v/>
       </c>
-      <c r="P41" s="58">
+      <c r="P41" s="54">
         <f>SUM(B41:M41)+N41+O41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="60" t="inlineStr">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B42" s="56">
+      <c r="B42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="C42" s="56">
+      <c r="C42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="D42" s="56">
+      <c r="D42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="E42" s="56">
+      <c r="E42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="F42" s="56">
+      <c r="F42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="G42" s="56">
+      <c r="G42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="H42" s="56">
+      <c r="H42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="I42" s="56">
+      <c r="I42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="J42" s="56">
+      <c r="J42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="K42" s="56">
+      <c r="K42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="L42" s="56">
+      <c r="L42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="M42" s="56">
+      <c r="M42" s="52">
         <f>Inputs!$B$91</f>
         <v/>
       </c>
-      <c r="N42" s="57">
+      <c r="N42" s="53">
         <f>Inputs!$B$91*12</f>
         <v/>
       </c>
-      <c r="O42" s="57">
+      <c r="O42" s="53">
         <f>Inputs!$B$91*12</f>
         <v/>
       </c>
-      <c r="P42" s="58">
+      <c r="P42" s="54">
         <f>SUM(B42:M42)+N42+O42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="60" t="inlineStr">
+      <c r="A43" s="56" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="B43" s="56">
+      <c r="B43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="C43" s="56">
+      <c r="C43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="D43" s="56">
+      <c r="D43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="E43" s="56">
+      <c r="E43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="F43" s="56">
+      <c r="F43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="G43" s="56">
+      <c r="G43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="H43" s="56">
+      <c r="H43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="I43" s="56">
+      <c r="I43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="J43" s="56">
+      <c r="J43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="K43" s="56">
+      <c r="K43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="L43" s="56">
+      <c r="L43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="M43" s="56">
+      <c r="M43" s="52">
         <f>Inputs!$B$92</f>
         <v/>
       </c>
-      <c r="N43" s="57">
+      <c r="N43" s="53">
         <f>Inputs!$B$92*12</f>
         <v/>
       </c>
-      <c r="O43" s="57">
+      <c r="O43" s="53">
         <f>Inputs!$B$92*12</f>
         <v/>
       </c>
-      <c r="P43" s="58">
+      <c r="P43" s="54">
         <f>SUM(B43:M43)+N43+O43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="A44" s="56" t="inlineStr">
         <is>
           <t>Telephone / Fax</t>
         </is>
       </c>
-      <c r="B44" s="56">
+      <c r="B44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="C44" s="56">
+      <c r="C44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="D44" s="56">
+      <c r="D44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="E44" s="56">
+      <c r="E44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="F44" s="56">
+      <c r="F44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="G44" s="56">
+      <c r="G44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="H44" s="56">
+      <c r="H44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="I44" s="56">
+      <c r="I44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="J44" s="56">
+      <c r="J44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="K44" s="56">
+      <c r="K44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="L44" s="56">
+      <c r="L44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="M44" s="56">
+      <c r="M44" s="52">
         <f>Inputs!$B$93</f>
         <v/>
       </c>
-      <c r="N44" s="57">
+      <c r="N44" s="53">
         <f>Inputs!$B$93*12</f>
         <v/>
       </c>
-      <c r="O44" s="57">
+      <c r="O44" s="53">
         <f>Inputs!$B$93*12</f>
         <v/>
       </c>
-      <c r="P44" s="58">
+      <c r="P44" s="54">
         <f>SUM(B44:M44)+N44+O44</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="60" t="inlineStr">
+      <c r="A45" s="56" t="inlineStr">
         <is>
           <t>After Hours Messaging (BVTM)</t>
         </is>
       </c>
-      <c r="B45" s="56">
+      <c r="B45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="C45" s="56">
+      <c r="C45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="D45" s="56">
+      <c r="D45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="E45" s="56">
+      <c r="E45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="F45" s="56">
+      <c r="F45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="G45" s="56">
+      <c r="G45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="H45" s="56">
+      <c r="H45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="I45" s="56">
+      <c r="I45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="J45" s="56">
+      <c r="J45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="K45" s="56">
+      <c r="K45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="L45" s="56">
+      <c r="L45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="M45" s="56">
+      <c r="M45" s="52">
         <f>Inputs!$B$94</f>
         <v/>
       </c>
-      <c r="N45" s="57">
+      <c r="N45" s="53">
         <f>Inputs!$B$94*12</f>
         <v/>
       </c>
-      <c r="O45" s="57">
+      <c r="O45" s="53">
         <f>Inputs!$B$94*12</f>
         <v/>
       </c>
-      <c r="P45" s="58">
+      <c r="P45" s="54">
         <f>SUM(B45:M45)+N45+O45</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="60" t="inlineStr">
+      <c r="A46" s="56" t="inlineStr">
         <is>
           <t>CFO / AP Support</t>
         </is>
       </c>
-      <c r="B46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M46" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N46" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O46" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P46" s="58">
+      <c r="B46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N46" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O46" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P46" s="54">
         <f>SUM(B46:M46)+N46+O46</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="60" t="inlineStr">
+      <c r="A47" s="56" t="inlineStr">
         <is>
           <t>Support Services</t>
         </is>
       </c>
-      <c r="B47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M47" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N47" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O47" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P47" s="58">
+      <c r="B47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N47" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O47" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P47" s="54">
         <f>SUM(B47:M47)+N47+O47</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="60" t="inlineStr">
+      <c r="A48" s="56" t="inlineStr">
         <is>
           <t>Messaging / CRG Signer</t>
         </is>
       </c>
-      <c r="B48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M48" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N48" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O48" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P48" s="58">
+      <c r="B48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N48" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O48" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P48" s="54">
         <f>SUM(B48:M48)+N48+O48</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="60" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>NM Room &amp; Board</t>
         </is>
       </c>
-      <c r="B49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M49" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N49" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O49" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P49" s="58">
+      <c r="B49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N49" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O49" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P49" s="54">
         <f>SUM(B49:M49)+N49+O49</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="60" t="inlineStr">
+      <c r="A50" s="56" t="inlineStr">
         <is>
           <t>Corporate Labor</t>
         </is>
       </c>
-      <c r="B50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M50" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N50" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O50" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P50" s="58">
+      <c r="B50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N50" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O50" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P50" s="54">
         <f>SUM(B50:M50)+N50+O50</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="60" t="inlineStr">
+      <c r="A51" s="56" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B51" s="56">
+      <c r="B51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="C51" s="56">
+      <c r="C51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="D51" s="56">
+      <c r="D51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="E51" s="56">
+      <c r="E51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="F51" s="56">
+      <c r="F51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="G51" s="56">
+      <c r="G51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="H51" s="56">
+      <c r="H51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="I51" s="56">
+      <c r="I51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="J51" s="56">
+      <c r="J51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="K51" s="56">
+      <c r="K51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="L51" s="56">
+      <c r="L51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="M51" s="56">
+      <c r="M51" s="52">
         <f>Inputs!$B$103</f>
         <v/>
       </c>
-      <c r="N51" s="57">
+      <c r="N51" s="53">
         <f>Inputs!$B$103*12</f>
         <v/>
       </c>
-      <c r="O51" s="57">
+      <c r="O51" s="53">
         <f>Inputs!$B$103*12</f>
         <v/>
       </c>
-      <c r="P51" s="58">
+      <c r="P51" s="54">
         <f>SUM(B51:M51)+N51+O51</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="60" t="inlineStr">
+      <c r="A52" s="56" t="inlineStr">
         <is>
           <t>Outsourced Billing Fee (1.5%)</t>
         </is>
       </c>
-      <c r="B52" s="56">
+      <c r="B52" s="52">
         <f>'Revenue Model'!C14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="C52" s="56">
+      <c r="C52" s="52">
         <f>'Revenue Model'!D14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="D52" s="56">
+      <c r="D52" s="52">
         <f>'Revenue Model'!E14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="E52" s="56">
+      <c r="E52" s="52">
         <f>'Revenue Model'!F14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="F52" s="56">
+      <c r="F52" s="52">
         <f>'Revenue Model'!G14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="G52" s="56">
+      <c r="G52" s="52">
         <f>'Revenue Model'!H14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="H52" s="56">
+      <c r="H52" s="52">
         <f>'Revenue Model'!I14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="I52" s="56">
+      <c r="I52" s="52">
         <f>'Revenue Model'!J14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="J52" s="56">
+      <c r="J52" s="52">
         <f>'Revenue Model'!K14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="K52" s="56">
+      <c r="K52" s="52">
         <f>'Revenue Model'!L14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="L52" s="56">
+      <c r="L52" s="52">
         <f>'Revenue Model'!M14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="M52" s="56">
+      <c r="M52" s="52">
         <f>'Revenue Model'!N14*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="N52" s="57">
+      <c r="N52" s="53">
         <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="O52" s="57">
+      <c r="O52" s="53">
         <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$106</f>
         <v/>
       </c>
-      <c r="P52" s="58">
+      <c r="P52" s="54">
         <f>SUM(B52:M52)+N52+O52</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="60" t="inlineStr">
+      <c r="A53" s="56" t="inlineStr">
         <is>
           <t>EMR System</t>
         </is>
       </c>
-      <c r="B53" s="56">
+      <c r="B53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="C53" s="56">
+      <c r="C53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="D53" s="56">
+      <c r="D53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="E53" s="56">
+      <c r="E53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="F53" s="56">
+      <c r="F53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="G53" s="56">
+      <c r="G53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="H53" s="56">
+      <c r="H53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="I53" s="56">
+      <c r="I53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="J53" s="56">
+      <c r="J53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="K53" s="56">
+      <c r="K53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="L53" s="56">
+      <c r="L53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="M53" s="56">
+      <c r="M53" s="52">
         <f>Inputs!$B$95</f>
         <v/>
       </c>
-      <c r="N53" s="57">
+      <c r="N53" s="53">
         <f>Inputs!$B$95*12</f>
         <v/>
       </c>
-      <c r="O53" s="57">
+      <c r="O53" s="53">
         <f>Inputs!$B$95*12</f>
         <v/>
       </c>
-      <c r="P53" s="58">
+      <c r="P53" s="54">
         <f>SUM(B53:M53)+N53+O53</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="60" t="inlineStr">
+      <c r="A54" s="56" t="inlineStr">
         <is>
           <t>Other EMR</t>
         </is>
       </c>
-      <c r="B54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M54" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N54" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O54" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P54" s="58">
+      <c r="B54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N54" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O54" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P54" s="54">
         <f>SUM(B54:M54)+N54+O54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="60" t="inlineStr">
+      <c r="A55" s="56" t="inlineStr">
         <is>
           <t>PCR (CPM)</t>
         </is>
       </c>
-      <c r="B55" s="56">
+      <c r="B55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="C55" s="56">
+      <c r="C55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="D55" s="56">
+      <c r="D55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="E55" s="56">
+      <c r="E55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="F55" s="56">
+      <c r="F55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="G55" s="56">
+      <c r="G55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="H55" s="56">
+      <c r="H55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="I55" s="56">
+      <c r="I55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="J55" s="56">
+      <c r="J55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="K55" s="56">
+      <c r="K55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="L55" s="56">
+      <c r="L55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="M55" s="56">
+      <c r="M55" s="52">
         <f>Inputs!$B$96</f>
         <v/>
       </c>
-      <c r="N55" s="57">
+      <c r="N55" s="53">
         <f>Inputs!$B$96*12</f>
         <v/>
       </c>
-      <c r="O55" s="57">
+      <c r="O55" s="53">
         <f>Inputs!$B$96*12</f>
         <v/>
       </c>
-      <c r="P55" s="58">
+      <c r="P55" s="54">
         <f>SUM(B55:M55)+N55+O55</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="60" t="inlineStr">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>Ancillary</t>
         </is>
       </c>
-      <c r="B56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M56" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N56" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O56" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P56" s="58">
+      <c r="B56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N56" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O56" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P56" s="54">
         <f>SUM(B56:M56)+N56+O56</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="60" t="inlineStr">
+      <c r="A57" s="56" t="inlineStr">
         <is>
           <t>Liability Insurance (D&amp;O)</t>
         </is>
       </c>
-      <c r="B57" s="56">
+      <c r="B57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="C57" s="56">
+      <c r="C57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="D57" s="56">
+      <c r="D57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="E57" s="56">
+      <c r="E57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="F57" s="56">
+      <c r="F57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="G57" s="56">
+      <c r="G57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="H57" s="56">
+      <c r="H57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="I57" s="56">
+      <c r="I57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="J57" s="56">
+      <c r="J57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="K57" s="56">
+      <c r="K57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="L57" s="56">
+      <c r="L57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="M57" s="56">
+      <c r="M57" s="52">
         <f>Inputs!$B$98</f>
         <v/>
       </c>
-      <c r="N57" s="57">
+      <c r="N57" s="53">
         <f>Inputs!$B$98*12</f>
         <v/>
       </c>
-      <c r="O57" s="57">
+      <c r="O57" s="53">
         <f>Inputs!$B$98*12</f>
         <v/>
       </c>
-      <c r="P57" s="58">
+      <c r="P57" s="54">
         <f>SUM(B57:M57)+N57+O57</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="60" t="inlineStr">
+      <c r="A58" s="56" t="inlineStr">
         <is>
           <t>QR Payment Fee (0.75%)</t>
         </is>
       </c>
-      <c r="B58" s="56">
+      <c r="B58" s="52">
         <f>'Revenue Model'!C14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="C58" s="56">
+      <c r="C58" s="52">
         <f>'Revenue Model'!D14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="D58" s="56">
+      <c r="D58" s="52">
         <f>'Revenue Model'!E14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="E58" s="56">
+      <c r="E58" s="52">
         <f>'Revenue Model'!F14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="F58" s="56">
+      <c r="F58" s="52">
         <f>'Revenue Model'!G14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="G58" s="56">
+      <c r="G58" s="52">
         <f>'Revenue Model'!H14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="H58" s="56">
+      <c r="H58" s="52">
         <f>'Revenue Model'!I14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="I58" s="56">
+      <c r="I58" s="52">
         <f>'Revenue Model'!J14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="J58" s="56">
+      <c r="J58" s="52">
         <f>'Revenue Model'!K14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="K58" s="56">
+      <c r="K58" s="52">
         <f>'Revenue Model'!L14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="L58" s="56">
+      <c r="L58" s="52">
         <f>'Revenue Model'!M14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="M58" s="56">
+      <c r="M58" s="52">
         <f>'Revenue Model'!N14*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="N58" s="57">
+      <c r="N58" s="53">
         <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="O58" s="57">
+      <c r="O58" s="53">
         <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$107</f>
         <v/>
       </c>
-      <c r="P58" s="58">
+      <c r="P58" s="54">
         <f>SUM(B58:M58)+N58+O58</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="60" t="inlineStr">
+      <c r="A59" s="56" t="inlineStr">
         <is>
           <t>Training / CEUs</t>
         </is>
       </c>
-      <c r="B59" s="56">
+      <c r="B59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="C59" s="56">
+      <c r="C59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="D59" s="56">
+      <c r="D59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="E59" s="56">
+      <c r="E59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="F59" s="56">
+      <c r="F59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="G59" s="56">
+      <c r="G59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="H59" s="56">
+      <c r="H59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="I59" s="56">
+      <c r="I59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="J59" s="56">
+      <c r="J59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="K59" s="56">
+      <c r="K59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="L59" s="56">
+      <c r="L59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="M59" s="56">
+      <c r="M59" s="52">
         <f>Inputs!$B$99</f>
         <v/>
       </c>
-      <c r="N59" s="57">
+      <c r="N59" s="53">
         <f>Inputs!$B$99*12</f>
         <v/>
       </c>
-      <c r="O59" s="57">
+      <c r="O59" s="53">
         <f>Inputs!$B$99*12</f>
         <v/>
       </c>
-      <c r="P59" s="58">
+      <c r="P59" s="54">
         <f>SUM(B59:M59)+N59+O59</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="60" t="inlineStr">
+      <c r="A60" s="56" t="inlineStr">
         <is>
           <t>Credit Card Fees</t>
         </is>
       </c>
-      <c r="B60" s="56">
+      <c r="B60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="C60" s="56">
+      <c r="C60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="D60" s="56">
+      <c r="D60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="E60" s="56">
+      <c r="E60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="F60" s="56">
+      <c r="F60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="G60" s="56">
+      <c r="G60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="H60" s="56">
+      <c r="H60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="I60" s="56">
+      <c r="I60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="J60" s="56">
+      <c r="J60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="K60" s="56">
+      <c r="K60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="L60" s="56">
+      <c r="L60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="M60" s="56">
+      <c r="M60" s="52">
         <f>Inputs!$B$97</f>
         <v/>
       </c>
-      <c r="N60" s="57">
+      <c r="N60" s="53">
         <f>Inputs!$B$97*12</f>
         <v/>
       </c>
-      <c r="O60" s="57">
+      <c r="O60" s="53">
         <f>Inputs!$B$97*12</f>
         <v/>
       </c>
-      <c r="P60" s="58">
+      <c r="P60" s="54">
         <f>SUM(B60:M60)+N60+O60</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="60" t="inlineStr">
+      <c r="A61" s="56" t="inlineStr">
         <is>
           <t>Other (QPf)</t>
         </is>
       </c>
-      <c r="B61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M61" s="56">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N61" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O61" s="57">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P61" s="58">
+      <c r="B61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N61" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O61" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P61" s="54">
         <f>SUM(B61:M61)+N61+O61</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="60" t="inlineStr">
+      <c r="A62" s="56" t="inlineStr">
         <is>
           <t>Other (Client)</t>
         </is>
       </c>
-      <c r="B62" s="56">
+      <c r="B62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="C62" s="56">
+      <c r="C62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="D62" s="56">
+      <c r="D62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="E62" s="56">
+      <c r="E62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="F62" s="56">
+      <c r="F62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="G62" s="56">
+      <c r="G62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="H62" s="56">
+      <c r="H62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="I62" s="56">
+      <c r="I62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="J62" s="56">
+      <c r="J62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="K62" s="56">
+      <c r="K62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="L62" s="56">
+      <c r="L62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="M62" s="56">
+      <c r="M62" s="52">
         <f>Inputs!$B$100</f>
         <v/>
       </c>
-      <c r="N62" s="57">
+      <c r="N62" s="53">
         <f>Inputs!$B$100*12</f>
         <v/>
       </c>
-      <c r="O62" s="57">
+      <c r="O62" s="53">
         <f>Inputs!$B$100*12</f>
         <v/>
       </c>
-      <c r="P62" s="58">
+      <c r="P62" s="54">
         <f>SUM(B62:M62)+N62+O62</f>
         <v/>
       </c>
@@ -20352,63 +19744,63 @@
           <t>Total General &amp; Administrative</t>
         </is>
       </c>
-      <c r="B63" s="59">
+      <c r="B63" s="55">
         <f>SUM(B40:B62)</f>
         <v/>
       </c>
-      <c r="C63" s="59">
+      <c r="C63" s="55">
         <f>SUM(C40:C62)</f>
         <v/>
       </c>
-      <c r="D63" s="59">
+      <c r="D63" s="55">
         <f>SUM(D40:D62)</f>
         <v/>
       </c>
-      <c r="E63" s="59">
+      <c r="E63" s="55">
         <f>SUM(E40:E62)</f>
         <v/>
       </c>
-      <c r="F63" s="59">
+      <c r="F63" s="55">
         <f>SUM(F40:F62)</f>
         <v/>
       </c>
-      <c r="G63" s="59">
+      <c r="G63" s="55">
         <f>SUM(G40:G62)</f>
         <v/>
       </c>
-      <c r="H63" s="59">
+      <c r="H63" s="55">
         <f>SUM(H40:H62)</f>
         <v/>
       </c>
-      <c r="I63" s="59">
+      <c r="I63" s="55">
         <f>SUM(I40:I62)</f>
         <v/>
       </c>
-      <c r="J63" s="59">
+      <c r="J63" s="55">
         <f>SUM(J40:J62)</f>
         <v/>
       </c>
-      <c r="K63" s="59">
+      <c r="K63" s="55">
         <f>SUM(K40:K62)</f>
         <v/>
       </c>
-      <c r="L63" s="59">
+      <c r="L63" s="55">
         <f>SUM(L40:L62)</f>
         <v/>
       </c>
-      <c r="M63" s="59">
+      <c r="M63" s="55">
         <f>SUM(M40:M62)</f>
         <v/>
       </c>
-      <c r="N63" s="59">
+      <c r="N63" s="55">
         <f>SUM(N40:N62)</f>
         <v/>
       </c>
-      <c r="O63" s="59">
+      <c r="O63" s="55">
         <f>SUM(O40:O62)</f>
         <v/>
       </c>
-      <c r="P63" s="59">
+      <c r="P63" s="55">
         <f>SUM(P40:P62)</f>
         <v/>
       </c>
@@ -20419,63 +19811,63 @@
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B65" s="59">
+      <c r="B65" s="55">
         <f>B37+B63</f>
         <v/>
       </c>
-      <c r="C65" s="59">
+      <c r="C65" s="55">
         <f>C37+C63</f>
         <v/>
       </c>
-      <c r="D65" s="59">
+      <c r="D65" s="55">
         <f>D37+D63</f>
         <v/>
       </c>
-      <c r="E65" s="59">
+      <c r="E65" s="55">
         <f>E37+E63</f>
         <v/>
       </c>
-      <c r="F65" s="59">
+      <c r="F65" s="55">
         <f>F37+F63</f>
         <v/>
       </c>
-      <c r="G65" s="59">
+      <c r="G65" s="55">
         <f>G37+G63</f>
         <v/>
       </c>
-      <c r="H65" s="59">
+      <c r="H65" s="55">
         <f>H37+H63</f>
         <v/>
       </c>
-      <c r="I65" s="59">
+      <c r="I65" s="55">
         <f>I37+I63</f>
         <v/>
       </c>
-      <c r="J65" s="59">
+      <c r="J65" s="55">
         <f>J37+J63</f>
         <v/>
       </c>
-      <c r="K65" s="59">
+      <c r="K65" s="55">
         <f>K37+K63</f>
         <v/>
       </c>
-      <c r="L65" s="59">
+      <c r="L65" s="55">
         <f>L37+L63</f>
         <v/>
       </c>
-      <c r="M65" s="59">
+      <c r="M65" s="55">
         <f>M37+M63</f>
         <v/>
       </c>
-      <c r="N65" s="59">
+      <c r="N65" s="55">
         <f>N37+N63</f>
         <v/>
       </c>
-      <c r="O65" s="59">
+      <c r="O65" s="55">
         <f>O37+O63</f>
         <v/>
       </c>
-      <c r="P65" s="59">
+      <c r="P65" s="55">
         <f>P37+P63</f>
         <v/>
       </c>
@@ -20486,63 +19878,63 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B67" s="61">
+      <c r="B67" s="57">
         <f>B24-B65</f>
         <v/>
       </c>
-      <c r="C67" s="61">
+      <c r="C67" s="57">
         <f>C24-C65</f>
         <v/>
       </c>
-      <c r="D67" s="61">
+      <c r="D67" s="57">
         <f>D24-D65</f>
         <v/>
       </c>
-      <c r="E67" s="61">
+      <c r="E67" s="57">
         <f>E24-E65</f>
         <v/>
       </c>
-      <c r="F67" s="61">
+      <c r="F67" s="57">
         <f>F24-F65</f>
         <v/>
       </c>
-      <c r="G67" s="61">
+      <c r="G67" s="57">
         <f>G24-G65</f>
         <v/>
       </c>
-      <c r="H67" s="61">
+      <c r="H67" s="57">
         <f>H24-H65</f>
         <v/>
       </c>
-      <c r="I67" s="61">
+      <c r="I67" s="57">
         <f>I24-I65</f>
         <v/>
       </c>
-      <c r="J67" s="61">
+      <c r="J67" s="57">
         <f>J24-J65</f>
         <v/>
       </c>
-      <c r="K67" s="61">
+      <c r="K67" s="57">
         <f>K24-K65</f>
         <v/>
       </c>
-      <c r="L67" s="61">
+      <c r="L67" s="57">
         <f>L24-L65</f>
         <v/>
       </c>
-      <c r="M67" s="61">
+      <c r="M67" s="57">
         <f>M24-M65</f>
         <v/>
       </c>
-      <c r="N67" s="61">
+      <c r="N67" s="57">
         <f>N24-N65</f>
         <v/>
       </c>
-      <c r="O67" s="61">
+      <c r="O67" s="57">
         <f>O24-O65</f>
         <v/>
       </c>
-      <c r="P67" s="61">
+      <c r="P67" s="57">
         <f>P24-P65</f>
         <v/>
       </c>

--- a/sba_application/09_financial_model/Azalea_Hospice_Investor_Package.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_Investor_Package.xlsx
@@ -12,13 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investor Position" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Economics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVI Upside" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="rhc_tier1">Inputs!$B$5</definedName>
@@ -393,6 +394,9 @@
     <xf numFmtId="169" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -410,9 +414,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1369,6 +1370,21 @@
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
+        <t>Sustained incremental census from MVI 'Perfect Visit' certification + the national campaign. Illustrative only - not used for underwriting.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Azalea Hospice</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
         <t>Source: Paloma P&amp;L 2025.</t>
       </text>
     </comment>
@@ -3708,6 +3724,3667 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12.5" customWidth="1" min="2" max="2"/>
+    <col width="12.5" customWidth="1" min="3" max="3"/>
+    <col width="12.5" customWidth="1" min="4" max="4"/>
+    <col width="12.5" customWidth="1" min="5" max="5"/>
+    <col width="12.5" customWidth="1" min="6" max="6"/>
+    <col width="12.5" customWidth="1" min="7" max="7"/>
+    <col width="12.5" customWidth="1" min="8" max="8"/>
+    <col width="12.5" customWidth="1" min="9" max="9"/>
+    <col width="12.5" customWidth="1" min="10" max="10"/>
+    <col width="12.5" customWidth="1" min="11" max="11"/>
+    <col width="12.5" customWidth="1" min="12" max="12"/>
+    <col width="12.5" customWidth="1" min="13" max="13"/>
+    <col width="12.5" customWidth="1" min="14" max="14"/>
+    <col width="12.5" customWidth="1" min="15" max="15"/>
+    <col width="12.5" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>Azalea Hospice &amp; Palliative Care - Tyler, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="50" t="inlineStr">
+        <is>
+          <t>Profit and Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Year 1 (monthly) | Years 2-3 (annual) | model data, cash basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="H5" s="51" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="I5" s="51" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="J5" s="51" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="K5" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="L5" s="51" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="M5" s="51" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="N5" s="51" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="O5" s="51" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="P5" s="51" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Gross Billed Revenue</t>
+        </is>
+      </c>
+      <c r="B7" s="52">
+        <f>'Revenue Model'!C14</f>
+        <v/>
+      </c>
+      <c r="C7" s="52">
+        <f>'Revenue Model'!D14</f>
+        <v/>
+      </c>
+      <c r="D7" s="52">
+        <f>'Revenue Model'!E14</f>
+        <v/>
+      </c>
+      <c r="E7" s="52">
+        <f>'Revenue Model'!F14</f>
+        <v/>
+      </c>
+      <c r="F7" s="52">
+        <f>'Revenue Model'!G14</f>
+        <v/>
+      </c>
+      <c r="G7" s="52">
+        <f>'Revenue Model'!H14</f>
+        <v/>
+      </c>
+      <c r="H7" s="52">
+        <f>'Revenue Model'!I14</f>
+        <v/>
+      </c>
+      <c r="I7" s="52">
+        <f>'Revenue Model'!J14</f>
+        <v/>
+      </c>
+      <c r="J7" s="52">
+        <f>'Revenue Model'!K14</f>
+        <v/>
+      </c>
+      <c r="K7" s="52">
+        <f>'Revenue Model'!L14</f>
+        <v/>
+      </c>
+      <c r="L7" s="52">
+        <f>'Revenue Model'!M14</f>
+        <v/>
+      </c>
+      <c r="M7" s="52">
+        <f>'Revenue Model'!N14</f>
+        <v/>
+      </c>
+      <c r="N7" s="53">
+        <f>SUM('Revenue Model'!O14:R14)</f>
+        <v/>
+      </c>
+      <c r="O7" s="53">
+        <f>SUM('Revenue Model'!S14:V14)</f>
+        <v/>
+      </c>
+      <c r="P7" s="54">
+        <f>SUM(B7:M7)+N7+O7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Less: CDAs Adjustment</t>
+        </is>
+      </c>
+      <c r="B8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M8" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N8" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O8" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P8" s="54">
+        <f>SUM(B8:M8)+N8+O8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Less: Net Due Zero (Write-offs)</t>
+        </is>
+      </c>
+      <c r="B9" s="52">
+        <f>'Revenue Model'!C14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="C9" s="52">
+        <f>'Revenue Model'!D14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="D9" s="52">
+        <f>'Revenue Model'!E14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="E9" s="52">
+        <f>'Revenue Model'!F14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="F9" s="52">
+        <f>'Revenue Model'!G14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="G9" s="52">
+        <f>'Revenue Model'!H14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="H9" s="52">
+        <f>'Revenue Model'!I14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="I9" s="52">
+        <f>'Revenue Model'!J14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="J9" s="52">
+        <f>'Revenue Model'!K14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="K9" s="52">
+        <f>'Revenue Model'!L14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="L9" s="52">
+        <f>'Revenue Model'!M14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="M9" s="52">
+        <f>'Revenue Model'!N14*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="N9" s="53">
+        <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="O9" s="53">
+        <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$11</f>
+        <v/>
+      </c>
+      <c r="P9" s="54">
+        <f>SUM(B9:M9)+N9+O9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Less: Sequestration</t>
+        </is>
+      </c>
+      <c r="B10" s="52">
+        <f>'Revenue Model'!C14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="C10" s="52">
+        <f>'Revenue Model'!D14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="D10" s="52">
+        <f>'Revenue Model'!E14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="E10" s="52">
+        <f>'Revenue Model'!F14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="F10" s="52">
+        <f>'Revenue Model'!G14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="G10" s="52">
+        <f>'Revenue Model'!H14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="H10" s="52">
+        <f>'Revenue Model'!I14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="I10" s="52">
+        <f>'Revenue Model'!J14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="J10" s="52">
+        <f>'Revenue Model'!K14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="K10" s="52">
+        <f>'Revenue Model'!L14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="L10" s="52">
+        <f>'Revenue Model'!M14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="M10" s="52">
+        <f>'Revenue Model'!N14*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="N10" s="53">
+        <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="O10" s="53">
+        <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$10</f>
+        <v/>
+      </c>
+      <c r="P10" s="54">
+        <f>SUM(B10:M10)+N10+O10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Less: Medication Adjustments</t>
+        </is>
+      </c>
+      <c r="B11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M11" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N11" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O11" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P11" s="54">
+        <f>SUM(B11:M11)+N11+O11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B12" s="55">
+        <f>B7-B8-B9-B10-B11</f>
+        <v/>
+      </c>
+      <c r="C12" s="55">
+        <f>C7-C8-C9-C10-C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="55">
+        <f>D7-D8-D9-D10-D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="55">
+        <f>E7-E8-E9-E10-E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="55">
+        <f>F7-F8-F9-F10-F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="55">
+        <f>G7-G8-G9-G10-G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="55">
+        <f>H7-H8-H9-H10-H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="55">
+        <f>I7-I8-I9-I10-I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="55">
+        <f>J7-J8-J9-J10-J11</f>
+        <v/>
+      </c>
+      <c r="K12" s="55">
+        <f>K7-K8-K9-K10-K11</f>
+        <v/>
+      </c>
+      <c r="L12" s="55">
+        <f>L7-L8-L9-L10-L11</f>
+        <v/>
+      </c>
+      <c r="M12" s="55">
+        <f>M7-M8-M9-M10-M11</f>
+        <v/>
+      </c>
+      <c r="N12" s="55">
+        <f>N7-N8-N9-N10-N11</f>
+        <v/>
+      </c>
+      <c r="O12" s="55">
+        <f>O7-O8-O9-O10-O11</f>
+        <v/>
+      </c>
+      <c r="P12" s="55">
+        <f>P7-P8-P9-P10-P11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Cost of Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="B15" s="52">
+        <f>'Revenue Model'!C12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="C15" s="52">
+        <f>'Revenue Model'!D12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="D15" s="52">
+        <f>'Revenue Model'!E12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="E15" s="52">
+        <f>'Revenue Model'!F12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="F15" s="52">
+        <f>'Revenue Model'!G12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="G15" s="52">
+        <f>'Revenue Model'!H12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="H15" s="52">
+        <f>'Revenue Model'!I12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="I15" s="52">
+        <f>'Revenue Model'!J12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="J15" s="52">
+        <f>'Revenue Model'!K12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="K15" s="52">
+        <f>'Revenue Model'!L12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="L15" s="52">
+        <f>'Revenue Model'!M12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="M15" s="52">
+        <f>'Revenue Model'!N12*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="N15" s="53">
+        <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="O15" s="53">
+        <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$88</f>
+        <v/>
+      </c>
+      <c r="P15" s="54">
+        <f>SUM(B15:M15)+N15+O15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Medical Supplies</t>
+        </is>
+      </c>
+      <c r="B16" s="52">
+        <f>'Revenue Model'!C12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="C16" s="52">
+        <f>'Revenue Model'!D12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="D16" s="52">
+        <f>'Revenue Model'!E12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="E16" s="52">
+        <f>'Revenue Model'!F12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="F16" s="52">
+        <f>'Revenue Model'!G12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="G16" s="52">
+        <f>'Revenue Model'!H12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="H16" s="52">
+        <f>'Revenue Model'!I12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="I16" s="52">
+        <f>'Revenue Model'!J12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="J16" s="52">
+        <f>'Revenue Model'!K12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="K16" s="52">
+        <f>'Revenue Model'!L12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="L16" s="52">
+        <f>'Revenue Model'!M12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="M16" s="52">
+        <f>'Revenue Model'!N12*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="N16" s="53">
+        <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="O16" s="53">
+        <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="P16" s="54">
+        <f>SUM(B16:M16)+N16+O16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Durable Medical Equipment (DME)</t>
+        </is>
+      </c>
+      <c r="B17" s="52">
+        <f>'Revenue Model'!C12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="C17" s="52">
+        <f>'Revenue Model'!D12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="D17" s="52">
+        <f>'Revenue Model'!E12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="E17" s="52">
+        <f>'Revenue Model'!F12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="F17" s="52">
+        <f>'Revenue Model'!G12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="G17" s="52">
+        <f>'Revenue Model'!H12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="H17" s="52">
+        <f>'Revenue Model'!I12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="I17" s="52">
+        <f>'Revenue Model'!J12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="J17" s="52">
+        <f>'Revenue Model'!K12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="K17" s="52">
+        <f>'Revenue Model'!L12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="L17" s="52">
+        <f>'Revenue Model'!M12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="M17" s="52">
+        <f>'Revenue Model'!N12*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="N17" s="53">
+        <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="O17" s="53">
+        <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$87</f>
+        <v/>
+      </c>
+      <c r="P17" s="54">
+        <f>SUM(B17:M17)+N17+O17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Respite Care</t>
+        </is>
+      </c>
+      <c r="B18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M18" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N18" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O18" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P18" s="54">
+        <f>SUM(B18:M18)+N18+O18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="B19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M19" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N19" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O19" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P19" s="54">
+        <f>SUM(B19:M19)+N19+O19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Infusion / Labs</t>
+        </is>
+      </c>
+      <c r="B20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M20" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N20" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O20" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P20" s="54">
+        <f>SUM(B20:M20)+N20+O20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PT / OT / ST</t>
+        </is>
+      </c>
+      <c r="B21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M21" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N21" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O21" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P21" s="54">
+        <f>SUM(B21:M21)+N21+O21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Total Cost of Services</t>
+        </is>
+      </c>
+      <c r="B22" s="55">
+        <f>SUM(B15:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="55">
+        <f>SUM(C15:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="55">
+        <f>SUM(D15:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="55">
+        <f>SUM(E15:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="55">
+        <f>SUM(F15:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="55">
+        <f>SUM(G15:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="55">
+        <f>SUM(H15:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="55">
+        <f>SUM(I15:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="55">
+        <f>SUM(J15:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="55">
+        <f>SUM(K15:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="55">
+        <f>SUM(L15:L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="55">
+        <f>SUM(M15:M21)</f>
+        <v/>
+      </c>
+      <c r="N22" s="55">
+        <f>SUM(N15:N21)</f>
+        <v/>
+      </c>
+      <c r="O22" s="55">
+        <f>SUM(O15:O21)</f>
+        <v/>
+      </c>
+      <c r="P22" s="55">
+        <f>SUM(P15:P21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B24" s="55">
+        <f>B12-B22</f>
+        <v/>
+      </c>
+      <c r="C24" s="55">
+        <f>C12-C22</f>
+        <v/>
+      </c>
+      <c r="D24" s="55">
+        <f>D12-D22</f>
+        <v/>
+      </c>
+      <c r="E24" s="55">
+        <f>E12-E22</f>
+        <v/>
+      </c>
+      <c r="F24" s="55">
+        <f>F12-F22</f>
+        <v/>
+      </c>
+      <c r="G24" s="55">
+        <f>G12-G22</f>
+        <v/>
+      </c>
+      <c r="H24" s="55">
+        <f>H12-H22</f>
+        <v/>
+      </c>
+      <c r="I24" s="55">
+        <f>I12-I22</f>
+        <v/>
+      </c>
+      <c r="J24" s="55">
+        <f>J12-J22</f>
+        <v/>
+      </c>
+      <c r="K24" s="55">
+        <f>K12-K22</f>
+        <v/>
+      </c>
+      <c r="L24" s="55">
+        <f>L12-L22</f>
+        <v/>
+      </c>
+      <c r="M24" s="55">
+        <f>M12-M22</f>
+        <v/>
+      </c>
+      <c r="N24" s="55">
+        <f>N12-N22</f>
+        <v/>
+      </c>
+      <c r="O24" s="55">
+        <f>O12-O22</f>
+        <v/>
+      </c>
+      <c r="P24" s="55">
+        <f>P12-P22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="56" t="inlineStr">
+        <is>
+          <t>Payroll - 1st Half</t>
+        </is>
+      </c>
+      <c r="B28" s="52">
+        <f>('Staffing &amp; Payroll'!C30+'Staffing &amp; Payroll'!C42+'Staffing &amp; Payroll'!C38+'Staffing &amp; Payroll'!C43)/2</f>
+        <v/>
+      </c>
+      <c r="C28" s="52">
+        <f>('Staffing &amp; Payroll'!D30+'Staffing &amp; Payroll'!D42+'Staffing &amp; Payroll'!D38+'Staffing &amp; Payroll'!D43)/2</f>
+        <v/>
+      </c>
+      <c r="D28" s="52">
+        <f>('Staffing &amp; Payroll'!E30+'Staffing &amp; Payroll'!E42+'Staffing &amp; Payroll'!E38+'Staffing &amp; Payroll'!E43)/2</f>
+        <v/>
+      </c>
+      <c r="E28" s="52">
+        <f>('Staffing &amp; Payroll'!F30+'Staffing &amp; Payroll'!F42+'Staffing &amp; Payroll'!F38+'Staffing &amp; Payroll'!F43)/2</f>
+        <v/>
+      </c>
+      <c r="F28" s="52">
+        <f>('Staffing &amp; Payroll'!G30+'Staffing &amp; Payroll'!G42+'Staffing &amp; Payroll'!G38+'Staffing &amp; Payroll'!G43)/2</f>
+        <v/>
+      </c>
+      <c r="G28" s="52">
+        <f>('Staffing &amp; Payroll'!H30+'Staffing &amp; Payroll'!H42+'Staffing &amp; Payroll'!H38+'Staffing &amp; Payroll'!H43)/2</f>
+        <v/>
+      </c>
+      <c r="H28" s="52">
+        <f>('Staffing &amp; Payroll'!I30+'Staffing &amp; Payroll'!I42+'Staffing &amp; Payroll'!I38+'Staffing &amp; Payroll'!I43)/2</f>
+        <v/>
+      </c>
+      <c r="I28" s="52">
+        <f>('Staffing &amp; Payroll'!J30+'Staffing &amp; Payroll'!J42+'Staffing &amp; Payroll'!J38+'Staffing &amp; Payroll'!J43)/2</f>
+        <v/>
+      </c>
+      <c r="J28" s="52">
+        <f>('Staffing &amp; Payroll'!K30+'Staffing &amp; Payroll'!K42+'Staffing &amp; Payroll'!K38+'Staffing &amp; Payroll'!K43)/2</f>
+        <v/>
+      </c>
+      <c r="K28" s="52">
+        <f>('Staffing &amp; Payroll'!L30+'Staffing &amp; Payroll'!L42+'Staffing &amp; Payroll'!L38+'Staffing &amp; Payroll'!L43)/2</f>
+        <v/>
+      </c>
+      <c r="L28" s="52">
+        <f>('Staffing &amp; Payroll'!M30+'Staffing &amp; Payroll'!M42+'Staffing &amp; Payroll'!M38+'Staffing &amp; Payroll'!M43)/2</f>
+        <v/>
+      </c>
+      <c r="M28" s="52">
+        <f>('Staffing &amp; Payroll'!N30+'Staffing &amp; Payroll'!N42+'Staffing &amp; Payroll'!N38+'Staffing &amp; Payroll'!N43)/2</f>
+        <v/>
+      </c>
+      <c r="N28" s="53">
+        <f>(SUM('Staffing &amp; Payroll'!O30:R30)+SUM('Staffing &amp; Payroll'!O42:R42)+SUM('Staffing &amp; Payroll'!O38:R38)+SUM('Staffing &amp; Payroll'!O43:R43))/2</f>
+        <v/>
+      </c>
+      <c r="O28" s="53">
+        <f>(SUM('Staffing &amp; Payroll'!S30:V30)+SUM('Staffing &amp; Payroll'!S42:V42)+SUM('Staffing &amp; Payroll'!S38:V38)+SUM('Staffing &amp; Payroll'!S43:V43))/2</f>
+        <v/>
+      </c>
+      <c r="P28" s="54">
+        <f>SUM(B28:M28)+N28+O28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="56" t="inlineStr">
+        <is>
+          <t>Payroll - 2nd Half</t>
+        </is>
+      </c>
+      <c r="B29" s="52">
+        <f>('Staffing &amp; Payroll'!C30+'Staffing &amp; Payroll'!C42+'Staffing &amp; Payroll'!C38+'Staffing &amp; Payroll'!C43)/2</f>
+        <v/>
+      </c>
+      <c r="C29" s="52">
+        <f>('Staffing &amp; Payroll'!D30+'Staffing &amp; Payroll'!D42+'Staffing &amp; Payroll'!D38+'Staffing &amp; Payroll'!D43)/2</f>
+        <v/>
+      </c>
+      <c r="D29" s="52">
+        <f>('Staffing &amp; Payroll'!E30+'Staffing &amp; Payroll'!E42+'Staffing &amp; Payroll'!E38+'Staffing &amp; Payroll'!E43)/2</f>
+        <v/>
+      </c>
+      <c r="E29" s="52">
+        <f>('Staffing &amp; Payroll'!F30+'Staffing &amp; Payroll'!F42+'Staffing &amp; Payroll'!F38+'Staffing &amp; Payroll'!F43)/2</f>
+        <v/>
+      </c>
+      <c r="F29" s="52">
+        <f>('Staffing &amp; Payroll'!G30+'Staffing &amp; Payroll'!G42+'Staffing &amp; Payroll'!G38+'Staffing &amp; Payroll'!G43)/2</f>
+        <v/>
+      </c>
+      <c r="G29" s="52">
+        <f>('Staffing &amp; Payroll'!H30+'Staffing &amp; Payroll'!H42+'Staffing &amp; Payroll'!H38+'Staffing &amp; Payroll'!H43)/2</f>
+        <v/>
+      </c>
+      <c r="H29" s="52">
+        <f>('Staffing &amp; Payroll'!I30+'Staffing &amp; Payroll'!I42+'Staffing &amp; Payroll'!I38+'Staffing &amp; Payroll'!I43)/2</f>
+        <v/>
+      </c>
+      <c r="I29" s="52">
+        <f>('Staffing &amp; Payroll'!J30+'Staffing &amp; Payroll'!J42+'Staffing &amp; Payroll'!J38+'Staffing &amp; Payroll'!J43)/2</f>
+        <v/>
+      </c>
+      <c r="J29" s="52">
+        <f>('Staffing &amp; Payroll'!K30+'Staffing &amp; Payroll'!K42+'Staffing &amp; Payroll'!K38+'Staffing &amp; Payroll'!K43)/2</f>
+        <v/>
+      </c>
+      <c r="K29" s="52">
+        <f>('Staffing &amp; Payroll'!L30+'Staffing &amp; Payroll'!L42+'Staffing &amp; Payroll'!L38+'Staffing &amp; Payroll'!L43)/2</f>
+        <v/>
+      </c>
+      <c r="L29" s="52">
+        <f>('Staffing &amp; Payroll'!M30+'Staffing &amp; Payroll'!M42+'Staffing &amp; Payroll'!M38+'Staffing &amp; Payroll'!M43)/2</f>
+        <v/>
+      </c>
+      <c r="M29" s="52">
+        <f>('Staffing &amp; Payroll'!N30+'Staffing &amp; Payroll'!N42+'Staffing &amp; Payroll'!N38+'Staffing &amp; Payroll'!N43)/2</f>
+        <v/>
+      </c>
+      <c r="N29" s="53">
+        <f>(SUM('Staffing &amp; Payroll'!O30:R30)+SUM('Staffing &amp; Payroll'!O42:R42)+SUM('Staffing &amp; Payroll'!O38:R38)+SUM('Staffing &amp; Payroll'!O43:R43))/2</f>
+        <v/>
+      </c>
+      <c r="O29" s="53">
+        <f>(SUM('Staffing &amp; Payroll'!S30:V30)+SUM('Staffing &amp; Payroll'!S42:V42)+SUM('Staffing &amp; Payroll'!S38:V38)+SUM('Staffing &amp; Payroll'!S43:V43))/2</f>
+        <v/>
+      </c>
+      <c r="P29" s="54">
+        <f>SUM(B29:M29)+N29+O29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="56" t="inlineStr">
+        <is>
+          <t>Payroll YTD Adjustments</t>
+        </is>
+      </c>
+      <c r="B30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M30" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N30" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O30" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P30" s="54">
+        <f>SUM(B30:M30)+N30+O30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="56" t="inlineStr">
+        <is>
+          <t>Employer Taxes (FUTA/SUI/FICA/WC)</t>
+        </is>
+      </c>
+      <c r="B31" s="52">
+        <f>'Staffing &amp; Payroll'!C48+'Staffing &amp; Payroll'!C49</f>
+        <v/>
+      </c>
+      <c r="C31" s="52">
+        <f>'Staffing &amp; Payroll'!D48+'Staffing &amp; Payroll'!D49</f>
+        <v/>
+      </c>
+      <c r="D31" s="52">
+        <f>'Staffing &amp; Payroll'!E48+'Staffing &amp; Payroll'!E49</f>
+        <v/>
+      </c>
+      <c r="E31" s="52">
+        <f>'Staffing &amp; Payroll'!F48+'Staffing &amp; Payroll'!F49</f>
+        <v/>
+      </c>
+      <c r="F31" s="52">
+        <f>'Staffing &amp; Payroll'!G48+'Staffing &amp; Payroll'!G49</f>
+        <v/>
+      </c>
+      <c r="G31" s="52">
+        <f>'Staffing &amp; Payroll'!H48+'Staffing &amp; Payroll'!H49</f>
+        <v/>
+      </c>
+      <c r="H31" s="52">
+        <f>'Staffing &amp; Payroll'!I48+'Staffing &amp; Payroll'!I49</f>
+        <v/>
+      </c>
+      <c r="I31" s="52">
+        <f>'Staffing &amp; Payroll'!J48+'Staffing &amp; Payroll'!J49</f>
+        <v/>
+      </c>
+      <c r="J31" s="52">
+        <f>'Staffing &amp; Payroll'!K48+'Staffing &amp; Payroll'!K49</f>
+        <v/>
+      </c>
+      <c r="K31" s="52">
+        <f>'Staffing &amp; Payroll'!L48+'Staffing &amp; Payroll'!L49</f>
+        <v/>
+      </c>
+      <c r="L31" s="52">
+        <f>'Staffing &amp; Payroll'!M48+'Staffing &amp; Payroll'!M49</f>
+        <v/>
+      </c>
+      <c r="M31" s="52">
+        <f>'Staffing &amp; Payroll'!N48+'Staffing &amp; Payroll'!N49</f>
+        <v/>
+      </c>
+      <c r="N31" s="53">
+        <f>SUM('Staffing &amp; Payroll'!O48:R48)+SUM('Staffing &amp; Payroll'!O49:R49)</f>
+        <v/>
+      </c>
+      <c r="O31" s="53">
+        <f>SUM('Staffing &amp; Payroll'!S48:V48)+SUM('Staffing &amp; Payroll'!S49:V49)</f>
+        <v/>
+      </c>
+      <c r="P31" s="54">
+        <f>SUM(B31:M31)+N31+O31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="56" t="inlineStr">
+        <is>
+          <t>Contract Labor</t>
+        </is>
+      </c>
+      <c r="B32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M32" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N32" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O32" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P32" s="54">
+        <f>SUM(B32:M32)+N32+O32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="56" t="inlineStr">
+        <is>
+          <t>Medical Director</t>
+        </is>
+      </c>
+      <c r="B33" s="52">
+        <f>'Staffing &amp; Payroll'!C39</f>
+        <v/>
+      </c>
+      <c r="C33" s="52">
+        <f>'Staffing &amp; Payroll'!D39</f>
+        <v/>
+      </c>
+      <c r="D33" s="52">
+        <f>'Staffing &amp; Payroll'!E39</f>
+        <v/>
+      </c>
+      <c r="E33" s="52">
+        <f>'Staffing &amp; Payroll'!F39</f>
+        <v/>
+      </c>
+      <c r="F33" s="52">
+        <f>'Staffing &amp; Payroll'!G39</f>
+        <v/>
+      </c>
+      <c r="G33" s="52">
+        <f>'Staffing &amp; Payroll'!H39</f>
+        <v/>
+      </c>
+      <c r="H33" s="52">
+        <f>'Staffing &amp; Payroll'!I39</f>
+        <v/>
+      </c>
+      <c r="I33" s="52">
+        <f>'Staffing &amp; Payroll'!J39</f>
+        <v/>
+      </c>
+      <c r="J33" s="52">
+        <f>'Staffing &amp; Payroll'!K39</f>
+        <v/>
+      </c>
+      <c r="K33" s="52">
+        <f>'Staffing &amp; Payroll'!L39</f>
+        <v/>
+      </c>
+      <c r="L33" s="52">
+        <f>'Staffing &amp; Payroll'!M39</f>
+        <v/>
+      </c>
+      <c r="M33" s="52">
+        <f>'Staffing &amp; Payroll'!N39</f>
+        <v/>
+      </c>
+      <c r="N33" s="53">
+        <f>SUM('Staffing &amp; Payroll'!O39:R39)</f>
+        <v/>
+      </c>
+      <c r="O33" s="53">
+        <f>SUM('Staffing &amp; Payroll'!S39:V39)</f>
+        <v/>
+      </c>
+      <c r="P33" s="54">
+        <f>SUM(B33:M33)+N33+O33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>Medical Director 2</t>
+        </is>
+      </c>
+      <c r="B34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M34" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N34" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O34" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P34" s="54">
+        <f>SUM(B34:M34)+N34+O34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>Intercompany Transfer</t>
+        </is>
+      </c>
+      <c r="B35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M35" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N35" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O35" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P35" s="54">
+        <f>SUM(B35:M35)+N35+O35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>Staff Other (health insurance)</t>
+        </is>
+      </c>
+      <c r="B36" s="52">
+        <f>'Staffing &amp; Payroll'!C50+'Staffing &amp; Payroll'!C51</f>
+        <v/>
+      </c>
+      <c r="C36" s="52">
+        <f>'Staffing &amp; Payroll'!D50+'Staffing &amp; Payroll'!D51</f>
+        <v/>
+      </c>
+      <c r="D36" s="52">
+        <f>'Staffing &amp; Payroll'!E50+'Staffing &amp; Payroll'!E51</f>
+        <v/>
+      </c>
+      <c r="E36" s="52">
+        <f>'Staffing &amp; Payroll'!F50+'Staffing &amp; Payroll'!F51</f>
+        <v/>
+      </c>
+      <c r="F36" s="52">
+        <f>'Staffing &amp; Payroll'!G50+'Staffing &amp; Payroll'!G51</f>
+        <v/>
+      </c>
+      <c r="G36" s="52">
+        <f>'Staffing &amp; Payroll'!H50+'Staffing &amp; Payroll'!H51</f>
+        <v/>
+      </c>
+      <c r="H36" s="52">
+        <f>'Staffing &amp; Payroll'!I50+'Staffing &amp; Payroll'!I51</f>
+        <v/>
+      </c>
+      <c r="I36" s="52">
+        <f>'Staffing &amp; Payroll'!J50+'Staffing &amp; Payroll'!J51</f>
+        <v/>
+      </c>
+      <c r="J36" s="52">
+        <f>'Staffing &amp; Payroll'!K50+'Staffing &amp; Payroll'!K51</f>
+        <v/>
+      </c>
+      <c r="K36" s="52">
+        <f>'Staffing &amp; Payroll'!L50+'Staffing &amp; Payroll'!L51</f>
+        <v/>
+      </c>
+      <c r="L36" s="52">
+        <f>'Staffing &amp; Payroll'!M50+'Staffing &amp; Payroll'!M51</f>
+        <v/>
+      </c>
+      <c r="M36" s="52">
+        <f>'Staffing &amp; Payroll'!N50+'Staffing &amp; Payroll'!N51</f>
+        <v/>
+      </c>
+      <c r="N36" s="53">
+        <f>SUM('Staffing &amp; Payroll'!O50:R50)+SUM('Staffing &amp; Payroll'!O51:R51)</f>
+        <v/>
+      </c>
+      <c r="O36" s="53">
+        <f>SUM('Staffing &amp; Payroll'!S50:V50)+SUM('Staffing &amp; Payroll'!S51:V51)</f>
+        <v/>
+      </c>
+      <c r="P36" s="54">
+        <f>SUM(B36:M36)+N36+O36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Total Payroll &amp; Related</t>
+        </is>
+      </c>
+      <c r="B37" s="55">
+        <f>SUM(B28:B36)</f>
+        <v/>
+      </c>
+      <c r="C37" s="55">
+        <f>SUM(C28:C36)</f>
+        <v/>
+      </c>
+      <c r="D37" s="55">
+        <f>SUM(D28:D36)</f>
+        <v/>
+      </c>
+      <c r="E37" s="55">
+        <f>SUM(E28:E36)</f>
+        <v/>
+      </c>
+      <c r="F37" s="55">
+        <f>SUM(F28:F36)</f>
+        <v/>
+      </c>
+      <c r="G37" s="55">
+        <f>SUM(G28:G36)</f>
+        <v/>
+      </c>
+      <c r="H37" s="55">
+        <f>SUM(H28:H36)</f>
+        <v/>
+      </c>
+      <c r="I37" s="55">
+        <f>SUM(I28:I36)</f>
+        <v/>
+      </c>
+      <c r="J37" s="55">
+        <f>SUM(J28:J36)</f>
+        <v/>
+      </c>
+      <c r="K37" s="55">
+        <f>SUM(K28:K36)</f>
+        <v/>
+      </c>
+      <c r="L37" s="55">
+        <f>SUM(L28:L36)</f>
+        <v/>
+      </c>
+      <c r="M37" s="55">
+        <f>SUM(M28:M36)</f>
+        <v/>
+      </c>
+      <c r="N37" s="55">
+        <f>SUM(N28:N36)</f>
+        <v/>
+      </c>
+      <c r="O37" s="55">
+        <f>SUM(O28:O36)</f>
+        <v/>
+      </c>
+      <c r="P37" s="55">
+        <f>SUM(P28:P36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>General &amp; Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>Bank / Payroll Fees</t>
+        </is>
+      </c>
+      <c r="B40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="C40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="D40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="E40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="F40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="G40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="H40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="I40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="J40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="K40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="L40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="M40" s="52">
+        <f>Inputs!$B$101</f>
+        <v/>
+      </c>
+      <c r="N40" s="53">
+        <f>Inputs!$B$101*12</f>
+        <v/>
+      </c>
+      <c r="O40" s="53">
+        <f>Inputs!$B$101*12</f>
+        <v/>
+      </c>
+      <c r="P40" s="54">
+        <f>SUM(B40:M40)+N40+O40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="56" t="inlineStr">
+        <is>
+          <t>Triple Net Rent</t>
+        </is>
+      </c>
+      <c r="B41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="C41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="D41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="E41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="F41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="G41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="H41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="I41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="J41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="K41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="L41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="M41" s="52">
+        <f>Inputs!$B$102</f>
+        <v/>
+      </c>
+      <c r="N41" s="53">
+        <f>Inputs!$B$102*12</f>
+        <v/>
+      </c>
+      <c r="O41" s="53">
+        <f>Inputs!$B$102*12</f>
+        <v/>
+      </c>
+      <c r="P41" s="54">
+        <f>SUM(B41:M41)+N41+O41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="56" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="B42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="C42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="D42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="E42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="F42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="G42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="H42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="I42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="J42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="K42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="L42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="M42" s="52">
+        <f>Inputs!$B$91</f>
+        <v/>
+      </c>
+      <c r="N42" s="53">
+        <f>Inputs!$B$91*12</f>
+        <v/>
+      </c>
+      <c r="O42" s="53">
+        <f>Inputs!$B$91*12</f>
+        <v/>
+      </c>
+      <c r="P42" s="54">
+        <f>SUM(B42:M42)+N42+O42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="56" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="B43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="C43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="D43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="E43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="F43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="G43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="H43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="I43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="J43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="K43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="L43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="M43" s="52">
+        <f>Inputs!$B$92</f>
+        <v/>
+      </c>
+      <c r="N43" s="53">
+        <f>Inputs!$B$92*12</f>
+        <v/>
+      </c>
+      <c r="O43" s="53">
+        <f>Inputs!$B$92*12</f>
+        <v/>
+      </c>
+      <c r="P43" s="54">
+        <f>SUM(B43:M43)+N43+O43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="56" t="inlineStr">
+        <is>
+          <t>Telephone / Fax</t>
+        </is>
+      </c>
+      <c r="B44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="C44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="D44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="E44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="F44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="G44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="H44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="I44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="J44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="K44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="L44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="M44" s="52">
+        <f>Inputs!$B$93</f>
+        <v/>
+      </c>
+      <c r="N44" s="53">
+        <f>Inputs!$B$93*12</f>
+        <v/>
+      </c>
+      <c r="O44" s="53">
+        <f>Inputs!$B$93*12</f>
+        <v/>
+      </c>
+      <c r="P44" s="54">
+        <f>SUM(B44:M44)+N44+O44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="56" t="inlineStr">
+        <is>
+          <t>After Hours Messaging (BVTM)</t>
+        </is>
+      </c>
+      <c r="B45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="C45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="D45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="E45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="F45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="G45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="H45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="I45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="J45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="K45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="L45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="M45" s="52">
+        <f>Inputs!$B$94</f>
+        <v/>
+      </c>
+      <c r="N45" s="53">
+        <f>Inputs!$B$94*12</f>
+        <v/>
+      </c>
+      <c r="O45" s="53">
+        <f>Inputs!$B$94*12</f>
+        <v/>
+      </c>
+      <c r="P45" s="54">
+        <f>SUM(B45:M45)+N45+O45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="56" t="inlineStr">
+        <is>
+          <t>CFO / AP Support</t>
+        </is>
+      </c>
+      <c r="B46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M46" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N46" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O46" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P46" s="54">
+        <f>SUM(B46:M46)+N46+O46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="56" t="inlineStr">
+        <is>
+          <t>Support Services</t>
+        </is>
+      </c>
+      <c r="B47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M47" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N47" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O47" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P47" s="54">
+        <f>SUM(B47:M47)+N47+O47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>Messaging / CRG Signer</t>
+        </is>
+      </c>
+      <c r="B48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M48" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N48" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O48" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P48" s="54">
+        <f>SUM(B48:M48)+N48+O48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="56" t="inlineStr">
+        <is>
+          <t>NM Room &amp; Board</t>
+        </is>
+      </c>
+      <c r="B49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M49" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N49" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O49" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P49" s="54">
+        <f>SUM(B49:M49)+N49+O49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="56" t="inlineStr">
+        <is>
+          <t>Corporate Labor</t>
+        </is>
+      </c>
+      <c r="B50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M50" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N50" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O50" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P50" s="54">
+        <f>SUM(B50:M50)+N50+O50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="56" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="C51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="D51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="E51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="F51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="G51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="H51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="I51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="J51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="K51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="L51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="M51" s="52">
+        <f>Inputs!$B$103</f>
+        <v/>
+      </c>
+      <c r="N51" s="53">
+        <f>Inputs!$B$103*12</f>
+        <v/>
+      </c>
+      <c r="O51" s="53">
+        <f>Inputs!$B$103*12</f>
+        <v/>
+      </c>
+      <c r="P51" s="54">
+        <f>SUM(B51:M51)+N51+O51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="56" t="inlineStr">
+        <is>
+          <t>Outsourced Billing Fee (1.5%)</t>
+        </is>
+      </c>
+      <c r="B52" s="52">
+        <f>'Revenue Model'!C14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="C52" s="52">
+        <f>'Revenue Model'!D14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="D52" s="52">
+        <f>'Revenue Model'!E14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="E52" s="52">
+        <f>'Revenue Model'!F14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="F52" s="52">
+        <f>'Revenue Model'!G14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="G52" s="52">
+        <f>'Revenue Model'!H14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="H52" s="52">
+        <f>'Revenue Model'!I14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="I52" s="52">
+        <f>'Revenue Model'!J14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="J52" s="52">
+        <f>'Revenue Model'!K14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="K52" s="52">
+        <f>'Revenue Model'!L14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="L52" s="52">
+        <f>'Revenue Model'!M14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="M52" s="52">
+        <f>'Revenue Model'!N14*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="N52" s="53">
+        <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="O52" s="53">
+        <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$106</f>
+        <v/>
+      </c>
+      <c r="P52" s="54">
+        <f>SUM(B52:M52)+N52+O52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="56" t="inlineStr">
+        <is>
+          <t>EMR System</t>
+        </is>
+      </c>
+      <c r="B53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="C53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="D53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="E53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="F53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="G53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="H53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="I53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="J53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="K53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="L53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="M53" s="52">
+        <f>Inputs!$B$95</f>
+        <v/>
+      </c>
+      <c r="N53" s="53">
+        <f>Inputs!$B$95*12</f>
+        <v/>
+      </c>
+      <c r="O53" s="53">
+        <f>Inputs!$B$95*12</f>
+        <v/>
+      </c>
+      <c r="P53" s="54">
+        <f>SUM(B53:M53)+N53+O53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="56" t="inlineStr">
+        <is>
+          <t>Other EMR</t>
+        </is>
+      </c>
+      <c r="B54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M54" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N54" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O54" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P54" s="54">
+        <f>SUM(B54:M54)+N54+O54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="56" t="inlineStr">
+        <is>
+          <t>PCR (CPM)</t>
+        </is>
+      </c>
+      <c r="B55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="C55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="D55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="E55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="F55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="G55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="H55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="I55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="J55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="K55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="L55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="M55" s="52">
+        <f>Inputs!$B$96</f>
+        <v/>
+      </c>
+      <c r="N55" s="53">
+        <f>Inputs!$B$96*12</f>
+        <v/>
+      </c>
+      <c r="O55" s="53">
+        <f>Inputs!$B$96*12</f>
+        <v/>
+      </c>
+      <c r="P55" s="54">
+        <f>SUM(B55:M55)+N55+O55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="56" t="inlineStr">
+        <is>
+          <t>Ancillary</t>
+        </is>
+      </c>
+      <c r="B56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M56" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N56" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O56" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P56" s="54">
+        <f>SUM(B56:M56)+N56+O56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="56" t="inlineStr">
+        <is>
+          <t>Liability Insurance (D&amp;O)</t>
+        </is>
+      </c>
+      <c r="B57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="C57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="D57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="E57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="F57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="G57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="H57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="I57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="J57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="K57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="L57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="M57" s="52">
+        <f>Inputs!$B$98</f>
+        <v/>
+      </c>
+      <c r="N57" s="53">
+        <f>Inputs!$B$98*12</f>
+        <v/>
+      </c>
+      <c r="O57" s="53">
+        <f>Inputs!$B$98*12</f>
+        <v/>
+      </c>
+      <c r="P57" s="54">
+        <f>SUM(B57:M57)+N57+O57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="56" t="inlineStr">
+        <is>
+          <t>QR Payment Fee (0.75%)</t>
+        </is>
+      </c>
+      <c r="B58" s="52">
+        <f>'Revenue Model'!C14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="C58" s="52">
+        <f>'Revenue Model'!D14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="D58" s="52">
+        <f>'Revenue Model'!E14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="E58" s="52">
+        <f>'Revenue Model'!F14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="F58" s="52">
+        <f>'Revenue Model'!G14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="G58" s="52">
+        <f>'Revenue Model'!H14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="H58" s="52">
+        <f>'Revenue Model'!I14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="I58" s="52">
+        <f>'Revenue Model'!J14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="J58" s="52">
+        <f>'Revenue Model'!K14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="K58" s="52">
+        <f>'Revenue Model'!L14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="L58" s="52">
+        <f>'Revenue Model'!M14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="M58" s="52">
+        <f>'Revenue Model'!N14*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="N58" s="53">
+        <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="O58" s="53">
+        <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$107</f>
+        <v/>
+      </c>
+      <c r="P58" s="54">
+        <f>SUM(B58:M58)+N58+O58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="56" t="inlineStr">
+        <is>
+          <t>Training / CEUs</t>
+        </is>
+      </c>
+      <c r="B59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="C59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="D59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="E59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="F59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="G59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="H59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="I59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="J59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="K59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="L59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="M59" s="52">
+        <f>Inputs!$B$99</f>
+        <v/>
+      </c>
+      <c r="N59" s="53">
+        <f>Inputs!$B$99*12</f>
+        <v/>
+      </c>
+      <c r="O59" s="53">
+        <f>Inputs!$B$99*12</f>
+        <v/>
+      </c>
+      <c r="P59" s="54">
+        <f>SUM(B59:M59)+N59+O59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="56" t="inlineStr">
+        <is>
+          <t>Credit Card Fees</t>
+        </is>
+      </c>
+      <c r="B60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="C60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="D60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="E60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="F60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="G60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="H60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="I60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="J60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="K60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="L60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="M60" s="52">
+        <f>Inputs!$B$97</f>
+        <v/>
+      </c>
+      <c r="N60" s="53">
+        <f>Inputs!$B$97*12</f>
+        <v/>
+      </c>
+      <c r="O60" s="53">
+        <f>Inputs!$B$97*12</f>
+        <v/>
+      </c>
+      <c r="P60" s="54">
+        <f>SUM(B60:M60)+N60+O60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="56" t="inlineStr">
+        <is>
+          <t>Other (QPf)</t>
+        </is>
+      </c>
+      <c r="B61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M61" s="52">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N61" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O61" s="53">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P61" s="54">
+        <f>SUM(B61:M61)+N61+O61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="56" t="inlineStr">
+        <is>
+          <t>Other (Client)</t>
+        </is>
+      </c>
+      <c r="B62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="C62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="D62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="E62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="F62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="G62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="H62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="I62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="J62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="K62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="L62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="M62" s="52">
+        <f>Inputs!$B$100</f>
+        <v/>
+      </c>
+      <c r="N62" s="53">
+        <f>Inputs!$B$100*12</f>
+        <v/>
+      </c>
+      <c r="O62" s="53">
+        <f>Inputs!$B$100*12</f>
+        <v/>
+      </c>
+      <c r="P62" s="54">
+        <f>SUM(B62:M62)+N62+O62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Total General &amp; Administrative</t>
+        </is>
+      </c>
+      <c r="B63" s="55">
+        <f>SUM(B40:B62)</f>
+        <v/>
+      </c>
+      <c r="C63" s="55">
+        <f>SUM(C40:C62)</f>
+        <v/>
+      </c>
+      <c r="D63" s="55">
+        <f>SUM(D40:D62)</f>
+        <v/>
+      </c>
+      <c r="E63" s="55">
+        <f>SUM(E40:E62)</f>
+        <v/>
+      </c>
+      <c r="F63" s="55">
+        <f>SUM(F40:F62)</f>
+        <v/>
+      </c>
+      <c r="G63" s="55">
+        <f>SUM(G40:G62)</f>
+        <v/>
+      </c>
+      <c r="H63" s="55">
+        <f>SUM(H40:H62)</f>
+        <v/>
+      </c>
+      <c r="I63" s="55">
+        <f>SUM(I40:I62)</f>
+        <v/>
+      </c>
+      <c r="J63" s="55">
+        <f>SUM(J40:J62)</f>
+        <v/>
+      </c>
+      <c r="K63" s="55">
+        <f>SUM(K40:K62)</f>
+        <v/>
+      </c>
+      <c r="L63" s="55">
+        <f>SUM(L40:L62)</f>
+        <v/>
+      </c>
+      <c r="M63" s="55">
+        <f>SUM(M40:M62)</f>
+        <v/>
+      </c>
+      <c r="N63" s="55">
+        <f>SUM(N40:N62)</f>
+        <v/>
+      </c>
+      <c r="O63" s="55">
+        <f>SUM(O40:O62)</f>
+        <v/>
+      </c>
+      <c r="P63" s="55">
+        <f>SUM(P40:P62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B65" s="55">
+        <f>B37+B63</f>
+        <v/>
+      </c>
+      <c r="C65" s="55">
+        <f>C37+C63</f>
+        <v/>
+      </c>
+      <c r="D65" s="55">
+        <f>D37+D63</f>
+        <v/>
+      </c>
+      <c r="E65" s="55">
+        <f>E37+E63</f>
+        <v/>
+      </c>
+      <c r="F65" s="55">
+        <f>F37+F63</f>
+        <v/>
+      </c>
+      <c r="G65" s="55">
+        <f>G37+G63</f>
+        <v/>
+      </c>
+      <c r="H65" s="55">
+        <f>H37+H63</f>
+        <v/>
+      </c>
+      <c r="I65" s="55">
+        <f>I37+I63</f>
+        <v/>
+      </c>
+      <c r="J65" s="55">
+        <f>J37+J63</f>
+        <v/>
+      </c>
+      <c r="K65" s="55">
+        <f>K37+K63</f>
+        <v/>
+      </c>
+      <c r="L65" s="55">
+        <f>L37+L63</f>
+        <v/>
+      </c>
+      <c r="M65" s="55">
+        <f>M37+M63</f>
+        <v/>
+      </c>
+      <c r="N65" s="55">
+        <f>N37+N63</f>
+        <v/>
+      </c>
+      <c r="O65" s="55">
+        <f>O37+O63</f>
+        <v/>
+      </c>
+      <c r="P65" s="55">
+        <f>P37+P63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B67" s="57">
+        <f>B24-B65</f>
+        <v/>
+      </c>
+      <c r="C67" s="57">
+        <f>C24-C65</f>
+        <v/>
+      </c>
+      <c r="D67" s="57">
+        <f>D24-D65</f>
+        <v/>
+      </c>
+      <c r="E67" s="57">
+        <f>E24-E65</f>
+        <v/>
+      </c>
+      <c r="F67" s="57">
+        <f>F24-F65</f>
+        <v/>
+      </c>
+      <c r="G67" s="57">
+        <f>G24-G65</f>
+        <v/>
+      </c>
+      <c r="H67" s="57">
+        <f>H24-H65</f>
+        <v/>
+      </c>
+      <c r="I67" s="57">
+        <f>I24-I65</f>
+        <v/>
+      </c>
+      <c r="J67" s="57">
+        <f>J24-J65</f>
+        <v/>
+      </c>
+      <c r="K67" s="57">
+        <f>K24-K65</f>
+        <v/>
+      </c>
+      <c r="L67" s="57">
+        <f>L24-L65</f>
+        <v/>
+      </c>
+      <c r="M67" s="57">
+        <f>M24-M65</f>
+        <v/>
+      </c>
+      <c r="N67" s="57">
+        <f>N24-N65</f>
+        <v/>
+      </c>
+      <c r="O67" s="57">
+        <f>O24-O65</f>
+        <v/>
+      </c>
+      <c r="P67" s="57">
+        <f>P24-P65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Net Margin %</t>
+        </is>
+      </c>
+      <c r="B69" s="32">
+        <f>IF(B12=0,0,B67/B12)</f>
+        <v/>
+      </c>
+      <c r="C69" s="32">
+        <f>IF(C12=0,0,C67/C12)</f>
+        <v/>
+      </c>
+      <c r="D69" s="32">
+        <f>IF(D12=0,0,D67/D12)</f>
+        <v/>
+      </c>
+      <c r="E69" s="32">
+        <f>IF(E12=0,0,E67/E12)</f>
+        <v/>
+      </c>
+      <c r="F69" s="32">
+        <f>IF(F12=0,0,F67/F12)</f>
+        <v/>
+      </c>
+      <c r="G69" s="32">
+        <f>IF(G12=0,0,G67/G12)</f>
+        <v/>
+      </c>
+      <c r="H69" s="32">
+        <f>IF(H12=0,0,H67/H12)</f>
+        <v/>
+      </c>
+      <c r="I69" s="32">
+        <f>IF(I12=0,0,I67/I12)</f>
+        <v/>
+      </c>
+      <c r="J69" s="32">
+        <f>IF(J12=0,0,J67/J12)</f>
+        <v/>
+      </c>
+      <c r="K69" s="32">
+        <f>IF(K12=0,0,K67/K12)</f>
+        <v/>
+      </c>
+      <c r="L69" s="32">
+        <f>IF(L12=0,0,L67/L12)</f>
+        <v/>
+      </c>
+      <c r="M69" s="32">
+        <f>IF(M12=0,0,M67/M12)</f>
+        <v/>
+      </c>
+      <c r="N69" s="32">
+        <f>IF(N12=0,0,N67/N12)</f>
+        <v/>
+      </c>
+      <c r="O69" s="32">
+        <f>IF(O12=0,0,O67/O12)</f>
+        <v/>
+      </c>
+      <c r="P69" s="32">
+        <f>IF(P12=0,0,P67/P12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="33" t="inlineStr">
+        <is>
+          <t>Cash-basis operating P&amp;L (QuickBooks layout): all payroll is in Operating Expenses, Cost of Services holds patient supplies only. "Net Income" here = operating result and ties to the engine's EBITDA; interest, D&amp;A and tax are below EBITDA on the Operating Budget / 3-statement tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A71:H72"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3779,29 +7456,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O8" s="43" t="inlineStr">
+      <c r="O8" s="44" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S8" s="43" t="inlineStr">
+      <c r="S8" s="44" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr"/>
+      <c r="A9" s="45" t="inlineStr"/>
       <c r="C9" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -5245,7 +8922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -5294,34 +8971,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Opening</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="43" t="inlineStr">
+      <c r="S4" s="44" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="44" t="inlineStr"/>
+      <c r="A5" s="45" t="inlineStr"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -8050,7 +11727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -8229,7 +11906,7 @@
         <f>AVERAGE(C8:E8)</f>
         <v/>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="48">
         <f>'Revenue Model'!E17</f>
         <v/>
       </c>
@@ -8264,7 +11941,7 @@
         <f>AVERAGE(C9:E9)</f>
         <v/>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="46">
         <f>'Revenue Model'!E10</f>
         <v/>
       </c>
@@ -8452,7 +12129,7 @@
         <f>AVERAGE(C19:E19)</f>
         <v/>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="48">
         <f>'Staffing &amp; Payroll'!E53+'Staffing &amp; Payroll'!E54</f>
         <v/>
       </c>
@@ -9372,6 +13049,360 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002E5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AZALEA HOSPICE &amp; PALLIATIVE CARE - Tyler, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MVI 'Perfect Visit' Upside - illustrative growth above the conservative base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMPTION (blue = adjust)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MVI-driven census / referral uplift %</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SCENARIO RESULTS (Year-2 annualized, SBA-only debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Base (plan)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>+30%</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>MVI case</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Census / referral uplift</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C9" s="36">
+        <f>0.10</f>
+        <v/>
+      </c>
+      <c r="D9" s="36">
+        <f>0.20</f>
+        <v/>
+      </c>
+      <c r="E9" s="36">
+        <f>0.30</f>
+        <v/>
+      </c>
+      <c r="F9" s="36">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Variable costs</t>
+        </is>
+      </c>
+      <c r="B11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+B9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+C9)</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+D9)</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Fixed costs (held at plan)</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B13" s="41">
+        <f>B10+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="41">
+        <f>C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="41">
+        <f>D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="41">
+        <f>E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="41">
+        <f>F10+F11+F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>EBITDA lift vs base</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>B13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>C13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>D13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>E13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>F13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Net income (after D&amp;A, interest, tax)</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(B13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*B9</f>
+        <v/>
+      </c>
+      <c r="C15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(C13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(D13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*D9</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(E13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*E9</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(F13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>SBA debt service</t>
+        </is>
+      </c>
+      <c r="B16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>DSCR (SBA-only)</t>
+        </is>
+      </c>
+      <c r="B17" s="31">
+        <f>IF(B16=0,0,B13/B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="31">
+        <f>IF(C16=0,0,C13/C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="31">
+        <f>IF(D16=0,0,D13/D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="31">
+        <f>IF(E16=0,0,E13/E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="31">
+        <f>IF(F16=0,0,F13/F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>Illustrative upside ONLY - not used for loan underwriting. The base case (Lender Summary / Business Plan Section 11) assumes no lift from the MVI 'Perfect Visit' / 'Perfect Phones' certification or Andrew Reid's national advertising campaign; SBA debt service is fully covered without it. This tab scales Year-2 census/referrals by the uplift while holding the cost base at plan (static roster); sustained higher census would trigger the model's capacity hiring, so realized EBITDA would run modestly below the static figures shown. Higher EBITDA also raises the equity exit value and MOIC on the Returns tab. For a full dynamic re-run, set Census scenario = Upside on the Inputs tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F22"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -9430,7 +13461,7 @@
           <t>Blended GROSS rate ($/PD)</t>
         </is>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="42">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
@@ -9441,35 +13472,35 @@
           <t>Blended NET rate ($/PD)</t>
         </is>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="42">
         <f>Inputs!$B$21</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O8" s="43" t="inlineStr">
+      <c r="O8" s="44" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S8" s="43" t="inlineStr">
+      <c r="S8" s="44" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr"/>
+      <c r="A9" s="45" t="inlineStr"/>
       <c r="C9" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -9577,83 +13608,83 @@
           <t>Average daily census (ADC)</t>
         </is>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="46">
         <f>Inputs!C$33</f>
         <v/>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="46">
         <f>Inputs!D$33</f>
         <v/>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="46">
         <f>Inputs!E$33</f>
         <v/>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="46">
         <f>Inputs!F$33</f>
         <v/>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="46">
         <f>Inputs!G$33</f>
         <v/>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="46">
         <f>Inputs!H$33</f>
         <v/>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="46">
         <f>Inputs!I$33</f>
         <v/>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="46">
         <f>Inputs!J$33</f>
         <v/>
       </c>
-      <c r="K10" s="45">
+      <c r="K10" s="46">
         <f>Inputs!K$33</f>
         <v/>
       </c>
-      <c r="L10" s="45">
+      <c r="L10" s="46">
         <f>Inputs!L$33</f>
         <v/>
       </c>
-      <c r="M10" s="45">
+      <c r="M10" s="46">
         <f>Inputs!M$33</f>
         <v/>
       </c>
-      <c r="N10" s="45">
+      <c r="N10" s="46">
         <f>Inputs!N$33</f>
         <v/>
       </c>
-      <c r="O10" s="45">
+      <c r="O10" s="46">
         <f>Inputs!O$33</f>
         <v/>
       </c>
-      <c r="P10" s="45">
+      <c r="P10" s="46">
         <f>Inputs!P$33</f>
         <v/>
       </c>
-      <c r="Q10" s="45">
+      <c r="Q10" s="46">
         <f>Inputs!Q$33</f>
         <v/>
       </c>
-      <c r="R10" s="45">
+      <c r="R10" s="46">
         <f>Inputs!R$33</f>
         <v/>
       </c>
-      <c r="S10" s="45">
+      <c r="S10" s="46">
         <f>Inputs!S$33</f>
         <v/>
       </c>
-      <c r="T10" s="45">
+      <c r="T10" s="46">
         <f>Inputs!T$33</f>
         <v/>
       </c>
-      <c r="U10" s="45">
+      <c r="U10" s="46">
         <f>Inputs!U$33</f>
         <v/>
       </c>
-      <c r="V10" s="45">
+      <c r="V10" s="46">
         <f>Inputs!V$33</f>
         <v/>
       </c>
@@ -9664,83 +13695,83 @@
           <t>Days in period</t>
         </is>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="J11" s="45">
+      <c r="J11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="K11" s="45">
+      <c r="K11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="L11" s="45">
+      <c r="L11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="M11" s="45">
+      <c r="M11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="46">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="O11" s="45">
+      <c r="O11" s="46">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="P11" s="45">
+      <c r="P11" s="46">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="Q11" s="45">
+      <c r="Q11" s="46">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="R11" s="45">
+      <c r="R11" s="46">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="S11" s="45">
+      <c r="S11" s="46">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="T11" s="45">
+      <c r="T11" s="46">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="U11" s="45">
+      <c r="U11" s="46">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="V11" s="45">
+      <c r="V11" s="46">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
@@ -9751,83 +13782,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="47">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="47">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="47">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="47">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="47">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="46">
+      <c r="H12" s="47">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="47">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="46">
+      <c r="J12" s="47">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="46">
+      <c r="K12" s="47">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="46">
+      <c r="L12" s="47">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="46">
+      <c r="M12" s="47">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="46">
+      <c r="N12" s="47">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="46">
+      <c r="O12" s="47">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="46">
+      <c r="P12" s="47">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="46">
+      <c r="Q12" s="47">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="46">
+      <c r="R12" s="47">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="46">
+      <c r="S12" s="47">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="46">
+      <c r="T12" s="47">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="46">
+      <c r="U12" s="47">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="46">
+      <c r="V12" s="47">
         <f>V10*V11</f>
         <v/>
       </c>
@@ -10367,7 +14398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -10416,29 +14447,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="43" t="inlineStr">
+      <c r="S4" s="44" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="44" t="inlineStr"/>
+      <c r="A5" s="45" t="inlineStr"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -10546,83 +14577,83 @@
           <t>ADC (driver)</t>
         </is>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="46">
         <f>'Revenue Model'!C10</f>
         <v/>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="46">
         <f>'Revenue Model'!D10</f>
         <v/>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="46">
         <f>'Revenue Model'!E10</f>
         <v/>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="46">
         <f>'Revenue Model'!F10</f>
         <v/>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="46">
         <f>'Revenue Model'!G10</f>
         <v/>
       </c>
-      <c r="H6" s="45">
+      <c r="H6" s="46">
         <f>'Revenue Model'!H10</f>
         <v/>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="46">
         <f>'Revenue Model'!I10</f>
         <v/>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="46">
         <f>'Revenue Model'!J10</f>
         <v/>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="46">
         <f>'Revenue Model'!K10</f>
         <v/>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="46">
         <f>'Revenue Model'!L10</f>
         <v/>
       </c>
-      <c r="M6" s="45">
+      <c r="M6" s="46">
         <f>'Revenue Model'!M10</f>
         <v/>
       </c>
-      <c r="N6" s="45">
+      <c r="N6" s="46">
         <f>'Revenue Model'!N10</f>
         <v/>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="46">
         <f>'Revenue Model'!O10</f>
         <v/>
       </c>
-      <c r="P6" s="45">
+      <c r="P6" s="46">
         <f>'Revenue Model'!P10</f>
         <v/>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="46">
         <f>'Revenue Model'!Q10</f>
         <v/>
       </c>
-      <c r="R6" s="45">
+      <c r="R6" s="46">
         <f>'Revenue Model'!R10</f>
         <v/>
       </c>
-      <c r="S6" s="45">
+      <c r="S6" s="46">
         <f>'Revenue Model'!S10</f>
         <v/>
       </c>
-      <c r="T6" s="45">
+      <c r="T6" s="46">
         <f>'Revenue Model'!T10</f>
         <v/>
       </c>
-      <c r="U6" s="45">
+      <c r="U6" s="46">
         <f>'Revenue Model'!U10</f>
         <v/>
       </c>
-      <c r="V6" s="45">
+      <c r="V6" s="46">
         <f>'Revenue Model'!V10</f>
         <v/>
       </c>
@@ -14151,7 +18182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -14200,29 +18231,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="44" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="43" t="inlineStr">
+      <c r="S4" s="44" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="44" t="inlineStr"/>
+      <c r="A5" s="45" t="inlineStr"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>M1</t>
@@ -14330,83 +18361,83 @@
           <t>NET REVENUE</t>
         </is>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="48">
         <f>'Revenue Model'!C17</f>
         <v/>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="48">
         <f>'Revenue Model'!D17</f>
         <v/>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <f>'Revenue Model'!E17</f>
         <v/>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="48">
         <f>'Revenue Model'!F17</f>
         <v/>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="48">
         <f>'Revenue Model'!G17</f>
         <v/>
       </c>
-      <c r="H6" s="47">
+      <c r="H6" s="48">
         <f>'Revenue Model'!H17</f>
         <v/>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="48">
         <f>'Revenue Model'!I17</f>
         <v/>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="48">
         <f>'Revenue Model'!J17</f>
         <v/>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="48">
         <f>'Revenue Model'!K17</f>
         <v/>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="48">
         <f>'Revenue Model'!L17</f>
         <v/>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="48">
         <f>'Revenue Model'!M17</f>
         <v/>
       </c>
-      <c r="N6" s="47">
+      <c r="N6" s="48">
         <f>'Revenue Model'!N17</f>
         <v/>
       </c>
-      <c r="O6" s="47">
+      <c r="O6" s="48">
         <f>'Revenue Model'!O17</f>
         <v/>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="48">
         <f>'Revenue Model'!P17</f>
         <v/>
       </c>
-      <c r="Q6" s="47">
+      <c r="Q6" s="48">
         <f>'Revenue Model'!Q17</f>
         <v/>
       </c>
-      <c r="R6" s="47">
+      <c r="R6" s="48">
         <f>'Revenue Model'!R17</f>
         <v/>
       </c>
-      <c r="S6" s="47">
+      <c r="S6" s="48">
         <f>'Revenue Model'!S17</f>
         <v/>
       </c>
-      <c r="T6" s="47">
+      <c r="T6" s="48">
         <f>'Revenue Model'!T17</f>
         <v/>
       </c>
-      <c r="U6" s="47">
+      <c r="U6" s="48">
         <f>'Revenue Model'!U17</f>
         <v/>
       </c>
-      <c r="V6" s="47">
+      <c r="V6" s="48">
         <f>'Revenue Model'!V17</f>
         <v/>
       </c>
@@ -15562,83 +19593,83 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C24" s="48">
+      <c r="C24" s="41">
         <f>C15-C23</f>
         <v/>
       </c>
-      <c r="D24" s="48">
+      <c r="D24" s="41">
         <f>D15-D23</f>
         <v/>
       </c>
-      <c r="E24" s="48">
+      <c r="E24" s="41">
         <f>E15-E23</f>
         <v/>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="41">
         <f>F15-F23</f>
         <v/>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="41">
         <f>G15-G23</f>
         <v/>
       </c>
-      <c r="H24" s="48">
+      <c r="H24" s="41">
         <f>H15-H23</f>
         <v/>
       </c>
-      <c r="I24" s="48">
+      <c r="I24" s="41">
         <f>I15-I23</f>
         <v/>
       </c>
-      <c r="J24" s="48">
+      <c r="J24" s="41">
         <f>J15-J23</f>
         <v/>
       </c>
-      <c r="K24" s="48">
+      <c r="K24" s="41">
         <f>K15-K23</f>
         <v/>
       </c>
-      <c r="L24" s="48">
+      <c r="L24" s="41">
         <f>L15-L23</f>
         <v/>
       </c>
-      <c r="M24" s="48">
+      <c r="M24" s="41">
         <f>M15-M23</f>
         <v/>
       </c>
-      <c r="N24" s="48">
+      <c r="N24" s="41">
         <f>N15-N23</f>
         <v/>
       </c>
-      <c r="O24" s="48">
+      <c r="O24" s="41">
         <f>O15-O23</f>
         <v/>
       </c>
-      <c r="P24" s="48">
+      <c r="P24" s="41">
         <f>P15-P23</f>
         <v/>
       </c>
-      <c r="Q24" s="48">
+      <c r="Q24" s="41">
         <f>Q15-Q23</f>
         <v/>
       </c>
-      <c r="R24" s="48">
+      <c r="R24" s="41">
         <f>R15-R23</f>
         <v/>
       </c>
-      <c r="S24" s="48">
+      <c r="S24" s="41">
         <f>S15-S23</f>
         <v/>
       </c>
-      <c r="T24" s="48">
+      <c r="T24" s="41">
         <f>T15-T23</f>
         <v/>
       </c>
-      <c r="U24" s="48">
+      <c r="U24" s="41">
         <f>U15-U23</f>
         <v/>
       </c>
-      <c r="V24" s="48">
+      <c r="V24" s="41">
         <f>V15-V23</f>
         <v/>
       </c>
@@ -16359,3665 +20390,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00808080"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12.5" customWidth="1" min="2" max="2"/>
-    <col width="12.5" customWidth="1" min="3" max="3"/>
-    <col width="12.5" customWidth="1" min="4" max="4"/>
-    <col width="12.5" customWidth="1" min="5" max="5"/>
-    <col width="12.5" customWidth="1" min="6" max="6"/>
-    <col width="12.5" customWidth="1" min="7" max="7"/>
-    <col width="12.5" customWidth="1" min="8" max="8"/>
-    <col width="12.5" customWidth="1" min="9" max="9"/>
-    <col width="12.5" customWidth="1" min="10" max="10"/>
-    <col width="12.5" customWidth="1" min="11" max="11"/>
-    <col width="12.5" customWidth="1" min="12" max="12"/>
-    <col width="12.5" customWidth="1" min="13" max="13"/>
-    <col width="12.5" customWidth="1" min="14" max="14"/>
-    <col width="12.5" customWidth="1" min="15" max="15"/>
-    <col width="12.5" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="49" t="inlineStr">
-        <is>
-          <t>Azalea Hospice &amp; Palliative Care - Tyler, TX</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="50" t="inlineStr">
-        <is>
-          <t>Profit and Loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Year 1 (monthly) | Years 2-3 (annual) | model data, cash basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="51" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="C5" s="51" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="D5" s="51" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="E5" s="51" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="F5" s="51" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="G5" s="51" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="H5" s="51" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="I5" s="51" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="J5" s="51" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="K5" s="51" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="L5" s="51" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="M5" s="51" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="N5" s="51" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="O5" s="51" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="P5" s="51" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Gross Billed Revenue</t>
-        </is>
-      </c>
-      <c r="B7" s="52">
-        <f>'Revenue Model'!C14</f>
-        <v/>
-      </c>
-      <c r="C7" s="52">
-        <f>'Revenue Model'!D14</f>
-        <v/>
-      </c>
-      <c r="D7" s="52">
-        <f>'Revenue Model'!E14</f>
-        <v/>
-      </c>
-      <c r="E7" s="52">
-        <f>'Revenue Model'!F14</f>
-        <v/>
-      </c>
-      <c r="F7" s="52">
-        <f>'Revenue Model'!G14</f>
-        <v/>
-      </c>
-      <c r="G7" s="52">
-        <f>'Revenue Model'!H14</f>
-        <v/>
-      </c>
-      <c r="H7" s="52">
-        <f>'Revenue Model'!I14</f>
-        <v/>
-      </c>
-      <c r="I7" s="52">
-        <f>'Revenue Model'!J14</f>
-        <v/>
-      </c>
-      <c r="J7" s="52">
-        <f>'Revenue Model'!K14</f>
-        <v/>
-      </c>
-      <c r="K7" s="52">
-        <f>'Revenue Model'!L14</f>
-        <v/>
-      </c>
-      <c r="L7" s="52">
-        <f>'Revenue Model'!M14</f>
-        <v/>
-      </c>
-      <c r="M7" s="52">
-        <f>'Revenue Model'!N14</f>
-        <v/>
-      </c>
-      <c r="N7" s="53">
-        <f>SUM('Revenue Model'!O14:R14)</f>
-        <v/>
-      </c>
-      <c r="O7" s="53">
-        <f>SUM('Revenue Model'!S14:V14)</f>
-        <v/>
-      </c>
-      <c r="P7" s="54">
-        <f>SUM(B7:M7)+N7+O7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Less: CDAs Adjustment</t>
-        </is>
-      </c>
-      <c r="B8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M8" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N8" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O8" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P8" s="54">
-        <f>SUM(B8:M8)+N8+O8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Less: Net Due Zero (Write-offs)</t>
-        </is>
-      </c>
-      <c r="B9" s="52">
-        <f>'Revenue Model'!C14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="C9" s="52">
-        <f>'Revenue Model'!D14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="D9" s="52">
-        <f>'Revenue Model'!E14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="E9" s="52">
-        <f>'Revenue Model'!F14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="F9" s="52">
-        <f>'Revenue Model'!G14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="G9" s="52">
-        <f>'Revenue Model'!H14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="H9" s="52">
-        <f>'Revenue Model'!I14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="I9" s="52">
-        <f>'Revenue Model'!J14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="J9" s="52">
-        <f>'Revenue Model'!K14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="K9" s="52">
-        <f>'Revenue Model'!L14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="L9" s="52">
-        <f>'Revenue Model'!M14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="M9" s="52">
-        <f>'Revenue Model'!N14*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="N9" s="53">
-        <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="O9" s="53">
-        <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$11</f>
-        <v/>
-      </c>
-      <c r="P9" s="54">
-        <f>SUM(B9:M9)+N9+O9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Less: Sequestration</t>
-        </is>
-      </c>
-      <c r="B10" s="52">
-        <f>'Revenue Model'!C14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="C10" s="52">
-        <f>'Revenue Model'!D14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="D10" s="52">
-        <f>'Revenue Model'!E14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="E10" s="52">
-        <f>'Revenue Model'!F14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="F10" s="52">
-        <f>'Revenue Model'!G14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="G10" s="52">
-        <f>'Revenue Model'!H14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="H10" s="52">
-        <f>'Revenue Model'!I14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="I10" s="52">
-        <f>'Revenue Model'!J14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="J10" s="52">
-        <f>'Revenue Model'!K14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="K10" s="52">
-        <f>'Revenue Model'!L14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="L10" s="52">
-        <f>'Revenue Model'!M14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="M10" s="52">
-        <f>'Revenue Model'!N14*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="N10" s="53">
-        <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="O10" s="53">
-        <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$10</f>
-        <v/>
-      </c>
-      <c r="P10" s="54">
-        <f>SUM(B10:M10)+N10+O10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Less: Medication Adjustments</t>
-        </is>
-      </c>
-      <c r="B11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M11" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N11" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O11" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P11" s="54">
-        <f>SUM(B11:M11)+N11+O11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Total Income</t>
-        </is>
-      </c>
-      <c r="B12" s="55">
-        <f>B7-B8-B9-B10-B11</f>
-        <v/>
-      </c>
-      <c r="C12" s="55">
-        <f>C7-C8-C9-C10-C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="55">
-        <f>D7-D8-D9-D10-D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="55">
-        <f>E7-E8-E9-E10-E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="55">
-        <f>F7-F8-F9-F10-F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="55">
-        <f>G7-G8-G9-G10-G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="55">
-        <f>H7-H8-H9-H10-H11</f>
-        <v/>
-      </c>
-      <c r="I12" s="55">
-        <f>I7-I8-I9-I10-I11</f>
-        <v/>
-      </c>
-      <c r="J12" s="55">
-        <f>J7-J8-J9-J10-J11</f>
-        <v/>
-      </c>
-      <c r="K12" s="55">
-        <f>K7-K8-K9-K10-K11</f>
-        <v/>
-      </c>
-      <c r="L12" s="55">
-        <f>L7-L8-L9-L10-L11</f>
-        <v/>
-      </c>
-      <c r="M12" s="55">
-        <f>M7-M8-M9-M10-M11</f>
-        <v/>
-      </c>
-      <c r="N12" s="55">
-        <f>N7-N8-N9-N10-N11</f>
-        <v/>
-      </c>
-      <c r="O12" s="55">
-        <f>O7-O8-O9-O10-O11</f>
-        <v/>
-      </c>
-      <c r="P12" s="55">
-        <f>P7-P8-P9-P10-P11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>Cost of Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Pharmacy</t>
-        </is>
-      </c>
-      <c r="B15" s="52">
-        <f>'Revenue Model'!C12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="C15" s="52">
-        <f>'Revenue Model'!D12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="D15" s="52">
-        <f>'Revenue Model'!E12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="E15" s="52">
-        <f>'Revenue Model'!F12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="F15" s="52">
-        <f>'Revenue Model'!G12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="G15" s="52">
-        <f>'Revenue Model'!H12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="H15" s="52">
-        <f>'Revenue Model'!I12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="I15" s="52">
-        <f>'Revenue Model'!J12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="J15" s="52">
-        <f>'Revenue Model'!K12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="K15" s="52">
-        <f>'Revenue Model'!L12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="L15" s="52">
-        <f>'Revenue Model'!M12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="M15" s="52">
-        <f>'Revenue Model'!N12*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="N15" s="53">
-        <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="O15" s="53">
-        <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$88</f>
-        <v/>
-      </c>
-      <c r="P15" s="54">
-        <f>SUM(B15:M15)+N15+O15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Medical Supplies</t>
-        </is>
-      </c>
-      <c r="B16" s="52">
-        <f>'Revenue Model'!C12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="C16" s="52">
-        <f>'Revenue Model'!D12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="D16" s="52">
-        <f>'Revenue Model'!E12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="E16" s="52">
-        <f>'Revenue Model'!F12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="F16" s="52">
-        <f>'Revenue Model'!G12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="G16" s="52">
-        <f>'Revenue Model'!H12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="H16" s="52">
-        <f>'Revenue Model'!I12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="I16" s="52">
-        <f>'Revenue Model'!J12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="J16" s="52">
-        <f>'Revenue Model'!K12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="K16" s="52">
-        <f>'Revenue Model'!L12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="L16" s="52">
-        <f>'Revenue Model'!M12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="M16" s="52">
-        <f>'Revenue Model'!N12*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="N16" s="53">
-        <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="O16" s="53">
-        <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$86</f>
-        <v/>
-      </c>
-      <c r="P16" s="54">
-        <f>SUM(B16:M16)+N16+O16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Durable Medical Equipment (DME)</t>
-        </is>
-      </c>
-      <c r="B17" s="52">
-        <f>'Revenue Model'!C12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="C17" s="52">
-        <f>'Revenue Model'!D12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="D17" s="52">
-        <f>'Revenue Model'!E12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="E17" s="52">
-        <f>'Revenue Model'!F12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="F17" s="52">
-        <f>'Revenue Model'!G12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="G17" s="52">
-        <f>'Revenue Model'!H12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="H17" s="52">
-        <f>'Revenue Model'!I12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="I17" s="52">
-        <f>'Revenue Model'!J12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="J17" s="52">
-        <f>'Revenue Model'!K12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="K17" s="52">
-        <f>'Revenue Model'!L12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="L17" s="52">
-        <f>'Revenue Model'!M12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="M17" s="52">
-        <f>'Revenue Model'!N12*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="N17" s="53">
-        <f>SUM('Revenue Model'!O12:R12)*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="O17" s="53">
-        <f>SUM('Revenue Model'!S12:V12)*Inputs!$B$87</f>
-        <v/>
-      </c>
-      <c r="P17" s="54">
-        <f>SUM(B17:M17)+N17+O17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Respite Care</t>
-        </is>
-      </c>
-      <c r="B18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M18" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N18" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O18" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P18" s="54">
-        <f>SUM(B18:M18)+N18+O18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Transportation</t>
-        </is>
-      </c>
-      <c r="B19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M19" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N19" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O19" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P19" s="54">
-        <f>SUM(B19:M19)+N19+O19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Infusion / Labs</t>
-        </is>
-      </c>
-      <c r="B20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M20" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N20" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O20" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P20" s="54">
-        <f>SUM(B20:M20)+N20+O20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>PT / OT / ST</t>
-        </is>
-      </c>
-      <c r="B21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M21" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N21" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O21" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P21" s="54">
-        <f>SUM(B21:M21)+N21+O21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Total Cost of Services</t>
-        </is>
-      </c>
-      <c r="B22" s="55">
-        <f>SUM(B15:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="55">
-        <f>SUM(C15:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="55">
-        <f>SUM(D15:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="55">
-        <f>SUM(E15:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="55">
-        <f>SUM(F15:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="55">
-        <f>SUM(G15:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="55">
-        <f>SUM(H15:H21)</f>
-        <v/>
-      </c>
-      <c r="I22" s="55">
-        <f>SUM(I15:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="55">
-        <f>SUM(J15:J21)</f>
-        <v/>
-      </c>
-      <c r="K22" s="55">
-        <f>SUM(K15:K21)</f>
-        <v/>
-      </c>
-      <c r="L22" s="55">
-        <f>SUM(L15:L21)</f>
-        <v/>
-      </c>
-      <c r="M22" s="55">
-        <f>SUM(M15:M21)</f>
-        <v/>
-      </c>
-      <c r="N22" s="55">
-        <f>SUM(N15:N21)</f>
-        <v/>
-      </c>
-      <c r="O22" s="55">
-        <f>SUM(O15:O21)</f>
-        <v/>
-      </c>
-      <c r="P22" s="55">
-        <f>SUM(P15:P21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B24" s="55">
-        <f>B12-B22</f>
-        <v/>
-      </c>
-      <c r="C24" s="55">
-        <f>C12-C22</f>
-        <v/>
-      </c>
-      <c r="D24" s="55">
-        <f>D12-D22</f>
-        <v/>
-      </c>
-      <c r="E24" s="55">
-        <f>E12-E22</f>
-        <v/>
-      </c>
-      <c r="F24" s="55">
-        <f>F12-F22</f>
-        <v/>
-      </c>
-      <c r="G24" s="55">
-        <f>G12-G22</f>
-        <v/>
-      </c>
-      <c r="H24" s="55">
-        <f>H12-H22</f>
-        <v/>
-      </c>
-      <c r="I24" s="55">
-        <f>I12-I22</f>
-        <v/>
-      </c>
-      <c r="J24" s="55">
-        <f>J12-J22</f>
-        <v/>
-      </c>
-      <c r="K24" s="55">
-        <f>K12-K22</f>
-        <v/>
-      </c>
-      <c r="L24" s="55">
-        <f>L12-L22</f>
-        <v/>
-      </c>
-      <c r="M24" s="55">
-        <f>M12-M22</f>
-        <v/>
-      </c>
-      <c r="N24" s="55">
-        <f>N12-N22</f>
-        <v/>
-      </c>
-      <c r="O24" s="55">
-        <f>O12-O22</f>
-        <v/>
-      </c>
-      <c r="P24" s="55">
-        <f>P12-P22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Payroll &amp; Related</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="56" t="inlineStr">
-        <is>
-          <t>Payroll - 1st Half</t>
-        </is>
-      </c>
-      <c r="B28" s="52">
-        <f>('Staffing &amp; Payroll'!C30+'Staffing &amp; Payroll'!C42+'Staffing &amp; Payroll'!C38+'Staffing &amp; Payroll'!C43)/2</f>
-        <v/>
-      </c>
-      <c r="C28" s="52">
-        <f>('Staffing &amp; Payroll'!D30+'Staffing &amp; Payroll'!D42+'Staffing &amp; Payroll'!D38+'Staffing &amp; Payroll'!D43)/2</f>
-        <v/>
-      </c>
-      <c r="D28" s="52">
-        <f>('Staffing &amp; Payroll'!E30+'Staffing &amp; Payroll'!E42+'Staffing &amp; Payroll'!E38+'Staffing &amp; Payroll'!E43)/2</f>
-        <v/>
-      </c>
-      <c r="E28" s="52">
-        <f>('Staffing &amp; Payroll'!F30+'Staffing &amp; Payroll'!F42+'Staffing &amp; Payroll'!F38+'Staffing &amp; Payroll'!F43)/2</f>
-        <v/>
-      </c>
-      <c r="F28" s="52">
-        <f>('Staffing &amp; Payroll'!G30+'Staffing &amp; Payroll'!G42+'Staffing &amp; Payroll'!G38+'Staffing &amp; Payroll'!G43)/2</f>
-        <v/>
-      </c>
-      <c r="G28" s="52">
-        <f>('Staffing &amp; Payroll'!H30+'Staffing &amp; Payroll'!H42+'Staffing &amp; Payroll'!H38+'Staffing &amp; Payroll'!H43)/2</f>
-        <v/>
-      </c>
-      <c r="H28" s="52">
-        <f>('Staffing &amp; Payroll'!I30+'Staffing &amp; Payroll'!I42+'Staffing &amp; Payroll'!I38+'Staffing &amp; Payroll'!I43)/2</f>
-        <v/>
-      </c>
-      <c r="I28" s="52">
-        <f>('Staffing &amp; Payroll'!J30+'Staffing &amp; Payroll'!J42+'Staffing &amp; Payroll'!J38+'Staffing &amp; Payroll'!J43)/2</f>
-        <v/>
-      </c>
-      <c r="J28" s="52">
-        <f>('Staffing &amp; Payroll'!K30+'Staffing &amp; Payroll'!K42+'Staffing &amp; Payroll'!K38+'Staffing &amp; Payroll'!K43)/2</f>
-        <v/>
-      </c>
-      <c r="K28" s="52">
-        <f>('Staffing &amp; Payroll'!L30+'Staffing &amp; Payroll'!L42+'Staffing &amp; Payroll'!L38+'Staffing &amp; Payroll'!L43)/2</f>
-        <v/>
-      </c>
-      <c r="L28" s="52">
-        <f>('Staffing &amp; Payroll'!M30+'Staffing &amp; Payroll'!M42+'Staffing &amp; Payroll'!M38+'Staffing &amp; Payroll'!M43)/2</f>
-        <v/>
-      </c>
-      <c r="M28" s="52">
-        <f>('Staffing &amp; Payroll'!N30+'Staffing &amp; Payroll'!N42+'Staffing &amp; Payroll'!N38+'Staffing &amp; Payroll'!N43)/2</f>
-        <v/>
-      </c>
-      <c r="N28" s="53">
-        <f>(SUM('Staffing &amp; Payroll'!O30:R30)+SUM('Staffing &amp; Payroll'!O42:R42)+SUM('Staffing &amp; Payroll'!O38:R38)+SUM('Staffing &amp; Payroll'!O43:R43))/2</f>
-        <v/>
-      </c>
-      <c r="O28" s="53">
-        <f>(SUM('Staffing &amp; Payroll'!S30:V30)+SUM('Staffing &amp; Payroll'!S42:V42)+SUM('Staffing &amp; Payroll'!S38:V38)+SUM('Staffing &amp; Payroll'!S43:V43))/2</f>
-        <v/>
-      </c>
-      <c r="P28" s="54">
-        <f>SUM(B28:M28)+N28+O28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="56" t="inlineStr">
-        <is>
-          <t>Payroll - 2nd Half</t>
-        </is>
-      </c>
-      <c r="B29" s="52">
-        <f>('Staffing &amp; Payroll'!C30+'Staffing &amp; Payroll'!C42+'Staffing &amp; Payroll'!C38+'Staffing &amp; Payroll'!C43)/2</f>
-        <v/>
-      </c>
-      <c r="C29" s="52">
-        <f>('Staffing &amp; Payroll'!D30+'Staffing &amp; Payroll'!D42+'Staffing &amp; Payroll'!D38+'Staffing &amp; Payroll'!D43)/2</f>
-        <v/>
-      </c>
-      <c r="D29" s="52">
-        <f>('Staffing &amp; Payroll'!E30+'Staffing &amp; Payroll'!E42+'Staffing &amp; Payroll'!E38+'Staffing &amp; Payroll'!E43)/2</f>
-        <v/>
-      </c>
-      <c r="E29" s="52">
-        <f>('Staffing &amp; Payroll'!F30+'Staffing &amp; Payroll'!F42+'Staffing &amp; Payroll'!F38+'Staffing &amp; Payroll'!F43)/2</f>
-        <v/>
-      </c>
-      <c r="F29" s="52">
-        <f>('Staffing &amp; Payroll'!G30+'Staffing &amp; Payroll'!G42+'Staffing &amp; Payroll'!G38+'Staffing &amp; Payroll'!G43)/2</f>
-        <v/>
-      </c>
-      <c r="G29" s="52">
-        <f>('Staffing &amp; Payroll'!H30+'Staffing &amp; Payroll'!H42+'Staffing &amp; Payroll'!H38+'Staffing &amp; Payroll'!H43)/2</f>
-        <v/>
-      </c>
-      <c r="H29" s="52">
-        <f>('Staffing &amp; Payroll'!I30+'Staffing &amp; Payroll'!I42+'Staffing &amp; Payroll'!I38+'Staffing &amp; Payroll'!I43)/2</f>
-        <v/>
-      </c>
-      <c r="I29" s="52">
-        <f>('Staffing &amp; Payroll'!J30+'Staffing &amp; Payroll'!J42+'Staffing &amp; Payroll'!J38+'Staffing &amp; Payroll'!J43)/2</f>
-        <v/>
-      </c>
-      <c r="J29" s="52">
-        <f>('Staffing &amp; Payroll'!K30+'Staffing &amp; Payroll'!K42+'Staffing &amp; Payroll'!K38+'Staffing &amp; Payroll'!K43)/2</f>
-        <v/>
-      </c>
-      <c r="K29" s="52">
-        <f>('Staffing &amp; Payroll'!L30+'Staffing &amp; Payroll'!L42+'Staffing &amp; Payroll'!L38+'Staffing &amp; Payroll'!L43)/2</f>
-        <v/>
-      </c>
-      <c r="L29" s="52">
-        <f>('Staffing &amp; Payroll'!M30+'Staffing &amp; Payroll'!M42+'Staffing &amp; Payroll'!M38+'Staffing &amp; Payroll'!M43)/2</f>
-        <v/>
-      </c>
-      <c r="M29" s="52">
-        <f>('Staffing &amp; Payroll'!N30+'Staffing &amp; Payroll'!N42+'Staffing &amp; Payroll'!N38+'Staffing &amp; Payroll'!N43)/2</f>
-        <v/>
-      </c>
-      <c r="N29" s="53">
-        <f>(SUM('Staffing &amp; Payroll'!O30:R30)+SUM('Staffing &amp; Payroll'!O42:R42)+SUM('Staffing &amp; Payroll'!O38:R38)+SUM('Staffing &amp; Payroll'!O43:R43))/2</f>
-        <v/>
-      </c>
-      <c r="O29" s="53">
-        <f>(SUM('Staffing &amp; Payroll'!S30:V30)+SUM('Staffing &amp; Payroll'!S42:V42)+SUM('Staffing &amp; Payroll'!S38:V38)+SUM('Staffing &amp; Payroll'!S43:V43))/2</f>
-        <v/>
-      </c>
-      <c r="P29" s="54">
-        <f>SUM(B29:M29)+N29+O29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="56" t="inlineStr">
-        <is>
-          <t>Payroll YTD Adjustments</t>
-        </is>
-      </c>
-      <c r="B30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M30" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N30" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O30" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P30" s="54">
-        <f>SUM(B30:M30)+N30+O30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="56" t="inlineStr">
-        <is>
-          <t>Employer Taxes (FUTA/SUI/FICA/WC)</t>
-        </is>
-      </c>
-      <c r="B31" s="52">
-        <f>'Staffing &amp; Payroll'!C48+'Staffing &amp; Payroll'!C49</f>
-        <v/>
-      </c>
-      <c r="C31" s="52">
-        <f>'Staffing &amp; Payroll'!D48+'Staffing &amp; Payroll'!D49</f>
-        <v/>
-      </c>
-      <c r="D31" s="52">
-        <f>'Staffing &amp; Payroll'!E48+'Staffing &amp; Payroll'!E49</f>
-        <v/>
-      </c>
-      <c r="E31" s="52">
-        <f>'Staffing &amp; Payroll'!F48+'Staffing &amp; Payroll'!F49</f>
-        <v/>
-      </c>
-      <c r="F31" s="52">
-        <f>'Staffing &amp; Payroll'!G48+'Staffing &amp; Payroll'!G49</f>
-        <v/>
-      </c>
-      <c r="G31" s="52">
-        <f>'Staffing &amp; Payroll'!H48+'Staffing &amp; Payroll'!H49</f>
-        <v/>
-      </c>
-      <c r="H31" s="52">
-        <f>'Staffing &amp; Payroll'!I48+'Staffing &amp; Payroll'!I49</f>
-        <v/>
-      </c>
-      <c r="I31" s="52">
-        <f>'Staffing &amp; Payroll'!J48+'Staffing &amp; Payroll'!J49</f>
-        <v/>
-      </c>
-      <c r="J31" s="52">
-        <f>'Staffing &amp; Payroll'!K48+'Staffing &amp; Payroll'!K49</f>
-        <v/>
-      </c>
-      <c r="K31" s="52">
-        <f>'Staffing &amp; Payroll'!L48+'Staffing &amp; Payroll'!L49</f>
-        <v/>
-      </c>
-      <c r="L31" s="52">
-        <f>'Staffing &amp; Payroll'!M48+'Staffing &amp; Payroll'!M49</f>
-        <v/>
-      </c>
-      <c r="M31" s="52">
-        <f>'Staffing &amp; Payroll'!N48+'Staffing &amp; Payroll'!N49</f>
-        <v/>
-      </c>
-      <c r="N31" s="53">
-        <f>SUM('Staffing &amp; Payroll'!O48:R48)+SUM('Staffing &amp; Payroll'!O49:R49)</f>
-        <v/>
-      </c>
-      <c r="O31" s="53">
-        <f>SUM('Staffing &amp; Payroll'!S48:V48)+SUM('Staffing &amp; Payroll'!S49:V49)</f>
-        <v/>
-      </c>
-      <c r="P31" s="54">
-        <f>SUM(B31:M31)+N31+O31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="56" t="inlineStr">
-        <is>
-          <t>Contract Labor</t>
-        </is>
-      </c>
-      <c r="B32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M32" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N32" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O32" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P32" s="54">
-        <f>SUM(B32:M32)+N32+O32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="56" t="inlineStr">
-        <is>
-          <t>Medical Director</t>
-        </is>
-      </c>
-      <c r="B33" s="52">
-        <f>'Staffing &amp; Payroll'!C39</f>
-        <v/>
-      </c>
-      <c r="C33" s="52">
-        <f>'Staffing &amp; Payroll'!D39</f>
-        <v/>
-      </c>
-      <c r="D33" s="52">
-        <f>'Staffing &amp; Payroll'!E39</f>
-        <v/>
-      </c>
-      <c r="E33" s="52">
-        <f>'Staffing &amp; Payroll'!F39</f>
-        <v/>
-      </c>
-      <c r="F33" s="52">
-        <f>'Staffing &amp; Payroll'!G39</f>
-        <v/>
-      </c>
-      <c r="G33" s="52">
-        <f>'Staffing &amp; Payroll'!H39</f>
-        <v/>
-      </c>
-      <c r="H33" s="52">
-        <f>'Staffing &amp; Payroll'!I39</f>
-        <v/>
-      </c>
-      <c r="I33" s="52">
-        <f>'Staffing &amp; Payroll'!J39</f>
-        <v/>
-      </c>
-      <c r="J33" s="52">
-        <f>'Staffing &amp; Payroll'!K39</f>
-        <v/>
-      </c>
-      <c r="K33" s="52">
-        <f>'Staffing &amp; Payroll'!L39</f>
-        <v/>
-      </c>
-      <c r="L33" s="52">
-        <f>'Staffing &amp; Payroll'!M39</f>
-        <v/>
-      </c>
-      <c r="M33" s="52">
-        <f>'Staffing &amp; Payroll'!N39</f>
-        <v/>
-      </c>
-      <c r="N33" s="53">
-        <f>SUM('Staffing &amp; Payroll'!O39:R39)</f>
-        <v/>
-      </c>
-      <c r="O33" s="53">
-        <f>SUM('Staffing &amp; Payroll'!S39:V39)</f>
-        <v/>
-      </c>
-      <c r="P33" s="54">
-        <f>SUM(B33:M33)+N33+O33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="56" t="inlineStr">
-        <is>
-          <t>Medical Director 2</t>
-        </is>
-      </c>
-      <c r="B34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M34" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N34" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O34" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P34" s="54">
-        <f>SUM(B34:M34)+N34+O34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="56" t="inlineStr">
-        <is>
-          <t>Intercompany Transfer</t>
-        </is>
-      </c>
-      <c r="B35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M35" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N35" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O35" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P35" s="54">
-        <f>SUM(B35:M35)+N35+O35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="56" t="inlineStr">
-        <is>
-          <t>Staff Other (health insurance)</t>
-        </is>
-      </c>
-      <c r="B36" s="52">
-        <f>'Staffing &amp; Payroll'!C50+'Staffing &amp; Payroll'!C51</f>
-        <v/>
-      </c>
-      <c r="C36" s="52">
-        <f>'Staffing &amp; Payroll'!D50+'Staffing &amp; Payroll'!D51</f>
-        <v/>
-      </c>
-      <c r="D36" s="52">
-        <f>'Staffing &amp; Payroll'!E50+'Staffing &amp; Payroll'!E51</f>
-        <v/>
-      </c>
-      <c r="E36" s="52">
-        <f>'Staffing &amp; Payroll'!F50+'Staffing &amp; Payroll'!F51</f>
-        <v/>
-      </c>
-      <c r="F36" s="52">
-        <f>'Staffing &amp; Payroll'!G50+'Staffing &amp; Payroll'!G51</f>
-        <v/>
-      </c>
-      <c r="G36" s="52">
-        <f>'Staffing &amp; Payroll'!H50+'Staffing &amp; Payroll'!H51</f>
-        <v/>
-      </c>
-      <c r="H36" s="52">
-        <f>'Staffing &amp; Payroll'!I50+'Staffing &amp; Payroll'!I51</f>
-        <v/>
-      </c>
-      <c r="I36" s="52">
-        <f>'Staffing &amp; Payroll'!J50+'Staffing &amp; Payroll'!J51</f>
-        <v/>
-      </c>
-      <c r="J36" s="52">
-        <f>'Staffing &amp; Payroll'!K50+'Staffing &amp; Payroll'!K51</f>
-        <v/>
-      </c>
-      <c r="K36" s="52">
-        <f>'Staffing &amp; Payroll'!L50+'Staffing &amp; Payroll'!L51</f>
-        <v/>
-      </c>
-      <c r="L36" s="52">
-        <f>'Staffing &amp; Payroll'!M50+'Staffing &amp; Payroll'!M51</f>
-        <v/>
-      </c>
-      <c r="M36" s="52">
-        <f>'Staffing &amp; Payroll'!N50+'Staffing &amp; Payroll'!N51</f>
-        <v/>
-      </c>
-      <c r="N36" s="53">
-        <f>SUM('Staffing &amp; Payroll'!O50:R50)+SUM('Staffing &amp; Payroll'!O51:R51)</f>
-        <v/>
-      </c>
-      <c r="O36" s="53">
-        <f>SUM('Staffing &amp; Payroll'!S50:V50)+SUM('Staffing &amp; Payroll'!S51:V51)</f>
-        <v/>
-      </c>
-      <c r="P36" s="54">
-        <f>SUM(B36:M36)+N36+O36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Total Payroll &amp; Related</t>
-        </is>
-      </c>
-      <c r="B37" s="55">
-        <f>SUM(B28:B36)</f>
-        <v/>
-      </c>
-      <c r="C37" s="55">
-        <f>SUM(C28:C36)</f>
-        <v/>
-      </c>
-      <c r="D37" s="55">
-        <f>SUM(D28:D36)</f>
-        <v/>
-      </c>
-      <c r="E37" s="55">
-        <f>SUM(E28:E36)</f>
-        <v/>
-      </c>
-      <c r="F37" s="55">
-        <f>SUM(F28:F36)</f>
-        <v/>
-      </c>
-      <c r="G37" s="55">
-        <f>SUM(G28:G36)</f>
-        <v/>
-      </c>
-      <c r="H37" s="55">
-        <f>SUM(H28:H36)</f>
-        <v/>
-      </c>
-      <c r="I37" s="55">
-        <f>SUM(I28:I36)</f>
-        <v/>
-      </c>
-      <c r="J37" s="55">
-        <f>SUM(J28:J36)</f>
-        <v/>
-      </c>
-      <c r="K37" s="55">
-        <f>SUM(K28:K36)</f>
-        <v/>
-      </c>
-      <c r="L37" s="55">
-        <f>SUM(L28:L36)</f>
-        <v/>
-      </c>
-      <c r="M37" s="55">
-        <f>SUM(M28:M36)</f>
-        <v/>
-      </c>
-      <c r="N37" s="55">
-        <f>SUM(N28:N36)</f>
-        <v/>
-      </c>
-      <c r="O37" s="55">
-        <f>SUM(O28:O36)</f>
-        <v/>
-      </c>
-      <c r="P37" s="55">
-        <f>SUM(P28:P36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>General &amp; Administrative</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="56" t="inlineStr">
-        <is>
-          <t>Bank / Payroll Fees</t>
-        </is>
-      </c>
-      <c r="B40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="C40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="D40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="E40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="F40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="G40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="H40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="I40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="J40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="K40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="L40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="M40" s="52">
-        <f>Inputs!$B$101</f>
-        <v/>
-      </c>
-      <c r="N40" s="53">
-        <f>Inputs!$B$101*12</f>
-        <v/>
-      </c>
-      <c r="O40" s="53">
-        <f>Inputs!$B$101*12</f>
-        <v/>
-      </c>
-      <c r="P40" s="54">
-        <f>SUM(B40:M40)+N40+O40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="56" t="inlineStr">
-        <is>
-          <t>Triple Net Rent</t>
-        </is>
-      </c>
-      <c r="B41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="C41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="D41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="E41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="F41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="G41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="H41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="I41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="J41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="K41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="L41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="M41" s="52">
-        <f>Inputs!$B$102</f>
-        <v/>
-      </c>
-      <c r="N41" s="53">
-        <f>Inputs!$B$102*12</f>
-        <v/>
-      </c>
-      <c r="O41" s="53">
-        <f>Inputs!$B$102*12</f>
-        <v/>
-      </c>
-      <c r="P41" s="54">
-        <f>SUM(B41:M41)+N41+O41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="56" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="B42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="C42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="D42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="E42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="F42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="G42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="H42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="I42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="J42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="K42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="L42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="M42" s="52">
-        <f>Inputs!$B$91</f>
-        <v/>
-      </c>
-      <c r="N42" s="53">
-        <f>Inputs!$B$91*12</f>
-        <v/>
-      </c>
-      <c r="O42" s="53">
-        <f>Inputs!$B$91*12</f>
-        <v/>
-      </c>
-      <c r="P42" s="54">
-        <f>SUM(B42:M42)+N42+O42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="56" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="B43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="C43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="D43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="E43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="F43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="G43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="H43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="I43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="J43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="K43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="L43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="M43" s="52">
-        <f>Inputs!$B$92</f>
-        <v/>
-      </c>
-      <c r="N43" s="53">
-        <f>Inputs!$B$92*12</f>
-        <v/>
-      </c>
-      <c r="O43" s="53">
-        <f>Inputs!$B$92*12</f>
-        <v/>
-      </c>
-      <c r="P43" s="54">
-        <f>SUM(B43:M43)+N43+O43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="56" t="inlineStr">
-        <is>
-          <t>Telephone / Fax</t>
-        </is>
-      </c>
-      <c r="B44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="C44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="D44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="E44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="F44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="G44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="H44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="I44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="J44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="K44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="L44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="M44" s="52">
-        <f>Inputs!$B$93</f>
-        <v/>
-      </c>
-      <c r="N44" s="53">
-        <f>Inputs!$B$93*12</f>
-        <v/>
-      </c>
-      <c r="O44" s="53">
-        <f>Inputs!$B$93*12</f>
-        <v/>
-      </c>
-      <c r="P44" s="54">
-        <f>SUM(B44:M44)+N44+O44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="56" t="inlineStr">
-        <is>
-          <t>After Hours Messaging (BVTM)</t>
-        </is>
-      </c>
-      <c r="B45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="C45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="D45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="E45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="F45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="G45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="H45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="I45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="J45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="K45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="L45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="M45" s="52">
-        <f>Inputs!$B$94</f>
-        <v/>
-      </c>
-      <c r="N45" s="53">
-        <f>Inputs!$B$94*12</f>
-        <v/>
-      </c>
-      <c r="O45" s="53">
-        <f>Inputs!$B$94*12</f>
-        <v/>
-      </c>
-      <c r="P45" s="54">
-        <f>SUM(B45:M45)+N45+O45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="56" t="inlineStr">
-        <is>
-          <t>CFO / AP Support</t>
-        </is>
-      </c>
-      <c r="B46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M46" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N46" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O46" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P46" s="54">
-        <f>SUM(B46:M46)+N46+O46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="56" t="inlineStr">
-        <is>
-          <t>Support Services</t>
-        </is>
-      </c>
-      <c r="B47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M47" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N47" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O47" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P47" s="54">
-        <f>SUM(B47:M47)+N47+O47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="56" t="inlineStr">
-        <is>
-          <t>Messaging / CRG Signer</t>
-        </is>
-      </c>
-      <c r="B48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M48" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N48" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O48" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P48" s="54">
-        <f>SUM(B48:M48)+N48+O48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="56" t="inlineStr">
-        <is>
-          <t>NM Room &amp; Board</t>
-        </is>
-      </c>
-      <c r="B49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M49" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N49" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O49" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P49" s="54">
-        <f>SUM(B49:M49)+N49+O49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="56" t="inlineStr">
-        <is>
-          <t>Corporate Labor</t>
-        </is>
-      </c>
-      <c r="B50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M50" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N50" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O50" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P50" s="54">
-        <f>SUM(B50:M50)+N50+O50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="56" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="C51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="D51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="E51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="F51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="G51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="H51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="I51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="J51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="K51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="L51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="M51" s="52">
-        <f>Inputs!$B$103</f>
-        <v/>
-      </c>
-      <c r="N51" s="53">
-        <f>Inputs!$B$103*12</f>
-        <v/>
-      </c>
-      <c r="O51" s="53">
-        <f>Inputs!$B$103*12</f>
-        <v/>
-      </c>
-      <c r="P51" s="54">
-        <f>SUM(B51:M51)+N51+O51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="56" t="inlineStr">
-        <is>
-          <t>Outsourced Billing Fee (1.5%)</t>
-        </is>
-      </c>
-      <c r="B52" s="52">
-        <f>'Revenue Model'!C14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="C52" s="52">
-        <f>'Revenue Model'!D14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="D52" s="52">
-        <f>'Revenue Model'!E14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="E52" s="52">
-        <f>'Revenue Model'!F14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="F52" s="52">
-        <f>'Revenue Model'!G14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="G52" s="52">
-        <f>'Revenue Model'!H14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="H52" s="52">
-        <f>'Revenue Model'!I14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="I52" s="52">
-        <f>'Revenue Model'!J14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="J52" s="52">
-        <f>'Revenue Model'!K14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="K52" s="52">
-        <f>'Revenue Model'!L14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="L52" s="52">
-        <f>'Revenue Model'!M14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="M52" s="52">
-        <f>'Revenue Model'!N14*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="N52" s="53">
-        <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="O52" s="53">
-        <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$106</f>
-        <v/>
-      </c>
-      <c r="P52" s="54">
-        <f>SUM(B52:M52)+N52+O52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="56" t="inlineStr">
-        <is>
-          <t>EMR System</t>
-        </is>
-      </c>
-      <c r="B53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="C53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="D53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="E53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="F53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="G53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="H53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="I53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="J53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="K53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="L53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="M53" s="52">
-        <f>Inputs!$B$95</f>
-        <v/>
-      </c>
-      <c r="N53" s="53">
-        <f>Inputs!$B$95*12</f>
-        <v/>
-      </c>
-      <c r="O53" s="53">
-        <f>Inputs!$B$95*12</f>
-        <v/>
-      </c>
-      <c r="P53" s="54">
-        <f>SUM(B53:M53)+N53+O53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="56" t="inlineStr">
-        <is>
-          <t>Other EMR</t>
-        </is>
-      </c>
-      <c r="B54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M54" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N54" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O54" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P54" s="54">
-        <f>SUM(B54:M54)+N54+O54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="56" t="inlineStr">
-        <is>
-          <t>PCR (CPM)</t>
-        </is>
-      </c>
-      <c r="B55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="C55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="D55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="E55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="F55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="G55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="H55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="I55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="J55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="K55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="L55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="M55" s="52">
-        <f>Inputs!$B$96</f>
-        <v/>
-      </c>
-      <c r="N55" s="53">
-        <f>Inputs!$B$96*12</f>
-        <v/>
-      </c>
-      <c r="O55" s="53">
-        <f>Inputs!$B$96*12</f>
-        <v/>
-      </c>
-      <c r="P55" s="54">
-        <f>SUM(B55:M55)+N55+O55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="56" t="inlineStr">
-        <is>
-          <t>Ancillary</t>
-        </is>
-      </c>
-      <c r="B56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M56" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N56" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O56" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P56" s="54">
-        <f>SUM(B56:M56)+N56+O56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="56" t="inlineStr">
-        <is>
-          <t>Liability Insurance (D&amp;O)</t>
-        </is>
-      </c>
-      <c r="B57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="C57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="D57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="E57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="F57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="G57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="H57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="I57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="J57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="K57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="L57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="M57" s="52">
-        <f>Inputs!$B$98</f>
-        <v/>
-      </c>
-      <c r="N57" s="53">
-        <f>Inputs!$B$98*12</f>
-        <v/>
-      </c>
-      <c r="O57" s="53">
-        <f>Inputs!$B$98*12</f>
-        <v/>
-      </c>
-      <c r="P57" s="54">
-        <f>SUM(B57:M57)+N57+O57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="56" t="inlineStr">
-        <is>
-          <t>QR Payment Fee (0.75%)</t>
-        </is>
-      </c>
-      <c r="B58" s="52">
-        <f>'Revenue Model'!C14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="C58" s="52">
-        <f>'Revenue Model'!D14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="D58" s="52">
-        <f>'Revenue Model'!E14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="E58" s="52">
-        <f>'Revenue Model'!F14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="F58" s="52">
-        <f>'Revenue Model'!G14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="G58" s="52">
-        <f>'Revenue Model'!H14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="H58" s="52">
-        <f>'Revenue Model'!I14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="I58" s="52">
-        <f>'Revenue Model'!J14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="J58" s="52">
-        <f>'Revenue Model'!K14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="K58" s="52">
-        <f>'Revenue Model'!L14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="L58" s="52">
-        <f>'Revenue Model'!M14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="M58" s="52">
-        <f>'Revenue Model'!N14*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="N58" s="53">
-        <f>SUM('Revenue Model'!O14:R14)*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="O58" s="53">
-        <f>SUM('Revenue Model'!S14:V14)*Inputs!$B$107</f>
-        <v/>
-      </c>
-      <c r="P58" s="54">
-        <f>SUM(B58:M58)+N58+O58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="56" t="inlineStr">
-        <is>
-          <t>Training / CEUs</t>
-        </is>
-      </c>
-      <c r="B59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="C59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="D59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="E59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="F59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="G59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="H59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="I59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="J59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="K59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="L59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="M59" s="52">
-        <f>Inputs!$B$99</f>
-        <v/>
-      </c>
-      <c r="N59" s="53">
-        <f>Inputs!$B$99*12</f>
-        <v/>
-      </c>
-      <c r="O59" s="53">
-        <f>Inputs!$B$99*12</f>
-        <v/>
-      </c>
-      <c r="P59" s="54">
-        <f>SUM(B59:M59)+N59+O59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="56" t="inlineStr">
-        <is>
-          <t>Credit Card Fees</t>
-        </is>
-      </c>
-      <c r="B60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="C60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="D60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="E60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="F60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="G60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="H60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="I60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="J60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="K60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="L60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="M60" s="52">
-        <f>Inputs!$B$97</f>
-        <v/>
-      </c>
-      <c r="N60" s="53">
-        <f>Inputs!$B$97*12</f>
-        <v/>
-      </c>
-      <c r="O60" s="53">
-        <f>Inputs!$B$97*12</f>
-        <v/>
-      </c>
-      <c r="P60" s="54">
-        <f>SUM(B60:M60)+N60+O60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="56" t="inlineStr">
-        <is>
-          <t>Other (QPf)</t>
-        </is>
-      </c>
-      <c r="B61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="C61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="J61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="K61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="L61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M61" s="52">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N61" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="O61" s="53">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="P61" s="54">
-        <f>SUM(B61:M61)+N61+O61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="56" t="inlineStr">
-        <is>
-          <t>Other (Client)</t>
-        </is>
-      </c>
-      <c r="B62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="C62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="D62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="E62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="F62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="G62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="H62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="I62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="J62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="K62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="L62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="M62" s="52">
-        <f>Inputs!$B$100</f>
-        <v/>
-      </c>
-      <c r="N62" s="53">
-        <f>Inputs!$B$100*12</f>
-        <v/>
-      </c>
-      <c r="O62" s="53">
-        <f>Inputs!$B$100*12</f>
-        <v/>
-      </c>
-      <c r="P62" s="54">
-        <f>SUM(B62:M62)+N62+O62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Total General &amp; Administrative</t>
-        </is>
-      </c>
-      <c r="B63" s="55">
-        <f>SUM(B40:B62)</f>
-        <v/>
-      </c>
-      <c r="C63" s="55">
-        <f>SUM(C40:C62)</f>
-        <v/>
-      </c>
-      <c r="D63" s="55">
-        <f>SUM(D40:D62)</f>
-        <v/>
-      </c>
-      <c r="E63" s="55">
-        <f>SUM(E40:E62)</f>
-        <v/>
-      </c>
-      <c r="F63" s="55">
-        <f>SUM(F40:F62)</f>
-        <v/>
-      </c>
-      <c r="G63" s="55">
-        <f>SUM(G40:G62)</f>
-        <v/>
-      </c>
-      <c r="H63" s="55">
-        <f>SUM(H40:H62)</f>
-        <v/>
-      </c>
-      <c r="I63" s="55">
-        <f>SUM(I40:I62)</f>
-        <v/>
-      </c>
-      <c r="J63" s="55">
-        <f>SUM(J40:J62)</f>
-        <v/>
-      </c>
-      <c r="K63" s="55">
-        <f>SUM(K40:K62)</f>
-        <v/>
-      </c>
-      <c r="L63" s="55">
-        <f>SUM(L40:L62)</f>
-        <v/>
-      </c>
-      <c r="M63" s="55">
-        <f>SUM(M40:M62)</f>
-        <v/>
-      </c>
-      <c r="N63" s="55">
-        <f>SUM(N40:N62)</f>
-        <v/>
-      </c>
-      <c r="O63" s="55">
-        <f>SUM(O40:O62)</f>
-        <v/>
-      </c>
-      <c r="P63" s="55">
-        <f>SUM(P40:P62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="28" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B65" s="55">
-        <f>B37+B63</f>
-        <v/>
-      </c>
-      <c r="C65" s="55">
-        <f>C37+C63</f>
-        <v/>
-      </c>
-      <c r="D65" s="55">
-        <f>D37+D63</f>
-        <v/>
-      </c>
-      <c r="E65" s="55">
-        <f>E37+E63</f>
-        <v/>
-      </c>
-      <c r="F65" s="55">
-        <f>F37+F63</f>
-        <v/>
-      </c>
-      <c r="G65" s="55">
-        <f>G37+G63</f>
-        <v/>
-      </c>
-      <c r="H65" s="55">
-        <f>H37+H63</f>
-        <v/>
-      </c>
-      <c r="I65" s="55">
-        <f>I37+I63</f>
-        <v/>
-      </c>
-      <c r="J65" s="55">
-        <f>J37+J63</f>
-        <v/>
-      </c>
-      <c r="K65" s="55">
-        <f>K37+K63</f>
-        <v/>
-      </c>
-      <c r="L65" s="55">
-        <f>L37+L63</f>
-        <v/>
-      </c>
-      <c r="M65" s="55">
-        <f>M37+M63</f>
-        <v/>
-      </c>
-      <c r="N65" s="55">
-        <f>N37+N63</f>
-        <v/>
-      </c>
-      <c r="O65" s="55">
-        <f>O37+O63</f>
-        <v/>
-      </c>
-      <c r="P65" s="55">
-        <f>P37+P63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="B67" s="57">
-        <f>B24-B65</f>
-        <v/>
-      </c>
-      <c r="C67" s="57">
-        <f>C24-C65</f>
-        <v/>
-      </c>
-      <c r="D67" s="57">
-        <f>D24-D65</f>
-        <v/>
-      </c>
-      <c r="E67" s="57">
-        <f>E24-E65</f>
-        <v/>
-      </c>
-      <c r="F67" s="57">
-        <f>F24-F65</f>
-        <v/>
-      </c>
-      <c r="G67" s="57">
-        <f>G24-G65</f>
-        <v/>
-      </c>
-      <c r="H67" s="57">
-        <f>H24-H65</f>
-        <v/>
-      </c>
-      <c r="I67" s="57">
-        <f>I24-I65</f>
-        <v/>
-      </c>
-      <c r="J67" s="57">
-        <f>J24-J65</f>
-        <v/>
-      </c>
-      <c r="K67" s="57">
-        <f>K24-K65</f>
-        <v/>
-      </c>
-      <c r="L67" s="57">
-        <f>L24-L65</f>
-        <v/>
-      </c>
-      <c r="M67" s="57">
-        <f>M24-M65</f>
-        <v/>
-      </c>
-      <c r="N67" s="57">
-        <f>N24-N65</f>
-        <v/>
-      </c>
-      <c r="O67" s="57">
-        <f>O24-O65</f>
-        <v/>
-      </c>
-      <c r="P67" s="57">
-        <f>P24-P65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>Net Margin %</t>
-        </is>
-      </c>
-      <c r="B69" s="32">
-        <f>IF(B12=0,0,B67/B12)</f>
-        <v/>
-      </c>
-      <c r="C69" s="32">
-        <f>IF(C12=0,0,C67/C12)</f>
-        <v/>
-      </c>
-      <c r="D69" s="32">
-        <f>IF(D12=0,0,D67/D12)</f>
-        <v/>
-      </c>
-      <c r="E69" s="32">
-        <f>IF(E12=0,0,E67/E12)</f>
-        <v/>
-      </c>
-      <c r="F69" s="32">
-        <f>IF(F12=0,0,F67/F12)</f>
-        <v/>
-      </c>
-      <c r="G69" s="32">
-        <f>IF(G12=0,0,G67/G12)</f>
-        <v/>
-      </c>
-      <c r="H69" s="32">
-        <f>IF(H12=0,0,H67/H12)</f>
-        <v/>
-      </c>
-      <c r="I69" s="32">
-        <f>IF(I12=0,0,I67/I12)</f>
-        <v/>
-      </c>
-      <c r="J69" s="32">
-        <f>IF(J12=0,0,J67/J12)</f>
-        <v/>
-      </c>
-      <c r="K69" s="32">
-        <f>IF(K12=0,0,K67/K12)</f>
-        <v/>
-      </c>
-      <c r="L69" s="32">
-        <f>IF(L12=0,0,L67/L12)</f>
-        <v/>
-      </c>
-      <c r="M69" s="32">
-        <f>IF(M12=0,0,M67/M12)</f>
-        <v/>
-      </c>
-      <c r="N69" s="32">
-        <f>IF(N12=0,0,N67/N12)</f>
-        <v/>
-      </c>
-      <c r="O69" s="32">
-        <f>IF(O12=0,0,O67/O12)</f>
-        <v/>
-      </c>
-      <c r="P69" s="32">
-        <f>IF(P12=0,0,P67/P12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="33" t="inlineStr">
-        <is>
-          <t>Cash-basis operating P&amp;L (QuickBooks layout): all payroll is in Operating Expenses, Cost of Services holds patient supplies only. "Net Income" here = operating result and ties to the engine's EBITDA; interest, D&amp;A and tax are below EBITDA on the Operating Budget / 3-statement tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A71:H72"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>